--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2074,7 +2074,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18256,7 +18256,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="GX29" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY29" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="HB29" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC29" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="GX30" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY30" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="HB30" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC30" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="GX31" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY31" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="HB31" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC31" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="GX32" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY32" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="HB32" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC32" t="inlineStr">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="GX33" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY33" t="inlineStr">
@@ -23042,7 +23042,7 @@
       </c>
       <c r="HB33" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC33" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="GX34" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY34" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="HB34" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC34" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="GX35" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY35" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="HB35" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC35" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="GX36" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY36" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="HB36" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC36" t="inlineStr">
@@ -25756,7 +25756,7 @@
       </c>
       <c r="GX37" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY37" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="HB37" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC37" t="inlineStr">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="GX38" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY38" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="HB38" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC38" t="inlineStr">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="GX39" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY39" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="HB39" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC39" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="GX40" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY40" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="HB40" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC40" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="GX41" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY41" t="inlineStr">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="HB41" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC41" t="inlineStr">
@@ -29266,7 +29266,7 @@
       </c>
       <c r="GX42" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY42" t="inlineStr">
@@ -29286,7 +29286,7 @@
       </c>
       <c r="HB42" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC42" t="inlineStr">
@@ -29968,7 +29968,7 @@
       </c>
       <c r="GX43" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY43" t="inlineStr">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="HB43" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC43" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="GX44" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY44" t="inlineStr">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="HB44" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC44" t="inlineStr">
@@ -31372,7 +31372,7 @@
       </c>
       <c r="GX45" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY45" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="HB45" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC45" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="GX46" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY46" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="HB46" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC46" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="GX47" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY47" t="inlineStr">
@@ -32796,7 +32796,7 @@
       </c>
       <c r="HB47" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC47" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="GX48" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY48" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="HB48" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC48" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="GX49" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY49" t="inlineStr">
@@ -34126,7 +34126,7 @@
       </c>
       <c r="HB49" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC49" t="inlineStr">
@@ -34808,7 +34808,7 @@
       </c>
       <c r="GX50" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY50" t="inlineStr">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="HB50" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC50" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="GX51" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY51" t="inlineStr">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="HB51" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC51" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="GX52" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY52" t="inlineStr">
@@ -36232,7 +36232,7 @@
       </c>
       <c r="HB52" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC52" t="inlineStr">
@@ -36914,7 +36914,7 @@
       </c>
       <c r="GX53" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY53" t="inlineStr">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="HB53" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC53" t="inlineStr">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="GX54" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY54" t="inlineStr">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="HB54" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC54" t="inlineStr">
@@ -38318,7 +38318,7 @@
       </c>
       <c r="GX55" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY55" t="inlineStr">
@@ -38338,7 +38338,7 @@
       </c>
       <c r="HB55" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC55" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="GX56" t="inlineStr">
         <is>
-          <t>2026-10-04 02:40:18 AM</t>
+          <t>2026-10-04 11:48:09 AM</t>
         </is>
       </c>
       <c r="GY56" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="HB56" t="inlineStr">
         <is>
-          <t>2026-10-04T02:40:18.768935-04:00</t>
+          <t>2026-10-04T11:48:09.675210-04:00</t>
         </is>
       </c>
       <c r="HC56" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD28"/>
+  <dimension ref="A1:HD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14831,26 +14831,26 @@
         <v>849809</v>
       </c>
       <c r="D21" t="n">
-        <v>808975</v>
+        <v>669003</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hyeseong Kim</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -14879,35 +14879,35 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/808975</t>
+          <t>https://www.mlb.com/player/669003</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Hyeseong+Kim</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Garrett+Mitchell</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>694819</v>
+        <v>669373</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/694819</t>
+          <t>https://www.mlb.com/player/669373</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -14920,127 +14920,127 @@
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
-        <v>277</v>
+        <v>725</v>
       </c>
       <c r="AB21" t="n">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2707581227436823</v>
+        <v>0.2551724137931035</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.456140350877193</v>
+        <v>0.5271966527196653</v>
       </c>
       <c r="AE21" t="n">
-        <v>116</v>
+        <v>461</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="AG21" t="n">
-        <v>131</v>
+        <v>531</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.2586206896551724</v>
+        <v>0.262472885032538</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.456140350877193</v>
+        <v>0.5246913580246914</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AN21" t="n">
         <v>18</v>
       </c>
       <c r="AO21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AR21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AS21" t="n">
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.3</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AV21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>102</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.2156862745098039</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>202</v>
+      </c>
+      <c r="BE21" t="n">
         <v>51</v>
       </c>
-      <c r="AW21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>100</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>200</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>61</v>
-      </c>
       <c r="BF21" t="n">
-        <v>0.305</v>
+        <v>0.2524752475247525</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.456140350877193</v>
+        <v>0.53</v>
       </c>
       <c r="BH21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BK21" t="n">
         <v>5</v>
       </c>
       <c r="BL21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BM21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN21" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="BO21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
@@ -15048,88 +15048,88 @@
         </is>
       </c>
       <c r="BQ21" t="n">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="BR21" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="BS21" t="n">
-        <v>0.2766352501289324</v>
+        <v>0.2426287356321839</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.6692991208399384</v>
+        <v>0.6211121176235388</v>
       </c>
       <c r="BU21" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="BV21" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.2336448598130841</v>
       </c>
       <c r="BX21" t="n">
         <v>100</v>
       </c>
       <c r="BY21" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.2766352501289324</v>
+        <v>0.2426287356321839</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.2682303207384037</v>
+        <v>0.2469715517241379</v>
       </c>
       <c r="CB21" t="n">
-        <v>0.2616809695719444</v>
+        <v>0.2372402434077079</v>
       </c>
       <c r="CC21" t="n">
-        <v>0.2664110301701909</v>
+        <v>0.2441057124160692</v>
       </c>
       <c r="CD21" t="n">
-        <v>0.2682303207384037</v>
+        <v>0.2469715517241379</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.2682303207384037</v>
+        <v>0.2469715517241379</v>
       </c>
       <c r="CF21" t="n">
-        <v>0.2616809695719444</v>
+        <v>0.2372402434077079</v>
       </c>
       <c r="CG21" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.2336448598130841</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2375</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.242603550295858</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0.2810058493614052</v>
+        <v>0.2641632632161495</v>
       </c>
       <c r="CK21" t="n">
-        <v>0.2753082001031459</v>
+        <v>0.2555780689991869</v>
       </c>
       <c r="CL21" t="n">
-        <v>0.2808899626095925</v>
+        <v>0.2635896521070157</v>
       </c>
       <c r="CM21" t="n">
-        <v>0.2810058493614052</v>
+        <v>0.2641632632161495</v>
       </c>
       <c r="CN21" t="n">
-        <v>0.2810058493614052</v>
+        <v>0.2641632632161495</v>
       </c>
       <c r="CO21" t="n">
-        <v>0.2753082001031459</v>
+        <v>0.2555780689991869</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="CQ21" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2601769911504425</v>
       </c>
       <c r="CR21" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2624633431085044</v>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -15137,124 +15137,124 @@
         </is>
       </c>
       <c r="CT21" t="n">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="CU21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="CV21" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.2336448598130841</v>
       </c>
       <c r="CW21" t="n">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="CX21" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="CY21" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="CZ21" t="n">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="DA21" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="DB21" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2375</v>
       </c>
       <c r="DC21" t="n">
-        <v>242</v>
+        <v>565</v>
       </c>
       <c r="DD21" t="n">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2601769911504425</v>
       </c>
       <c r="DF21" t="n">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="DG21" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.242603550295858</v>
       </c>
       <c r="DI21" t="n">
-        <v>242</v>
+        <v>682</v>
       </c>
       <c r="DJ21" t="n">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="DK21" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2624633431085044</v>
       </c>
       <c r="DL21" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="DM21" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.3789473684210526</v>
+        <v>0.3</v>
       </c>
       <c r="DO21" t="n">
-        <v>0.06616541353383458</v>
+        <v>0.04354838709677419</v>
       </c>
       <c r="DP21" t="n">
-        <v>4.946564885496183</v>
+        <v>7.147058823529412</v>
       </c>
       <c r="DQ21" t="n">
-        <v>0.7213740458015268</v>
+        <v>0.7941176470588236</v>
       </c>
       <c r="DR21" t="n">
-        <v>665</v>
+        <v>620</v>
       </c>
       <c r="DS21" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="DT21" t="n">
         <v>14</v>
       </c>
       <c r="DU21" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="DV21" t="n">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="DW21" t="n">
-        <v>174.6666666666667</v>
+        <v>158.6666666666667</v>
       </c>
       <c r="DX21" t="n">
-        <v>0.5496183206106871</v>
+        <v>0.7941176470588236</v>
       </c>
       <c r="DY21" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ21" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EA21" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EB21" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EC21" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="ED21" t="n">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="EE21" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="EF21" t="n">
-        <v>455</v>
+        <v>669</v>
       </c>
       <c r="EG21" t="n">
-        <v>394</v>
+        <v>2748</v>
       </c>
       <c r="EH21" t="inlineStr">
         <is>
@@ -15262,150 +15262,150 @@
         </is>
       </c>
       <c r="EI21" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EJ21" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EK21" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EL21" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="EM21" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EN21" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EO21" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EP21" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="EQ21" t="n">
-        <v>0.9623202290076336</v>
+        <v>0.9654033088235294</v>
       </c>
       <c r="ER21" t="n">
-        <v>0.9623202290076336</v>
+        <v>0.9654033088235294</v>
       </c>
       <c r="ES21" t="n">
         <v>0.97</v>
       </c>
       <c r="ET21" t="inlineStr">
         <is>
-          <t>{'era': 1.8, 'whip': 0.8, 'k_rate': 0.37894736842105264, 'bb_rate': 0.06616541353383458, 'hits_per_9': 4.9465648854961835, 'hr_per_9': 0.7213740458015268, 'batters_faced': 665, 'baa_vs_lhb_season': 0.11411411411411411, 'baa_vs_rhb_season': 0.20938628158844766, 'baa_vs_lhb_career': 0.14285714285714285, 'baa_vs_rhb_career': 0.20812182741116753, 'pitcher': 'Jacob Misiorowski', 'pitcher_id': 694819, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/694819', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski', 'hitter': 'Hyeseong Kim', 'hitter_id': 808975, 'bats': 'L', 'team': 'LAD', 'opp': 'MIL', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Garrett Mitchell', 'hitter_id': 669003, 'bats': 'L', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU21" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="EV21" t="n">
         <v>3.32</v>
       </c>
       <c r="EW21" t="n">
-        <v>3.117026105125171</v>
+        <v>3.001424228192964</v>
       </c>
       <c r="EX21" t="n">
-        <v>2.760114719042136</v>
+        <v>2.605756250841726</v>
       </c>
       <c r="EY21" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="EZ21" t="n">
         <v>0.995</v>
       </c>
       <c r="FA21" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="FB21" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="FC21" t="n">
-        <v>0.2675721399228184</v>
+        <v>0.2491003037463022</v>
       </c>
       <c r="FD21" t="n">
-        <v>0.2785548689692484</v>
+        <v>0.240382766677409</v>
       </c>
       <c r="FE21" t="n">
-        <v>0.2785548689692484</v>
+        <v>0.2427602767871071</v>
       </c>
       <c r="FF21" t="n">
-        <v>0.2906022408963586</v>
+        <v>0.3043724340175953</v>
       </c>
       <c r="FG21" t="n">
-        <v>0.2836932106042965</v>
+        <v>0.2877907949362074</v>
       </c>
       <c r="FH21" t="n">
-        <v>0.2737687513594135</v>
+        <v>0.2541625840727266</v>
       </c>
       <c r="FI21" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ21" t="n">
-        <v>0.2463918762234721</v>
+        <v>0.228746325665454</v>
       </c>
       <c r="FK21" t="n">
-        <v>0.2451599168423548</v>
+        <v>0.2276025940371267</v>
       </c>
       <c r="FL21" t="n">
-        <v>0.2586206896551724</v>
+        <v>0.262472885032538</v>
       </c>
       <c r="FM21" t="n">
-        <v>0.2586206896551724</v>
+        <v>0.262472885032538</v>
       </c>
       <c r="FN21" t="n">
-        <v>0.2451599168423548</v>
+        <v>0.2276025940371267</v>
       </c>
       <c r="FO21" t="n">
-        <v>-0.01346077281281766</v>
+        <v>-0.03487029099541125</v>
       </c>
       <c r="FP21" t="n">
-        <v>0.01346077281281766</v>
+        <v>0.03487029099541125</v>
       </c>
       <c r="FQ21" t="n">
-        <v>0.6766694949957295</v>
+        <v>0.5930768821200347</v>
       </c>
       <c r="FR21" t="n">
-        <v>0.49169290431957</v>
+        <v>0.4473756937010537</v>
       </c>
       <c r="FS21" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="FT21" t="n">
-        <v>0.2877124183006536</v>
+        <v>0.3057634408602151</v>
       </c>
       <c r="FU21" t="n">
-        <v>37.7782491659549</v>
+        <v>23.84614702000578</v>
       </c>
       <c r="FV21" t="n">
-        <v>24.99999999999999</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="FW21" t="n">
-        <v>56.84426478172496</v>
+        <v>36.84043272481406</v>
       </c>
       <c r="FX21" t="n">
         <v>0</v>
       </c>
       <c r="FY21" t="n">
-        <v>63.360246059208</v>
+        <v>73.97849462365593</v>
       </c>
       <c r="FZ21" t="n">
-        <v>7.7</v>
+        <v>52.5</v>
       </c>
       <c r="GA21" t="n">
-        <v>49.26829268292683</v>
+        <v>29.26829268292683</v>
       </c>
       <c r="GB21" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="GC21" t="n">
-        <v>32.62889366272824</v>
+        <v>31.69879062736205</v>
       </c>
       <c r="GD21" t="n">
-        <v>22.73770591268999</v>
+        <v>18.06950642325896</v>
       </c>
       <c r="GE21" t="inlineStr">
         <is>
@@ -15413,10 +15413,10 @@
         </is>
       </c>
       <c r="GF21" t="n">
-        <v>35.72647533431985</v>
+        <v>25.71208986926811</v>
       </c>
       <c r="GG21" t="n">
-        <v>29.81277307379948</v>
+        <v>36.45725761849455</v>
       </c>
       <c r="GH21" t="inlineStr">
         <is>
@@ -15424,10 +15424,10 @@
         </is>
       </c>
       <c r="GI21" t="n">
-        <v>50.84773890670226</v>
+        <v>43.17027304648469</v>
       </c>
       <c r="GJ21" t="n">
-        <v>23.88205856231357</v>
+        <v>20.74436354017647</v>
       </c>
       <c r="GK21" t="inlineStr">
         <is>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="GR21" t="inlineStr">
         <is>
-          <t>['Real MLB split is favorable vs R-handed pitching']</t>
+          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.270 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS21" t="inlineStr">
         <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.114 season BAA', 'Model AVG is slightly below season AVG by -0.013', 'Model AVG is below preferred threshold at 0.245', 'Low matchup score (23)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is materially below season AVG by -0.035', 'Model AVG is below preferred threshold at 0.228', 'Low matchup score (18)', 'Low split reliability score (29)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT21" t="inlineStr">
         <is>
-          <t>Hyeseong Kim projects for 0.68 hits with a 49.2% 1+ hit probability.</t>
+          <t>Garrett Mitchell projects for 0.59 hits with a 44.7% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU21" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|808975</t>
+          <t>2026-10-11|849809|669003</t>
         </is>
       </c>
       <c r="GV21" t="b">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15533,26 +15533,26 @@
         <v>849809</v>
       </c>
       <c r="D22" t="n">
-        <v>669003</v>
+        <v>571771</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -15568,12 +15568,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P22" t="b">
@@ -15581,35 +15581,35 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/669003</t>
+          <t>https://www.mlb.com/player/571771</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Garrett+Mitchell</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Enrique+Hern%C3%A1ndez</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>669373</v>
+        <v>694819</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/669373</t>
+          <t>https://www.mlb.com/player/694819</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -15622,79 +15622,79 @@
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
-        <v>725</v>
+        <v>684</v>
       </c>
       <c r="AB22" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.2551724137931035</v>
+        <v>0.2192982456140351</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.5271966527196653</v>
+        <v>0.4401544401544402</v>
       </c>
       <c r="AE22" t="n">
-        <v>461</v>
+        <v>90</v>
       </c>
       <c r="AF22" t="n">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="n">
-        <v>531</v>
+        <v>96</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.262472885032538</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.5246913580246914</v>
+        <v>0.4012345679012346</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3125</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU22" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>31</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.2903225806451613</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
       <c r="AV22" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.26</v>
+        <v>0.2156862745098039</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="AZ22" t="n">
         <v>102</v>
@@ -15706,43 +15706,43 @@
         <v>0.2156862745098039</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="BD22" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BE22" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.2524752475247525</v>
+        <v>0.225</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.53</v>
+        <v>0.405</v>
       </c>
       <c r="BH22" t="n">
         <v>3</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ22" t="n">
         <v>8</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BM22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BN22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="BO22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
@@ -15750,88 +15750,88 @@
         </is>
       </c>
       <c r="BQ22" t="n">
-        <v>160</v>
+        <v>403</v>
       </c>
       <c r="BR22" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="BS22" t="n">
-        <v>0.2426287356321839</v>
+        <v>0.2314370743947593</v>
       </c>
       <c r="BT22" t="n">
-        <v>0.6211121176235388</v>
+        <v>0.6037651934348609</v>
       </c>
       <c r="BU22" t="n">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="BV22" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.2336448598130841</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="BX22" t="n">
         <v>100</v>
       </c>
       <c r="BY22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.2426287356321839</v>
+        <v>0.2314370743947593</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.2469715517241379</v>
+        <v>0.2152358548470322</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.2372402434077079</v>
+        <v>0.2152058268695141</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.2441057124160692</v>
+        <v>0.2165728577155254</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.2469715517241379</v>
+        <v>0.2152358548470322</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.2469715517241379</v>
+        <v>0.2152358548470322</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.2372402434077079</v>
+        <v>0.2152058268695141</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.2336448598130841</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.2375</v>
+        <v>0.2135231316725979</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.242603550295858</v>
+        <v>0.2486559139784946</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.2641632632161495</v>
+        <v>0.2274993744235204</v>
       </c>
       <c r="CK22" t="n">
-        <v>0.2555780689991869</v>
+        <v>0.2282869144177682</v>
       </c>
       <c r="CL22" t="n">
-        <v>0.2635896521070157</v>
+        <v>0.2304715132355454</v>
       </c>
       <c r="CM22" t="n">
-        <v>0.2641632632161495</v>
+        <v>0.2274993744235204</v>
       </c>
       <c r="CN22" t="n">
-        <v>0.2641632632161495</v>
+        <v>0.2274993744235204</v>
       </c>
       <c r="CO22" t="n">
-        <v>0.2555780689991869</v>
+        <v>0.2282869144177682</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="CQ22" t="n">
-        <v>0.2601769911504425</v>
+        <v>0.2233250620347395</v>
       </c>
       <c r="CR22" t="n">
-        <v>0.2624633431085044</v>
+        <v>0.2270573028866868</v>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -15839,124 +15839,124 @@
         </is>
       </c>
       <c r="CT22" t="n">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="CU22" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="CV22" t="n">
-        <v>0.2336448598130841</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="CW22" t="n">
-        <v>354</v>
+        <v>39</v>
       </c>
       <c r="CX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>281</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0.2135231316725979</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>403</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>90</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>0.2233250620347395</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>1488</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>370</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0.2486559139784946</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>2321</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>527</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>0.2270573028866868</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>0.3789473684210526</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>0.06616541353383458</v>
+      </c>
+      <c r="DP22" t="n">
+        <v>4.946564885496183</v>
+      </c>
+      <c r="DQ22" t="n">
+        <v>0.7213740458015268</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>665</v>
+      </c>
+      <c r="DS22" t="n">
         <v>96</v>
-      </c>
-      <c r="CY22" t="n">
-        <v>0.2711864406779661</v>
-      </c>
-      <c r="CZ22" t="n">
-        <v>160</v>
-      </c>
-      <c r="DA22" t="n">
-        <v>38</v>
-      </c>
-      <c r="DB22" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="DC22" t="n">
-        <v>565</v>
-      </c>
-      <c r="DD22" t="n">
-        <v>147</v>
-      </c>
-      <c r="DE22" t="n">
-        <v>0.2601769911504425</v>
-      </c>
-      <c r="DF22" t="n">
-        <v>169</v>
-      </c>
-      <c r="DG22" t="n">
-        <v>41</v>
-      </c>
-      <c r="DH22" t="n">
-        <v>0.242603550295858</v>
-      </c>
-      <c r="DI22" t="n">
-        <v>682</v>
-      </c>
-      <c r="DJ22" t="n">
-        <v>179</v>
-      </c>
-      <c r="DK22" t="n">
-        <v>0.2624633431085044</v>
-      </c>
-      <c r="DL22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="DM22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="DN22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DO22" t="n">
-        <v>0.04354838709677419</v>
-      </c>
-      <c r="DP22" t="n">
-        <v>7.147058823529412</v>
-      </c>
-      <c r="DQ22" t="n">
-        <v>0.7941176470588236</v>
-      </c>
-      <c r="DR22" t="n">
-        <v>620</v>
-      </c>
-      <c r="DS22" t="n">
-        <v>126</v>
       </c>
       <c r="DT22" t="n">
         <v>14</v>
       </c>
       <c r="DU22" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="DV22" t="n">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="DW22" t="n">
-        <v>158.6666666666667</v>
+        <v>174.6666666666667</v>
       </c>
       <c r="DX22" t="n">
-        <v>0.7941176470588236</v>
+        <v>0.5496183206106871</v>
       </c>
       <c r="DY22" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ22" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EA22" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EB22" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EC22" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="ED22" t="n">
-        <v>89</v>
+        <v>333</v>
       </c>
       <c r="EE22" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="EF22" t="n">
-        <v>669</v>
+        <v>455</v>
       </c>
       <c r="EG22" t="n">
-        <v>2748</v>
+        <v>394</v>
       </c>
       <c r="EH22" t="inlineStr">
         <is>
@@ -15964,150 +15964,150 @@
         </is>
       </c>
       <c r="EI22" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EJ22" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EK22" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EL22" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="EM22" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EN22" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EO22" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EP22" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="EQ22" t="n">
-        <v>0.9654033088235294</v>
+        <v>0.9623202290076336</v>
       </c>
       <c r="ER22" t="n">
-        <v>0.9654033088235294</v>
+        <v>0.9623202290076336</v>
       </c>
       <c r="ES22" t="n">
         <v>0.97</v>
       </c>
       <c r="ET22" t="inlineStr">
         <is>
-          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Garrett Mitchell', 'hitter_id': 669003, 'bats': 'L', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 1.8, 'whip': 0.8, 'k_rate': 0.37894736842105264, 'bb_rate': 0.06616541353383458, 'hits_per_9': 4.9465648854961835, 'hr_per_9': 0.7213740458015268, 'batters_faced': 665, 'baa_vs_lhb_season': 0.11411411411411411, 'baa_vs_rhb_season': 0.20938628158844766, 'baa_vs_lhb_career': 0.14285714285714285, 'baa_vs_rhb_career': 0.20812182741116753, 'pitcher': 'Jacob Misiorowski', 'pitcher_id': 694819, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/694819', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski', 'hitter': 'Enrique Hernández', 'hitter_id': 571771, 'bats': 'R', 'team': 'LAD', 'opp': 'MIL', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU22" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="EV22" t="n">
         <v>3.32</v>
       </c>
       <c r="EW22" t="n">
-        <v>3.001424228192964</v>
+        <v>3.117026105125171</v>
       </c>
       <c r="EX22" t="n">
-        <v>2.605756250841726</v>
+        <v>2.922211973554848</v>
       </c>
       <c r="EY22" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="EZ22" t="n">
         <v>0.995</v>
       </c>
       <c r="FA22" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="FB22" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="FC22" t="n">
-        <v>0.2491003037463022</v>
+        <v>0.2193068455452357</v>
       </c>
       <c r="FD22" t="n">
-        <v>0.240382766677409</v>
+        <v>0.24409062630889</v>
       </c>
       <c r="FE22" t="n">
-        <v>0.2427602767871071</v>
+        <v>0.24409062630889</v>
       </c>
       <c r="FF22" t="n">
-        <v>0.3043724340175953</v>
+        <v>0.2746936274509804</v>
       </c>
       <c r="FG22" t="n">
-        <v>0.2877907949362074</v>
+        <v>0.258077592879257</v>
       </c>
       <c r="FH22" t="n">
-        <v>0.2541625840727266</v>
+        <v>0.2337207142944558</v>
       </c>
       <c r="FI22" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ22" t="n">
-        <v>0.228746325665454</v>
+        <v>0.2103486428650102</v>
       </c>
       <c r="FK22" t="n">
-        <v>0.2276025940371267</v>
+        <v>0.2092968996506852</v>
       </c>
       <c r="FL22" t="n">
-        <v>0.262472885032538</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="FM22" t="n">
-        <v>0.262472885032538</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="FN22" t="n">
-        <v>0.2276025940371267</v>
+        <v>0.2092968996506852</v>
       </c>
       <c r="FO22" t="n">
-        <v>-0.03487029099541125</v>
+        <v>-0.01292532257153706</v>
       </c>
       <c r="FP22" t="n">
-        <v>0.03487029099541125</v>
+        <v>0.01292532257153706</v>
       </c>
       <c r="FQ22" t="n">
-        <v>0.5930768821200347</v>
+        <v>0.6116099061871396</v>
       </c>
       <c r="FR22" t="n">
-        <v>0.4473756937010537</v>
+        <v>0.4575231711012896</v>
       </c>
       <c r="FS22" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="FT22" t="n">
-        <v>0.3057634408602151</v>
+        <v>0.2743872549019608</v>
       </c>
       <c r="FU22" t="n">
-        <v>23.84614702000578</v>
+        <v>26.93498436452326</v>
       </c>
       <c r="FV22" t="n">
-        <v>16.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="FW22" t="n">
-        <v>36.84043272481406</v>
+        <v>30.25710258515253</v>
       </c>
       <c r="FX22" t="n">
         <v>0</v>
       </c>
       <c r="FY22" t="n">
-        <v>73.97849462365593</v>
+        <v>55.52191464821225</v>
       </c>
       <c r="FZ22" t="n">
-        <v>52.5</v>
+        <v>48.4</v>
       </c>
       <c r="GA22" t="n">
-        <v>29.26829268292683</v>
+        <v>88.53658536585365</v>
       </c>
       <c r="GB22" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="GC22" t="n">
-        <v>31.69879062736205</v>
+        <v>14.65041572184429</v>
       </c>
       <c r="GD22" t="n">
-        <v>18.06950642325896</v>
+        <v>12.10284103406102</v>
       </c>
       <c r="GE22" t="inlineStr">
         <is>
@@ -16115,10 +16115,10 @@
         </is>
       </c>
       <c r="GF22" t="n">
-        <v>25.71208986926811</v>
+        <v>19.48138207579904</v>
       </c>
       <c r="GG22" t="n">
-        <v>36.45725761849455</v>
+        <v>49.11444040705713</v>
       </c>
       <c r="GH22" t="inlineStr">
         <is>
@@ -16126,10 +16126,10 @@
         </is>
       </c>
       <c r="GI22" t="n">
-        <v>43.17027304648469</v>
+        <v>49.69087711686903</v>
       </c>
       <c r="GJ22" t="n">
-        <v>20.74436354017647</v>
+        <v>20.58964698959637</v>
       </c>
       <c r="GK22" t="inlineStr">
         <is>
@@ -16160,22 +16160,22 @@
       </c>
       <c r="GR22" t="inlineStr">
         <is>
-          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.270 season BAA vs this batter hand']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="GS22" t="inlineStr">
         <is>
-          <t>['Model AVG is materially below season AVG by -0.035', 'Model AVG is below preferred threshold at 0.228', 'Low matchup score (18)', 'Low split reliability score (29)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.209 season BAA', 'Model AVG is slightly below season AVG by -0.013', 'Model AVG is below preferred threshold at 0.209', 'Low matchup score (12)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT22" t="inlineStr">
         <is>
-          <t>Garrett Mitchell projects for 0.59 hits with a 44.7% 1+ hit probability.</t>
+          <t>Enrique Hernández projects for 0.61 hits with a 45.8% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU22" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|669003</t>
+          <t>2026-10-11|849809|571771</t>
         </is>
       </c>
       <c r="GV22" t="b">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16235,26 +16235,26 @@
         <v>849809</v>
       </c>
       <c r="D23" t="n">
-        <v>571771</v>
+        <v>806198</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Enrique Hernández</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -16283,35 +16283,35 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/571771</t>
+          <t>https://www.mlb.com/player/806198</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Enrique+Hern%C3%A1ndez</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Cooper+Pratt</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>694819</v>
+        <v>669373</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/694819</t>
+          <t>https://www.mlb.com/player/669373</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -16324,55 +16324,55 @@
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>684</v>
+        <v>228</v>
       </c>
       <c r="AB23" t="n">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.2192982456140351</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.4401544401544402</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="AE23" t="n">
-        <v>90</v>
+        <v>228</v>
       </c>
       <c r="AF23" t="n">
+        <v>64</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>266</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>20</v>
       </c>
-      <c r="AG23" t="n">
-        <v>96</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.4012345679012346</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>16</v>
-      </c>
       <c r="AK23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.3125</v>
+        <v>0.35</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AN23" t="n">
         <v>16</v>
       </c>
       <c r="AO23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.3125</v>
+        <v>0.375</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="AR23" t="n">
         <v>32</v>
@@ -16384,46 +16384,46 @@
         <v>0.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AV23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.39</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="BD23" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BE23" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="BF23" t="n">
-        <v>0.225</v>
+        <v>0.2772277227722773</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.405</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="BH23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI23" t="n">
         <v>2</v>
@@ -16432,19 +16432,19 @@
         <v>8</v>
       </c>
       <c r="BK23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL23" t="n">
         <v>18</v>
       </c>
       <c r="BM23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BN23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BO23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
@@ -16452,88 +16452,88 @@
         </is>
       </c>
       <c r="BQ23" t="n">
-        <v>403</v>
+        <v>58</v>
       </c>
       <c r="BR23" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="BS23" t="n">
-        <v>0.2314370743947593</v>
+        <v>0.2584319131161236</v>
       </c>
       <c r="BT23" t="n">
-        <v>0.6037651934348609</v>
+        <v>0.6443213600103912</v>
       </c>
       <c r="BU23" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="BV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.282051282051282</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="BX23" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="BY23" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.2314370743947593</v>
+        <v>0.2584319131161236</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.2152358548470322</v>
+        <v>0.2438239348370927</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.2152058268695141</v>
+        <v>0.2647455304928989</v>
       </c>
       <c r="CC23" t="n">
-        <v>0.2165728577155254</v>
+        <v>0.2612512845645467</v>
       </c>
       <c r="CD23" t="n">
-        <v>0.2152358548470322</v>
+        <v>0.2438239348370927</v>
       </c>
       <c r="CE23" t="n">
-        <v>0.2152358548470322</v>
+        <v>0.2438239348370927</v>
       </c>
       <c r="CF23" t="n">
-        <v>0.2152058268695141</v>
+        <v>0.2647455304928989</v>
       </c>
       <c r="CG23" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="CH23" t="n">
-        <v>0.2135231316725979</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="CI23" t="n">
-        <v>0.2486559139784946</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.2274993744235204</v>
+        <v>0.273687675070028</v>
       </c>
       <c r="CK23" t="n">
-        <v>0.2282869144177682</v>
+        <v>0.2966001867413632</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.2304715132355454</v>
+        <v>0.29509685682854</v>
       </c>
       <c r="CM23" t="n">
-        <v>0.2274993744235204</v>
+        <v>0.273687675070028</v>
       </c>
       <c r="CN23" t="n">
-        <v>0.2274993744235204</v>
+        <v>0.273687675070028</v>
       </c>
       <c r="CO23" t="n">
-        <v>0.2282869144177682</v>
+        <v>0.2966001867413632</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.2233250620347395</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="CR23" t="n">
-        <v>0.2270573028866868</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -16541,124 +16541,124 @@
         </is>
       </c>
       <c r="CT23" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="CU23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CV23" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="CW23" t="n">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="CX23" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="CY23" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="CZ23" t="n">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="DA23" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="DB23" t="n">
-        <v>0.2135231316725979</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="DC23" t="n">
-        <v>403</v>
+        <v>170</v>
       </c>
       <c r="DD23" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.2233250620347395</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="DF23" t="n">
-        <v>1488</v>
+        <v>58</v>
       </c>
       <c r="DG23" t="n">
-        <v>370</v>
+        <v>12</v>
       </c>
       <c r="DH23" t="n">
-        <v>0.2486559139784946</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="DI23" t="n">
-        <v>2321</v>
+        <v>170</v>
       </c>
       <c r="DJ23" t="n">
-        <v>527</v>
+        <v>52</v>
       </c>
       <c r="DK23" t="n">
-        <v>0.2270573028866868</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="DL23" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.3789473684210526</v>
+        <v>0.3</v>
       </c>
       <c r="DO23" t="n">
-        <v>0.06616541353383458</v>
+        <v>0.04354838709677419</v>
       </c>
       <c r="DP23" t="n">
-        <v>4.946564885496183</v>
+        <v>7.147058823529412</v>
       </c>
       <c r="DQ23" t="n">
-        <v>0.7213740458015268</v>
+        <v>0.7941176470588236</v>
       </c>
       <c r="DR23" t="n">
-        <v>665</v>
+        <v>620</v>
       </c>
       <c r="DS23" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="DT23" t="n">
         <v>14</v>
       </c>
       <c r="DU23" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="DV23" t="n">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="DW23" t="n">
-        <v>174.6666666666667</v>
+        <v>158.6666666666667</v>
       </c>
       <c r="DX23" t="n">
-        <v>0.5496183206106871</v>
+        <v>0.7941176470588236</v>
       </c>
       <c r="DY23" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ23" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EA23" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EB23" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EC23" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="ED23" t="n">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="EE23" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="EF23" t="n">
-        <v>455</v>
+        <v>669</v>
       </c>
       <c r="EG23" t="n">
-        <v>394</v>
+        <v>2748</v>
       </c>
       <c r="EH23" t="inlineStr">
         <is>
@@ -16666,54 +16666,54 @@
         </is>
       </c>
       <c r="EI23" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EJ23" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EK23" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EL23" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="EM23" t="n">
-        <v>0.1141141141141141</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="EN23" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="EO23" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2257100149476831</v>
       </c>
       <c r="EP23" t="n">
-        <v>0.2081218274111675</v>
+        <v>0.2143377001455604</v>
       </c>
       <c r="EQ23" t="n">
-        <v>0.9623202290076336</v>
+        <v>0.9654033088235294</v>
       </c>
       <c r="ER23" t="n">
-        <v>0.9623202290076336</v>
+        <v>0.9654033088235294</v>
       </c>
       <c r="ES23" t="n">
         <v>0.97</v>
       </c>
       <c r="ET23" t="inlineStr">
         <is>
-          <t>{'era': 1.8, 'whip': 0.8, 'k_rate': 0.37894736842105264, 'bb_rate': 0.06616541353383458, 'hits_per_9': 4.9465648854961835, 'hr_per_9': 0.7213740458015268, 'batters_faced': 665, 'baa_vs_lhb_season': 0.11411411411411411, 'baa_vs_rhb_season': 0.20938628158844766, 'baa_vs_lhb_career': 0.14285714285714285, 'baa_vs_rhb_career': 0.20812182741116753, 'pitcher': 'Jacob Misiorowski', 'pitcher_id': 694819, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/694819', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski', 'hitter': 'Enrique Hernández', 'hitter_id': 571771, 'bats': 'R', 'team': 'LAD', 'opp': 'MIL', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Cooper Pratt', 'hitter_id': 806198, 'bats': 'R', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU23" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="EV23" t="n">
         <v>3.32</v>
       </c>
       <c r="EW23" t="n">
-        <v>3.117026105125171</v>
+        <v>3.001424228192964</v>
       </c>
       <c r="EX23" t="n">
-        <v>2.922211973554848</v>
+        <v>2.572649338451112</v>
       </c>
       <c r="EY23" t="n">
         <v>0.44</v>
@@ -16722,94 +16722,94 @@
         <v>0.995</v>
       </c>
       <c r="FA23" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="FB23" t="n">
-        <v>0.2093862815884477</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="FC23" t="n">
-        <v>0.2193068455452357</v>
+        <v>0.2825614035087719</v>
       </c>
       <c r="FD23" t="n">
-        <v>0.24409062630889</v>
+        <v>0.2455480727681272</v>
       </c>
       <c r="FE23" t="n">
-        <v>0.24409062630889</v>
+        <v>0.2728033435862383</v>
       </c>
       <c r="FF23" t="n">
-        <v>0.2746936274509804</v>
+        <v>0.2975</v>
       </c>
       <c r="FG23" t="n">
-        <v>0.258077592879257</v>
+        <v>0.2930184210526315</v>
       </c>
       <c r="FH23" t="n">
-        <v>0.2337207142944558</v>
+        <v>0.2815162486899065</v>
       </c>
       <c r="FI23" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ23" t="n">
-        <v>0.2103486428650102</v>
+        <v>0.2533646238209159</v>
       </c>
       <c r="FK23" t="n">
-        <v>0.2092968996506852</v>
+        <v>0.2520978007018113</v>
       </c>
       <c r="FL23" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="FM23" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="FN23" t="n">
-        <v>0.2092968996506852</v>
+        <v>0.2520978007018113</v>
       </c>
       <c r="FO23" t="n">
-        <v>-0.01292532257153706</v>
+        <v>-0.02860395368415358</v>
       </c>
       <c r="FP23" t="n">
-        <v>0.01292532257153706</v>
+        <v>0.02860395368415358</v>
       </c>
       <c r="FQ23" t="n">
-        <v>0.6116099061871396</v>
+        <v>0.6485592402004952</v>
       </c>
       <c r="FR23" t="n">
-        <v>0.4575231711012896</v>
+        <v>0.4772015385816286</v>
       </c>
       <c r="FS23" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="FT23" t="n">
-        <v>0.2743872549019608</v>
+        <v>0.3025</v>
       </c>
       <c r="FU23" t="n">
-        <v>26.93498436452326</v>
+        <v>33.09320670008252</v>
       </c>
       <c r="FV23" t="n">
-        <v>0</v>
+        <v>33.33333333333332</v>
       </c>
       <c r="FW23" t="n">
-        <v>30.25710258515253</v>
+        <v>46.13641948007273</v>
       </c>
       <c r="FX23" t="n">
         <v>0</v>
       </c>
       <c r="FY23" t="n">
-        <v>55.52191464821225</v>
+        <v>72.05882352941177</v>
       </c>
       <c r="FZ23" t="n">
-        <v>48.4</v>
+        <v>2.8</v>
       </c>
       <c r="GA23" t="n">
-        <v>88.53658536585365</v>
+        <v>4.390243902439025</v>
       </c>
       <c r="GB23" t="n">
         <v>19.8</v>
       </c>
       <c r="GC23" t="n">
-        <v>14.65041572184429</v>
+        <v>40.92112520683948</v>
       </c>
       <c r="GD23" t="n">
-        <v>12.10284103406102</v>
+        <v>21.78790112536243</v>
       </c>
       <c r="GE23" t="inlineStr">
         <is>
@@ -16817,10 +16817,10 @@
         </is>
       </c>
       <c r="GF23" t="n">
-        <v>19.48138207579904</v>
+        <v>34.63737770612776</v>
       </c>
       <c r="GG23" t="n">
-        <v>49.11444040705713</v>
+        <v>17.56753463468446</v>
       </c>
       <c r="GH23" t="inlineStr">
         <is>
@@ -16828,10 +16828,10 @@
         </is>
       </c>
       <c r="GI23" t="n">
-        <v>49.69087711686903</v>
+        <v>45.2080240642982</v>
       </c>
       <c r="GJ23" t="n">
-        <v>20.58964698959637</v>
+        <v>19.91473893497295</v>
       </c>
       <c r="GK23" t="inlineStr">
         <is>
@@ -16867,17 +16867,17 @@
       </c>
       <c r="GS23" t="inlineStr">
         <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.209 season BAA', 'Model AVG is slightly below season AVG by -0.013', 'Model AVG is below preferred threshold at 0.209', 'Low matchup score (12)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is materially below season AVG by -0.029', 'Model AVG is below preferred threshold at 0.252', 'Low matchup score (22)', 'Low split reliability score (4)', 'Real handedness split sample is smaller than preferred', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT23" t="inlineStr">
         <is>
-          <t>Enrique Hernández projects for 0.61 hits with a 45.8% 1+ hit probability.</t>
+          <t>Cooper Pratt projects for 0.65 hits with a 47.7% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU23" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|571771</t>
+          <t>2026-10-11|849809|806198</t>
         </is>
       </c>
       <c r="GV23" t="b">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16937,11 +16937,11 @@
         <v>849809</v>
       </c>
       <c r="D24" t="n">
-        <v>806198</v>
+        <v>666152</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P24" t="b">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/806198</t>
+          <t>https://www.mlb.com/player/666152</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Cooper+Pratt</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=David+Hamilton</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -17026,216 +17026,216 @@
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>228</v>
+        <v>810</v>
       </c>
       <c r="AB24" t="n">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2358024691358025</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.4290322580645161</v>
       </c>
       <c r="AE24" t="n">
-        <v>228</v>
+        <v>339</v>
       </c>
       <c r="AF24" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="AG24" t="n">
-        <v>266</v>
+        <v>387</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2448377581120944</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.35</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="AM24" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="AN24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS24" t="n">
         <v>6</v>
       </c>
-      <c r="AP24" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8</v>
-      </c>
       <c r="AT24" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AV24" t="n">
         <v>50</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.29</v>
+        <v>0.2277227722772277</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.47</v>
       </c>
       <c r="BD24" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BE24" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="BF24" t="n">
-        <v>0.2772277227722773</v>
+        <v>0.2338308457711443</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.39</v>
       </c>
       <c r="BH24" t="n">
         <v>4</v>
       </c>
       <c r="BI24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BM24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BO24" t="n">
         <v>9</v>
       </c>
-      <c r="BN24" t="n">
-        <v>38</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>15</v>
-      </c>
       <c r="BP24" t="inlineStr">
         <is>
           <t>real_mlb_statSplits</t>
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="BR24" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>0.2584319131161236</v>
+        <v>0.2279611552028218</v>
       </c>
       <c r="BT24" t="n">
-        <v>0.6443213600103912</v>
+        <v>0.5982175961282646</v>
       </c>
       <c r="BU24" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="BV24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BW24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="BX24" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="BY24" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0.2584319131161236</v>
+        <v>0.2279611552028218</v>
       </c>
       <c r="CA24" t="n">
-        <v>0.2438239348370927</v>
+        <v>0.2309708664021164</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.2647455304928989</v>
+        <v>0.227913478617703</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.2612512845645467</v>
+        <v>0.2288416087880702</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.2438239348370927</v>
+        <v>0.2309708664021164</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.2438239348370927</v>
+        <v>0.2309708664021164</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.2647455304928989</v>
+        <v>0.227913478617703</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2101449275362319</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2127659574468085</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.273687675070028</v>
+        <v>0.2429126602564103</v>
       </c>
       <c r="CK24" t="n">
-        <v>0.2966001867413632</v>
+        <v>0.2406513920622832</v>
       </c>
       <c r="CL24" t="n">
-        <v>0.29509685682854</v>
+        <v>0.2423756418229366</v>
       </c>
       <c r="CM24" t="n">
-        <v>0.273687675070028</v>
+        <v>0.2429126602564103</v>
       </c>
       <c r="CN24" t="n">
-        <v>0.273687675070028</v>
+        <v>0.2429126602564103</v>
       </c>
       <c r="CO24" t="n">
-        <v>0.2966001867413632</v>
+        <v>0.2406513920622832</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.25</v>
       </c>
       <c r="CQ24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="CR24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.235042735042735</v>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -17243,58 +17243,58 @@
         </is>
       </c>
       <c r="CT24" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="CU24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CV24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="CW24" t="n">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="CX24" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="CY24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.25</v>
       </c>
       <c r="CZ24" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="DA24" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="DB24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2101449275362319</v>
       </c>
       <c r="DC24" t="n">
-        <v>170</v>
+        <v>672</v>
       </c>
       <c r="DD24" t="n">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="DF24" t="n">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="DG24" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="DH24" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2127659574468085</v>
       </c>
       <c r="DI24" t="n">
-        <v>170</v>
+        <v>702</v>
       </c>
       <c r="DJ24" t="n">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="DK24" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.235042735042735</v>
       </c>
       <c r="DL24" t="n">
         <v>2.72</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="ET24" t="inlineStr">
         <is>
-          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Cooper Pratt', 'hitter_id': 806198, 'bats': 'R', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'David Hamilton', 'hitter_id': 666152, 'bats': 'L', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU24" t="n">
@@ -17415,103 +17415,103 @@
         <v>3.001424228192964</v>
       </c>
       <c r="EX24" t="n">
-        <v>2.572649338451112</v>
+        <v>2.629154556479108</v>
       </c>
       <c r="EY24" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="EZ24" t="n">
         <v>0.995</v>
       </c>
       <c r="FA24" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="FB24" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="FC24" t="n">
-        <v>0.2825614035087719</v>
+        <v>0.2364453520081605</v>
       </c>
       <c r="FD24" t="n">
-        <v>0.2455480727681272</v>
+        <v>0.2273088945711305</v>
       </c>
       <c r="FE24" t="n">
-        <v>0.2728033435862383</v>
+        <v>0.2307143014340235</v>
       </c>
       <c r="FF24" t="n">
-        <v>0.2975</v>
+        <v>0.224061919504644</v>
       </c>
       <c r="FG24" t="n">
-        <v>0.2930184210526315</v>
+        <v>0.2277769492556989</v>
       </c>
       <c r="FH24" t="n">
-        <v>0.2815162486899065</v>
+        <v>0.2331657243404763</v>
       </c>
       <c r="FI24" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ24" t="n">
-        <v>0.2533646238209159</v>
+        <v>0.2098491519064287</v>
       </c>
       <c r="FK24" t="n">
-        <v>0.2520978007018113</v>
+        <v>0.2087999061468966</v>
       </c>
       <c r="FL24" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2448377581120944</v>
       </c>
       <c r="FM24" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2448377581120944</v>
       </c>
       <c r="FN24" t="n">
-        <v>0.2520978007018113</v>
+        <v>0.2087999061468966</v>
       </c>
       <c r="FO24" t="n">
-        <v>-0.02860395368415358</v>
+        <v>-0.03603785196519785</v>
       </c>
       <c r="FP24" t="n">
-        <v>0.02860395368415358</v>
+        <v>0.03603785196519785</v>
       </c>
       <c r="FQ24" t="n">
-        <v>0.6485592402004952</v>
+        <v>0.5489672246385233</v>
       </c>
       <c r="FR24" t="n">
-        <v>0.4772015385816286</v>
+        <v>0.4224540222700593</v>
       </c>
       <c r="FS24" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="FT24" t="n">
-        <v>0.3025</v>
+        <v>0.2256470588235294</v>
       </c>
       <c r="FU24" t="n">
-        <v>33.09320670008252</v>
+        <v>16.49453743975388</v>
       </c>
       <c r="FV24" t="n">
-        <v>33.33333333333332</v>
+        <v>24.99999999999999</v>
       </c>
       <c r="FW24" t="n">
-        <v>46.13641948007273</v>
+        <v>28.21244423695403</v>
       </c>
       <c r="FX24" t="n">
         <v>0</v>
       </c>
       <c r="FY24" t="n">
-        <v>72.05882352941177</v>
+        <v>26.85121107266437</v>
       </c>
       <c r="FZ24" t="n">
-        <v>2.8</v>
+        <v>61</v>
       </c>
       <c r="GA24" t="n">
-        <v>4.390243902439025</v>
+        <v>23.90243902439024</v>
       </c>
       <c r="GB24" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="GC24" t="n">
-        <v>40.92112520683948</v>
+        <v>21.7365835222978</v>
       </c>
       <c r="GD24" t="n">
-        <v>21.78790112536243</v>
+        <v>14.61831102811495</v>
       </c>
       <c r="GE24" t="inlineStr">
         <is>
@@ -17519,10 +17519,10 @@
         </is>
       </c>
       <c r="GF24" t="n">
-        <v>34.63737770612776</v>
+        <v>19.83532029223874</v>
       </c>
       <c r="GG24" t="n">
-        <v>17.56753463468446</v>
+        <v>35.89414606493004</v>
       </c>
       <c r="GH24" t="inlineStr">
         <is>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="GI24" t="n">
-        <v>45.2080240642982</v>
+        <v>41.40828473285719</v>
       </c>
       <c r="GJ24" t="n">
-        <v>19.91473893497295</v>
+        <v>17.98989994000507</v>
       </c>
       <c r="GK24" t="inlineStr">
         <is>
@@ -17564,22 +17564,22 @@
       </c>
       <c r="GR24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.270 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS24" t="inlineStr">
         <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is materially below season AVG by -0.029', 'Model AVG is below preferred threshold at 0.252', 'Low matchup score (22)', 'Low split reliability score (4)', 'Real handedness split sample is smaller than preferred', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is materially below season AVG by -0.036', 'Model AVG is below preferred threshold at 0.209', 'Low matchup score (15)', 'Low split reliability score (24)', 'Recent 30 AB form is below target at 0.200', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT24" t="inlineStr">
         <is>
-          <t>Cooper Pratt projects for 0.65 hits with a 47.7% 1+ hit probability.</t>
+          <t>David Hamilton projects for 0.55 hits with a 42.2% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU24" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|806198</t>
+          <t>2026-10-11|849809|666152</t>
         </is>
       </c>
       <c r="GV24" t="b">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17639,11 +17639,11 @@
         <v>849809</v>
       </c>
       <c r="D25" t="n">
-        <v>666152</v>
+        <v>800325</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -17674,12 +17674,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P25" t="b">
@@ -17687,12 +17687,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/666152</t>
+          <t>https://www.mlb.com/player/800325</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=David+Hamilton</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Luis+Lara</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -17728,67 +17728,67 @@
       </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>810</v>
+        <v>191</v>
       </c>
       <c r="AB25" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.2460732984293194</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.6065573770491803</v>
+      </c>
+      <c r="AE25" t="n">
         <v>191</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0.2358024691358025</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.4290322580645161</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>339</v>
-      </c>
       <c r="AF25" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AG25" t="n">
-        <v>387</v>
+        <v>212</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.2448377581120944</v>
+        <v>0.2460732984293194</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.4197530864197531</v>
+        <v>0.6065573770491803</v>
       </c>
       <c r="AJ25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AN25" t="n">
         <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="AQ25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AU25" t="n">
         <v>0.5333333333333333</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.5</v>
       </c>
       <c r="AV25" t="n">
         <v>50</v>
@@ -17800,52 +17800,52 @@
         <v>0.24</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BA25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.2277227722772277</v>
+        <v>0.2450980392156863</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.47</v>
+        <v>0.6065573770491803</v>
       </c>
       <c r="BD25" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="BE25" t="n">
         <v>47</v>
       </c>
       <c r="BF25" t="n">
-        <v>0.2338308457711443</v>
+        <v>0.2460732984293194</v>
       </c>
       <c r="BG25" t="n">
-        <v>0.39</v>
+        <v>0.6065573770491803</v>
       </c>
       <c r="BH25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BI25" t="n">
         <v>0</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BM25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN25" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="BO25" t="n">
         <v>9</v>
@@ -17856,88 +17856,88 @@
         </is>
       </c>
       <c r="BQ25" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="BR25" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BS25" t="n">
-        <v>0.2279611552028218</v>
+        <v>0.242260034904014</v>
       </c>
       <c r="BT25" t="n">
-        <v>0.5982175961282646</v>
+        <v>0.6205529204195548</v>
       </c>
       <c r="BU25" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="BV25" t="n">
         <v>16</v>
       </c>
       <c r="BW25" t="n">
-        <v>0.2253521126760563</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="BX25" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BY25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0.2279611552028218</v>
+        <v>0.242260034904014</v>
       </c>
       <c r="CA25" t="n">
-        <v>0.2309708664021164</v>
+        <v>0.2416950261780105</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.227913478617703</v>
+        <v>0.2428276357663484</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.2288416087880702</v>
+        <v>0.2428320244328098</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.2309708664021164</v>
+        <v>0.2416950261780105</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.2309708664021164</v>
+        <v>0.2416950261780105</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.227913478617703</v>
+        <v>0.2428276357663484</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.2253521126760563</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.2101449275362319</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.2429126602564103</v>
+        <v>0.2473646405312221</v>
       </c>
       <c r="CK25" t="n">
-        <v>0.2406513920622832</v>
+        <v>0.2488752244097741</v>
       </c>
       <c r="CL25" t="n">
-        <v>0.2423756418229366</v>
+        <v>0.2492575873664496</v>
       </c>
       <c r="CM25" t="n">
-        <v>0.2429126602564103</v>
+        <v>0.2473646405312221</v>
       </c>
       <c r="CN25" t="n">
-        <v>0.2429126602564103</v>
+        <v>0.2473646405312221</v>
       </c>
       <c r="CO25" t="n">
-        <v>0.2406513920622832</v>
+        <v>0.2488752244097741</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.25</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="CQ25" t="n">
-        <v>0.2410714285714286</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="CR25" t="n">
-        <v>0.235042735042735</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -17945,58 +17945,58 @@
         </is>
       </c>
       <c r="CT25" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="CU25" t="n">
         <v>16</v>
       </c>
       <c r="CV25" t="n">
-        <v>0.2253521126760563</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="CW25" t="n">
-        <v>268</v>
+        <v>123</v>
       </c>
       <c r="CX25" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="CY25" t="n">
-        <v>0.25</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="CZ25" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="DA25" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="DB25" t="n">
-        <v>0.2101449275362319</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="DC25" t="n">
-        <v>672</v>
+        <v>123</v>
       </c>
       <c r="DD25" t="n">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.2410714285714286</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="DF25" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="DG25" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="DH25" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="DI25" t="n">
-        <v>702</v>
+        <v>123</v>
       </c>
       <c r="DJ25" t="n">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="DK25" t="n">
-        <v>0.235042735042735</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="DL25" t="n">
         <v>2.72</v>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="ET25" t="inlineStr">
         <is>
-          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'David Hamilton', 'hitter_id': 666152, 'bats': 'L', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Luis Lara', 'hitter_id': 800325, 'bats': 'S', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU25" t="n">
@@ -18117,103 +18117,103 @@
         <v>3.001424228192964</v>
       </c>
       <c r="EX25" t="n">
-        <v>2.629154556479108</v>
+        <v>2.704113337664416</v>
       </c>
       <c r="EY25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="EZ25" t="n">
         <v>0.995</v>
       </c>
       <c r="FA25" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="FB25" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="FC25" t="n">
-        <v>0.2364453520081605</v>
+        <v>0.2458782465865928</v>
       </c>
       <c r="FD25" t="n">
-        <v>0.2273088945711305</v>
+        <v>0.2405185555897752</v>
       </c>
       <c r="FE25" t="n">
-        <v>0.2307143014340235</v>
+        <v>0.2442216148239401</v>
       </c>
       <c r="FF25" t="n">
-        <v>0.224061919504644</v>
+        <v>0.2914560733384263</v>
       </c>
       <c r="FG25" t="n">
-        <v>0.2277769492556989</v>
+        <v>0.2777827253128762</v>
       </c>
       <c r="FH25" t="n">
-        <v>0.2331657243404763</v>
+        <v>0.251124063228528</v>
       </c>
       <c r="FI25" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ25" t="n">
-        <v>0.2098491519064287</v>
+        <v>0.2260116569056752</v>
       </c>
       <c r="FK25" t="n">
-        <v>0.2087999061468966</v>
+        <v>0.2248815986211468</v>
       </c>
       <c r="FL25" t="n">
-        <v>0.2448377581120944</v>
+        <v>0.2460732984293194</v>
       </c>
       <c r="FM25" t="n">
-        <v>0.2448377581120944</v>
+        <v>0.2460732984293194</v>
       </c>
       <c r="FN25" t="n">
-        <v>0.2087999061468966</v>
+        <v>0.2248815986211468</v>
       </c>
       <c r="FO25" t="n">
-        <v>-0.03603785196519785</v>
+        <v>-0.02119169980817259</v>
       </c>
       <c r="FP25" t="n">
-        <v>0.03603785196519785</v>
+        <v>0.02119169980817259</v>
       </c>
       <c r="FQ25" t="n">
-        <v>0.5489672246385233</v>
+        <v>0.6081053302267386</v>
       </c>
       <c r="FR25" t="n">
-        <v>0.4224540222700593</v>
+        <v>0.455618684588081</v>
       </c>
       <c r="FS25" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="FT25" t="n">
-        <v>0.2256470588235294</v>
+        <v>0.2859679144385027</v>
       </c>
       <c r="FU25" t="n">
-        <v>16.49453743975388</v>
+        <v>26.3508883711231</v>
       </c>
       <c r="FV25" t="n">
-        <v>24.99999999999999</v>
+        <v>33.33333333333332</v>
       </c>
       <c r="FW25" t="n">
-        <v>28.21244423695403</v>
+        <v>36.62354994353765</v>
       </c>
       <c r="FX25" t="n">
         <v>0</v>
       </c>
       <c r="FY25" t="n">
-        <v>26.85121107266437</v>
+        <v>62.33406731676629</v>
       </c>
       <c r="FZ25" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="GA25" t="n">
-        <v>23.90243902439024</v>
+        <v>6.829268292682927</v>
       </c>
       <c r="GB25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="GC25" t="n">
-        <v>21.7365835222978</v>
+        <v>33.65506858481096</v>
       </c>
       <c r="GD25" t="n">
-        <v>14.61831102811495</v>
+        <v>17.9827533107484</v>
       </c>
       <c r="GE25" t="inlineStr">
         <is>
@@ -18221,10 +18221,10 @@
         </is>
       </c>
       <c r="GF25" t="n">
-        <v>19.83532029223874</v>
+        <v>29.64874171702522</v>
       </c>
       <c r="GG25" t="n">
-        <v>35.89414606493004</v>
+        <v>16.59216272674603</v>
       </c>
       <c r="GH25" t="inlineStr">
         <is>
@@ -18232,10 +18232,10 @@
         </is>
       </c>
       <c r="GI25" t="n">
-        <v>41.40828473285719</v>
+        <v>46.37194366792241</v>
       </c>
       <c r="GJ25" t="n">
-        <v>17.98989994000507</v>
+        <v>17.29958683414234</v>
       </c>
       <c r="GK25" t="inlineStr">
         <is>
@@ -18266,22 +18266,22 @@
       </c>
       <c r="GR25" t="inlineStr">
         <is>
-          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.270 season BAA vs this batter hand']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="GS25" t="inlineStr">
         <is>
-          <t>['Model AVG is materially below season AVG by -0.036', 'Model AVG is below preferred threshold at 0.209', 'Low matchup score (15)', 'Low split reliability score (24)', 'Recent 30 AB form is below target at 0.200', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is slightly below season AVG by -0.021', 'Model AVG is below preferred threshold at 0.225', 'Low matchup score (18)', 'Low split reliability score (7)', 'Real handedness split sample is smaller than preferred', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT25" t="inlineStr">
         <is>
-          <t>David Hamilton projects for 0.55 hits with a 42.2% 1+ hit probability.</t>
+          <t>Luis Lara projects for 0.61 hits with a 45.6% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU25" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|666152</t>
+          <t>2026-10-11|849809|800325</t>
         </is>
       </c>
       <c r="GV25" t="b">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18341,11 +18341,11 @@
         <v>849809</v>
       </c>
       <c r="D26" t="n">
-        <v>800325</v>
+        <v>596142</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -18376,12 +18376,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P26" t="b">
@@ -18389,12 +18389,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/800325</t>
+          <t>https://www.mlb.com/player/596142</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Luis+Lara</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Gary+S%C3%A1nchez</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -18430,127 +18430,127 @@
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
-        <v>191</v>
+        <v>561</v>
       </c>
       <c r="AB26" t="n">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2174688057040998</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AE26" t="n">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="AF26" t="n">
         <v>47</v>
       </c>
       <c r="AG26" t="n">
-        <v>212</v>
+        <v>275</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.4691358024691358</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO26" t="n">
         <v>5</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3125</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AR26" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AV26" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.24</v>
+        <v>0.2156862745098039</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="AZ26" t="n">
         <v>102</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.2450980392156863</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.44</v>
       </c>
       <c r="BD26" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="BE26" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.205</v>
       </c>
       <c r="BG26" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.465</v>
       </c>
       <c r="BH26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK26" t="n">
         <v>2</v>
       </c>
       <c r="BL26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN26" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="BO26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
@@ -18558,147 +18558,147 @@
         </is>
       </c>
       <c r="BQ26" t="n">
+        <v>243</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>54</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.2263298219616434</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0.5955872595860625</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>101</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0.2376237623762376</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.2263298219616434</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.2236689350986835</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>0.22224032815755</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>0.2231303486673969</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0.2236689350986835</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>0.2236689350986835</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0.22224032815755</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0.2376237623762376</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>0.2168674698795181</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>0.2065535126320483</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0.2039838775264724</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0.203732869871877</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>0.2065535126320483</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0.2065535126320483</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>0.2039838775264724</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>0.1854838709677419</v>
+      </c>
+      <c r="CQ26" t="n">
+        <v>0.2138364779874214</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>0.2259937472085753</v>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>mlb_statSplits</t>
+        </is>
+      </c>
+      <c r="CT26" t="n">
+        <v>101</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>0.2376237623762376</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>124</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>23</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>0.1854838709677419</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>243</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>318</v>
+      </c>
+      <c r="DD26" t="n">
         <v>68</v>
       </c>
-      <c r="BR26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>0.242260034904014</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>0.6205529204195548</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>68</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>68</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>0.242260034904014</v>
-      </c>
-      <c r="CA26" t="n">
-        <v>0.2416950261780105</v>
-      </c>
-      <c r="CB26" t="n">
-        <v>0.2428276357663484</v>
-      </c>
-      <c r="CC26" t="n">
-        <v>0.2428320244328098</v>
-      </c>
-      <c r="CD26" t="n">
-        <v>0.2416950261780105</v>
-      </c>
-      <c r="CE26" t="n">
-        <v>0.2416950261780105</v>
-      </c>
-      <c r="CF26" t="n">
-        <v>0.2428276357663484</v>
-      </c>
-      <c r="CG26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CH26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CI26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CJ26" t="n">
-        <v>0.2473646405312221</v>
-      </c>
-      <c r="CK26" t="n">
-        <v>0.2488752244097741</v>
-      </c>
-      <c r="CL26" t="n">
-        <v>0.2492575873664496</v>
-      </c>
-      <c r="CM26" t="n">
-        <v>0.2473646405312221</v>
-      </c>
-      <c r="CN26" t="n">
-        <v>0.2473646405312221</v>
-      </c>
-      <c r="CO26" t="n">
-        <v>0.2488752244097741</v>
-      </c>
-      <c r="CP26" t="n">
-        <v>0.2520325203252032</v>
-      </c>
-      <c r="CQ26" t="n">
-        <v>0.2520325203252032</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>0.2520325203252032</v>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>mlb_statSplits</t>
-        </is>
-      </c>
-      <c r="CT26" t="n">
-        <v>68</v>
-      </c>
-      <c r="CU26" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CW26" t="n">
-        <v>123</v>
-      </c>
-      <c r="CX26" t="n">
-        <v>31</v>
-      </c>
-      <c r="CY26" t="n">
-        <v>0.2520325203252032</v>
-      </c>
-      <c r="CZ26" t="n">
-        <v>68</v>
-      </c>
-      <c r="DA26" t="n">
-        <v>16</v>
-      </c>
-      <c r="DB26" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="DC26" t="n">
-        <v>123</v>
-      </c>
-      <c r="DD26" t="n">
-        <v>31</v>
-      </c>
       <c r="DE26" t="n">
-        <v>0.2520325203252032</v>
+        <v>0.2138364779874214</v>
       </c>
       <c r="DF26" t="n">
-        <v>68</v>
+        <v>913</v>
       </c>
       <c r="DG26" t="n">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="DH26" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2168674698795181</v>
       </c>
       <c r="DI26" t="n">
-        <v>123</v>
+        <v>2239</v>
       </c>
       <c r="DJ26" t="n">
-        <v>31</v>
+        <v>506</v>
       </c>
       <c r="DK26" t="n">
-        <v>0.2520325203252032</v>
+        <v>0.2259937472085753</v>
       </c>
       <c r="DL26" t="n">
         <v>2.72</v>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="ET26" t="inlineStr">
         <is>
-          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Luis Lara', 'hitter_id': 800325, 'bats': 'S', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Gary Sánchez', 'hitter_id': 596142, 'bats': 'R', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU26" t="n">
@@ -18819,10 +18819,10 @@
         <v>3.001424228192964</v>
       </c>
       <c r="EX26" t="n">
-        <v>2.704113337664416</v>
+        <v>2.45571073215788</v>
       </c>
       <c r="EY26" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="EZ26" t="n">
         <v>0.995</v>
@@ -18834,88 +18834,88 @@
         <v>0.1893939393939394</v>
       </c>
       <c r="FC26" t="n">
-        <v>0.2458782465865928</v>
+        <v>0.2130065359477124</v>
       </c>
       <c r="FD26" t="n">
-        <v>0.2405185555897752</v>
+        <v>0.2291533070652919</v>
       </c>
       <c r="FE26" t="n">
-        <v>0.2442216148239401</v>
+        <v>0.2291533070652919</v>
       </c>
       <c r="FF26" t="n">
-        <v>0.2914560733384263</v>
+        <v>0.2597923116615067</v>
       </c>
       <c r="FG26" t="n">
-        <v>0.2777827253128762</v>
+        <v>0.2457565789473684</v>
       </c>
       <c r="FH26" t="n">
-        <v>0.251124063228528</v>
+        <v>0.2237455750229243</v>
       </c>
       <c r="FI26" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ26" t="n">
-        <v>0.2260116569056752</v>
+        <v>0.2013710175206319</v>
       </c>
       <c r="FK26" t="n">
-        <v>0.2248815986211468</v>
+        <v>0.2003641624330288</v>
       </c>
       <c r="FL26" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="FM26" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="FN26" t="n">
-        <v>0.2248815986211468</v>
+        <v>0.2003641624330288</v>
       </c>
       <c r="FO26" t="n">
-        <v>-0.02119169980817259</v>
+        <v>-0.008524726455860138</v>
       </c>
       <c r="FP26" t="n">
-        <v>0.02119169980817259</v>
+        <v>0.008524726455860138</v>
       </c>
       <c r="FQ26" t="n">
-        <v>0.6081053302267386</v>
+        <v>0.4920364240266135</v>
       </c>
       <c r="FR26" t="n">
-        <v>0.455618684588081</v>
+        <v>0.3886199034980642</v>
       </c>
       <c r="FS26" t="n">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="FT26" t="n">
-        <v>0.2859679144385027</v>
+        <v>0.2693872549019608</v>
       </c>
       <c r="FU26" t="n">
-        <v>26.3508883711231</v>
+        <v>7.00607067110224</v>
       </c>
       <c r="FV26" t="n">
-        <v>33.33333333333332</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="FW26" t="n">
-        <v>36.62354994353765</v>
+        <v>27.25283644802551</v>
       </c>
       <c r="FX26" t="n">
         <v>0</v>
       </c>
       <c r="FY26" t="n">
-        <v>62.33406731676629</v>
+        <v>52.58073817762401</v>
       </c>
       <c r="FZ26" t="n">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="GA26" t="n">
-        <v>6.829268292682927</v>
+        <v>49.51219512195122</v>
       </c>
       <c r="GB26" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="GC26" t="n">
-        <v>33.65506858481096</v>
+        <v>27.53212396069539</v>
       </c>
       <c r="GD26" t="n">
-        <v>17.9827533107484</v>
+        <v>14.23446791254354</v>
       </c>
       <c r="GE26" t="inlineStr">
         <is>
@@ -18923,10 +18923,10 @@
         </is>
       </c>
       <c r="GF26" t="n">
-        <v>29.64874171702522</v>
+        <v>16.74309930525312</v>
       </c>
       <c r="GG26" t="n">
-        <v>16.59216272674603</v>
+        <v>37.06611127703114</v>
       </c>
       <c r="GH26" t="inlineStr">
         <is>
@@ -18934,10 +18934,10 @@
         </is>
       </c>
       <c r="GI26" t="n">
-        <v>46.37194366792241</v>
+        <v>48.78052589557785</v>
       </c>
       <c r="GJ26" t="n">
-        <v>17.29958683414234</v>
+        <v>17.15072469453137</v>
       </c>
       <c r="GK26" t="inlineStr">
         <is>
@@ -18973,17 +18973,17 @@
       </c>
       <c r="GS26" t="inlineStr">
         <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is slightly below season AVG by -0.021', 'Model AVG is below preferred threshold at 0.225', 'Low matchup score (18)', 'Low split reliability score (7)', 'Real handedness split sample is smaller than preferred', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is below preferred threshold at 0.200', 'Low matchup score (14)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT26" t="inlineStr">
         <is>
-          <t>Luis Lara projects for 0.61 hits with a 45.6% 1+ hit probability.</t>
+          <t>Gary Sánchez projects for 0.49 hits with a 38.9% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU26" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|800325</t>
+          <t>2026-10-11|849809|596142</t>
         </is>
       </c>
       <c r="GV26" t="b">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19043,26 +19043,26 @@
         <v>849809</v>
       </c>
       <c r="D27" t="n">
-        <v>596142</v>
+        <v>676439</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -19083,43 +19083,43 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/676439</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Hunter+Feduccia</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>694819</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="P27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/player/596142</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Gary+S%C3%A1nchez</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>669373</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/669373</t>
+          <t>https://www.mlb.com/player/694819</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -19132,64 +19132,64 @@
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
-        <v>561</v>
+        <v>317</v>
       </c>
       <c r="AB27" t="n">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.2174688057040998</v>
+        <v>0.2050473186119874</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="AE27" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AF27" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG27" t="n">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.2088888888888889</v>
+        <v>0.2211981566820277</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.4691358024691358</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.3125</v>
+        <v>0.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AR27" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AS27" t="n">
         <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="AU27" t="n">
         <v>0.4666666666666667</v>
@@ -19198,87 +19198,87 @@
         <v>51</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="AZ27" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BA27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2178217821782178</v>
       </c>
       <c r="BC27" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="BD27" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BE27" t="n">
+        <v>47</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0.2338308457711443</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0.4191176470588235</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN27" t="n">
         <v>41</v>
       </c>
-      <c r="BF27" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="BH27" t="n">
+      <c r="BO27" t="n">
         <v>4</v>
       </c>
-      <c r="BI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>34</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>7</v>
-      </c>
       <c r="BP27" t="inlineStr">
         <is>
           <t>real_mlb_statSplits</t>
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="BR27" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="BS27" t="n">
-        <v>0.2263298219616434</v>
+        <v>0.2314292098542887</v>
       </c>
       <c r="BT27" t="n">
-        <v>0.5955872595860625</v>
+        <v>0.6037527284201104</v>
       </c>
       <c r="BU27" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="BV27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW27" t="n">
-        <v>0.2376237623762376</v>
+        <v>0.2457627118644068</v>
       </c>
       <c r="BX27" t="n">
         <v>100</v>
@@ -19287,61 +19287,61 @@
         <v>23</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0.2263298219616434</v>
+        <v>0.2314292098542887</v>
       </c>
       <c r="CA27" t="n">
-        <v>0.2236689350986835</v>
+        <v>0.2100924629315448</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.22224032815755</v>
+        <v>0.1996891273534744</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.2231303486673969</v>
+        <v>0.2009571959658669</v>
       </c>
       <c r="CD27" t="n">
-        <v>0.2236689350986835</v>
+        <v>0.2100924629315448</v>
       </c>
       <c r="CE27" t="n">
-        <v>0.2236689350986835</v>
+        <v>0.2100924629315448</v>
       </c>
       <c r="CF27" t="n">
-        <v>0.22224032815755</v>
+        <v>0.1996891273534744</v>
       </c>
       <c r="CG27" t="n">
-        <v>0.2376237623762376</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.2168674698795181</v>
+        <v>0.09375</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.2065535126320483</v>
+        <v>0.237297397586795</v>
       </c>
       <c r="CK27" t="n">
-        <v>0.2039838775264724</v>
+        <v>0.2287077243190746</v>
       </c>
       <c r="CL27" t="n">
-        <v>0.203732869871877</v>
+        <v>0.231789455241817</v>
       </c>
       <c r="CM27" t="n">
-        <v>0.2065535126320483</v>
+        <v>0.237297397586795</v>
       </c>
       <c r="CN27" t="n">
-        <v>0.2065535126320483</v>
+        <v>0.237297397586795</v>
       </c>
       <c r="CO27" t="n">
-        <v>0.2039838775264724</v>
+        <v>0.2287077243190746</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.1854838709677419</v>
+        <v>0.2457627118644068</v>
       </c>
       <c r="CQ27" t="n">
-        <v>0.2138364779874214</v>
+        <v>0.233160621761658</v>
       </c>
       <c r="CR27" t="n">
-        <v>0.2259937472085753</v>
+        <v>0.233201581027668</v>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -19349,124 +19349,124 @@
         </is>
       </c>
       <c r="CT27" t="n">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="CU27" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="CV27" t="n">
-        <v>0.2376237623762376</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CW27" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="CX27" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="CY27" t="n">
-        <v>0.1854838709677419</v>
+        <v>0.2457627118644068</v>
       </c>
       <c r="CZ27" t="n">
-        <v>243</v>
+        <v>46</v>
       </c>
       <c r="DA27" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="DB27" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="DC27" t="n">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="DD27" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.2138364779874214</v>
+        <v>0.233160621761658</v>
       </c>
       <c r="DF27" t="n">
-        <v>913</v>
+        <v>64</v>
       </c>
       <c r="DG27" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="DH27" t="n">
-        <v>0.2168674698795181</v>
+        <v>0.09375</v>
       </c>
       <c r="DI27" t="n">
-        <v>2239</v>
+        <v>253</v>
       </c>
       <c r="DJ27" t="n">
-        <v>506</v>
+        <v>59</v>
       </c>
       <c r="DK27" t="n">
-        <v>0.2259937472085753</v>
+        <v>0.233201581027668</v>
       </c>
       <c r="DL27" t="n">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="DM27" t="n">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="DN27" t="n">
-        <v>0.3</v>
+        <v>0.3789473684210526</v>
       </c>
       <c r="DO27" t="n">
-        <v>0.04354838709677419</v>
+        <v>0.06616541353383458</v>
       </c>
       <c r="DP27" t="n">
-        <v>7.147058823529412</v>
+        <v>4.946564885496183</v>
       </c>
       <c r="DQ27" t="n">
-        <v>0.7941176470588236</v>
+        <v>0.7213740458015268</v>
       </c>
       <c r="DR27" t="n">
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="DS27" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="DT27" t="n">
         <v>14</v>
       </c>
       <c r="DU27" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="DV27" t="n">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="DW27" t="n">
-        <v>158.6666666666667</v>
+        <v>174.6666666666667</v>
       </c>
       <c r="DX27" t="n">
-        <v>0.7941176470588236</v>
+        <v>0.5496183206106871</v>
       </c>
       <c r="DY27" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ27" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EA27" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EB27" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EC27" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="ED27" t="n">
-        <v>89</v>
+        <v>333</v>
       </c>
       <c r="EE27" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="EF27" t="n">
-        <v>669</v>
+        <v>455</v>
       </c>
       <c r="EG27" t="n">
-        <v>2748</v>
+        <v>394</v>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
@@ -19474,54 +19474,54 @@
         </is>
       </c>
       <c r="EI27" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EJ27" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EK27" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EL27" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="EM27" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="EN27" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.2093862815884477</v>
       </c>
       <c r="EO27" t="n">
-        <v>0.2257100149476831</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EP27" t="n">
-        <v>0.2143377001455604</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="EQ27" t="n">
-        <v>0.9654033088235294</v>
+        <v>0.9623202290076336</v>
       </c>
       <c r="ER27" t="n">
-        <v>0.9654033088235294</v>
+        <v>0.9623202290076336</v>
       </c>
       <c r="ES27" t="n">
         <v>0.97</v>
       </c>
       <c r="ET27" t="inlineStr">
         <is>
-          <t>{'era': 2.72, 'whip': 0.96, 'k_rate': 0.3, 'bb_rate': 0.043548387096774194, 'hits_per_9': 7.147058823529412, 'hr_per_9': 0.7941176470588236, 'batters_faced': 620, 'baa_vs_lhb_season': 0.2696629213483146, 'baa_vs_rhb_season': 0.1893939393939394, 'baa_vs_lhb_career': 0.2257100149476831, 'baa_vs_rhb_career': 0.21433770014556042, 'pitcher': 'Tarik Skubal', 'pitcher_id': 669373, 'pitcher_hand': 'L', 'pitcher_mlb_url': 'https://www.mlb.com/player/669373', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Tarik+Skubal', 'hitter': 'Gary Sánchez', 'hitter_id': 596142, 'bats': 'R', 'team': 'MIL', 'opp': 'LAD', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 1.8, 'whip': 0.8, 'k_rate': 0.37894736842105264, 'bb_rate': 0.06616541353383458, 'hits_per_9': 4.9465648854961835, 'hr_per_9': 0.7213740458015268, 'batters_faced': 665, 'baa_vs_lhb_season': 0.11411411411411411, 'baa_vs_rhb_season': 0.20938628158844766, 'baa_vs_lhb_career': 0.14285714285714285, 'baa_vs_rhb_career': 0.20812182741116753, 'pitcher': 'Jacob Misiorowski', 'pitcher_id': 694819, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/694819', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski', 'hitter': 'Hunter Feduccia', 'hitter_id': 676439, 'bats': 'L', 'team': 'LAD', 'opp': 'MIL', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
         </is>
       </c>
       <c r="EU27" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="EV27" t="n">
         <v>3.32</v>
       </c>
       <c r="EW27" t="n">
-        <v>3.001424228192964</v>
+        <v>3.117026105125171</v>
       </c>
       <c r="EX27" t="n">
-        <v>2.45571073215788</v>
+        <v>2.694799461403036</v>
       </c>
       <c r="EY27" t="n">
         <v>0.44</v>
@@ -19530,94 +19530,94 @@
         <v>0.995</v>
       </c>
       <c r="FA27" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="FB27" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.1141141141141141</v>
       </c>
       <c r="FC27" t="n">
-        <v>0.2130065359477124</v>
+        <v>0.2116399208427436</v>
       </c>
       <c r="FD27" t="n">
-        <v>0.2291533070652919</v>
+        <v>0.2350125853568183</v>
       </c>
       <c r="FE27" t="n">
-        <v>0.2291533070652919</v>
+        <v>0.2321441219846364</v>
       </c>
       <c r="FF27" t="n">
-        <v>0.2597923116615067</v>
+        <v>0.2217184839196224</v>
       </c>
       <c r="FG27" t="n">
-        <v>0.2457565789473684</v>
+        <v>0.2186949149965587</v>
       </c>
       <c r="FH27" t="n">
-        <v>0.2237455750229243</v>
+        <v>0.2190610801329982</v>
       </c>
       <c r="FI27" t="n">
         <v>0.9</v>
       </c>
       <c r="FJ27" t="n">
-        <v>0.2013710175206319</v>
+        <v>0.1971549721196983</v>
       </c>
       <c r="FK27" t="n">
-        <v>0.2003641624330288</v>
+        <v>0.1961691972590998</v>
       </c>
       <c r="FL27" t="n">
-        <v>0.2088888888888889</v>
+        <v>0.2211981566820277</v>
       </c>
       <c r="FM27" t="n">
-        <v>0.2088888888888889</v>
+        <v>0.2211981566820277</v>
       </c>
       <c r="FN27" t="n">
-        <v>0.2003641624330288</v>
+        <v>0.1961691972590998</v>
       </c>
       <c r="FO27" t="n">
-        <v>-0.008524726455860138</v>
+        <v>-0.02502895942292782</v>
       </c>
       <c r="FP27" t="n">
-        <v>0.008524726455860138</v>
+        <v>0.02502895942292782</v>
       </c>
       <c r="FQ27" t="n">
-        <v>0.4920364240266135</v>
+        <v>0.5286366471176882</v>
       </c>
       <c r="FR27" t="n">
-        <v>0.3886199034980642</v>
+        <v>0.4105920067618321</v>
       </c>
       <c r="FS27" t="n">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="FT27" t="n">
-        <v>0.2693872549019608</v>
+        <v>0.2187223276407337</v>
       </c>
       <c r="FU27" t="n">
-        <v>7.00607067110224</v>
+        <v>13.10610785294803</v>
       </c>
       <c r="FV27" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="FW27" t="n">
-        <v>27.25283644802551</v>
+        <v>30.25247638487572</v>
       </c>
       <c r="FX27" t="n">
         <v>0</v>
       </c>
       <c r="FY27" t="n">
-        <v>52.58073817762401</v>
+        <v>22.77783978866688</v>
       </c>
       <c r="FZ27" t="n">
-        <v>36.1</v>
+        <v>11.7</v>
       </c>
       <c r="GA27" t="n">
-        <v>49.51219512195122</v>
+        <v>37.31707317073171</v>
       </c>
       <c r="GB27" t="n">
         <v>19.8</v>
       </c>
       <c r="GC27" t="n">
-        <v>27.53212396069539</v>
+        <v>27.59028611444577</v>
       </c>
       <c r="GD27" t="n">
-        <v>14.23446791254354</v>
+        <v>12.10099055395029</v>
       </c>
       <c r="GE27" t="inlineStr">
         <is>
@@ -19625,10 +19625,10 @@
         </is>
       </c>
       <c r="GF27" t="n">
-        <v>16.74309930525312</v>
+        <v>16.87879577416584</v>
       </c>
       <c r="GG27" t="n">
-        <v>37.06611127703114</v>
+        <v>26.95015267326443</v>
       </c>
       <c r="GH27" t="inlineStr">
         <is>
@@ -19636,10 +19636,10 @@
         </is>
       </c>
       <c r="GI27" t="n">
-        <v>48.78052589557785</v>
+        <v>43.21435340749922</v>
       </c>
       <c r="GJ27" t="n">
-        <v>17.15072469453137</v>
+        <v>14.3850055045109</v>
       </c>
       <c r="GK27" t="inlineStr">
         <is>
@@ -19675,17 +19675,17 @@
       </c>
       <c r="GS27" t="inlineStr">
         <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.189 season BAA', 'Model AVG is below preferred threshold at 0.200', 'Low matchup score (14)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.114 season BAA', 'Model AVG is materially below season AVG by -0.025', 'Model AVG is below preferred threshold at 0.196', 'Low matchup score (12)', 'Low split reliability score (37)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT27" t="inlineStr">
         <is>
-          <t>Gary Sánchez projects for 0.49 hits with a 38.9% 1+ hit probability.</t>
+          <t>Hunter Feduccia projects for 0.53 hits with a 41.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU27" t="inlineStr">
         <is>
-          <t>2026-10-11|849809|596142</t>
+          <t>2026-10-11|849809|676439</t>
         </is>
       </c>
       <c r="GV27" t="b">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:22:33 AM</t>
+          <t>2026-10-11 12:39:01 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
+          <t>2026-10-11T12:39:01.033130-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19727,708 +19727,6 @@
         </is>
       </c>
       <c r="HD27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>849809</v>
-      </c>
-      <c r="D28" t="n">
-        <v>676439</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Hunter Feduccia</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>active_roster_fallback</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/player/676439</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Hunter+Feduccia</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>694819</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/player/694819</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
-        <v>317</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.2050473186119874</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.4191176470588235</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>217</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>251</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.2211981566820277</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.4191176470588235</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>31</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>51</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.2549019607843137</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>101</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0.2178217821782178</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>201</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>47</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0.2338308457711443</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0.4191176470588235</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>19</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>41</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP28" t="inlineStr">
-        <is>
-          <t>real_mlb_statSplits</t>
-        </is>
-      </c>
-      <c r="BQ28" t="n">
-        <v>193</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>45</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>0.2314292098542887</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>0.6037527284201104</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>118</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>0.2457627118644068</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>23</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>0.2314292098542887</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>0.2100924629315448</v>
-      </c>
-      <c r="CB28" t="n">
-        <v>0.1996891273534744</v>
-      </c>
-      <c r="CC28" t="n">
-        <v>0.2009571959658669</v>
-      </c>
-      <c r="CD28" t="n">
-        <v>0.2100924629315448</v>
-      </c>
-      <c r="CE28" t="n">
-        <v>0.2100924629315448</v>
-      </c>
-      <c r="CF28" t="n">
-        <v>0.1996891273534744</v>
-      </c>
-      <c r="CG28" t="n">
-        <v>0.1739130434782609</v>
-      </c>
-      <c r="CH28" t="n">
-        <v>0.108695652173913</v>
-      </c>
-      <c r="CI28" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="CJ28" t="n">
-        <v>0.237297397586795</v>
-      </c>
-      <c r="CK28" t="n">
-        <v>0.2287077243190746</v>
-      </c>
-      <c r="CL28" t="n">
-        <v>0.231789455241817</v>
-      </c>
-      <c r="CM28" t="n">
-        <v>0.237297397586795</v>
-      </c>
-      <c r="CN28" t="n">
-        <v>0.237297397586795</v>
-      </c>
-      <c r="CO28" t="n">
-        <v>0.2287077243190746</v>
-      </c>
-      <c r="CP28" t="n">
-        <v>0.2457627118644068</v>
-      </c>
-      <c r="CQ28" t="n">
-        <v>0.233160621761658</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>0.233201581027668</v>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>mlb_statSplits</t>
-        </is>
-      </c>
-      <c r="CT28" t="n">
-        <v>23</v>
-      </c>
-      <c r="CU28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CV28" t="n">
-        <v>0.1739130434782609</v>
-      </c>
-      <c r="CW28" t="n">
-        <v>118</v>
-      </c>
-      <c r="CX28" t="n">
-        <v>29</v>
-      </c>
-      <c r="CY28" t="n">
-        <v>0.2457627118644068</v>
-      </c>
-      <c r="CZ28" t="n">
-        <v>46</v>
-      </c>
-      <c r="DA28" t="n">
-        <v>5</v>
-      </c>
-      <c r="DB28" t="n">
-        <v>0.108695652173913</v>
-      </c>
-      <c r="DC28" t="n">
-        <v>193</v>
-      </c>
-      <c r="DD28" t="n">
-        <v>45</v>
-      </c>
-      <c r="DE28" t="n">
-        <v>0.233160621761658</v>
-      </c>
-      <c r="DF28" t="n">
-        <v>64</v>
-      </c>
-      <c r="DG28" t="n">
-        <v>6</v>
-      </c>
-      <c r="DH28" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="DI28" t="n">
-        <v>253</v>
-      </c>
-      <c r="DJ28" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK28" t="n">
-        <v>0.233201581027668</v>
-      </c>
-      <c r="DL28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DM28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DN28" t="n">
-        <v>0.3789473684210526</v>
-      </c>
-      <c r="DO28" t="n">
-        <v>0.06616541353383458</v>
-      </c>
-      <c r="DP28" t="n">
-        <v>4.946564885496183</v>
-      </c>
-      <c r="DQ28" t="n">
-        <v>0.7213740458015268</v>
-      </c>
-      <c r="DR28" t="n">
-        <v>665</v>
-      </c>
-      <c r="DS28" t="n">
-        <v>96</v>
-      </c>
-      <c r="DT28" t="n">
-        <v>14</v>
-      </c>
-      <c r="DU28" t="n">
-        <v>44</v>
-      </c>
-      <c r="DV28" t="n">
-        <v>252</v>
-      </c>
-      <c r="DW28" t="n">
-        <v>174.6666666666667</v>
-      </c>
-      <c r="DX28" t="n">
-        <v>0.5496183206106871</v>
-      </c>
-      <c r="DY28" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="DZ28" t="n">
-        <v>0.1141141141141141</v>
-      </c>
-      <c r="EA28" t="n">
-        <v>0.2093862815884477</v>
-      </c>
-      <c r="EB28" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="EC28" t="n">
-        <v>0.2081218274111675</v>
-      </c>
-      <c r="ED28" t="n">
-        <v>333</v>
-      </c>
-      <c r="EE28" t="n">
-        <v>277</v>
-      </c>
-      <c r="EF28" t="n">
-        <v>455</v>
-      </c>
-      <c r="EG28" t="n">
-        <v>394</v>
-      </c>
-      <c r="EH28" t="inlineStr">
-        <is>
-          <t>mlb_pitching_statSplits</t>
-        </is>
-      </c>
-      <c r="EI28" t="n">
-        <v>0.1141141141141141</v>
-      </c>
-      <c r="EJ28" t="n">
-        <v>0.2093862815884477</v>
-      </c>
-      <c r="EK28" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="EL28" t="n">
-        <v>0.2081218274111675</v>
-      </c>
-      <c r="EM28" t="n">
-        <v>0.1141141141141141</v>
-      </c>
-      <c r="EN28" t="n">
-        <v>0.2093862815884477</v>
-      </c>
-      <c r="EO28" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="EP28" t="n">
-        <v>0.2081218274111675</v>
-      </c>
-      <c r="EQ28" t="n">
-        <v>0.9623202290076336</v>
-      </c>
-      <c r="ER28" t="n">
-        <v>0.9623202290076336</v>
-      </c>
-      <c r="ES28" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="ET28" t="inlineStr">
-        <is>
-          <t>{'era': 1.8, 'whip': 0.8, 'k_rate': 0.37894736842105264, 'bb_rate': 0.06616541353383458, 'hits_per_9': 4.9465648854961835, 'hr_per_9': 0.7213740458015268, 'batters_faced': 665, 'baa_vs_lhb_season': 0.11411411411411411, 'baa_vs_rhb_season': 0.20938628158844766, 'baa_vs_lhb_career': 0.14285714285714285, 'baa_vs_rhb_career': 0.20812182741116753, 'pitcher': 'Jacob Misiorowski', 'pitcher_id': 694819, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/694819', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Jacob+Misiorowski', 'hitter': 'Hunter Feduccia', 'hitter_id': 676439, 'bats': 'L', 'team': 'LAD', 'opp': 'MIL', 'game_pk': 849809, 'game_time_et': '8:00 PM'}</t>
-        </is>
-      </c>
-      <c r="EU28" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="EV28" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="EW28" t="n">
-        <v>3.117026105125171</v>
-      </c>
-      <c r="EX28" t="n">
-        <v>2.694799461403036</v>
-      </c>
-      <c r="EY28" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="EZ28" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="FA28" t="n">
-        <v>0.1141141141141141</v>
-      </c>
-      <c r="FB28" t="n">
-        <v>0.1141141141141141</v>
-      </c>
-      <c r="FC28" t="n">
-        <v>0.2116399208427436</v>
-      </c>
-      <c r="FD28" t="n">
-        <v>0.2350125853568183</v>
-      </c>
-      <c r="FE28" t="n">
-        <v>0.2321441219846364</v>
-      </c>
-      <c r="FF28" t="n">
-        <v>0.2217184839196224</v>
-      </c>
-      <c r="FG28" t="n">
-        <v>0.2186949149965587</v>
-      </c>
-      <c r="FH28" t="n">
-        <v>0.2190610801329982</v>
-      </c>
-      <c r="FI28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="FJ28" t="n">
-        <v>0.1971549721196983</v>
-      </c>
-      <c r="FK28" t="n">
-        <v>0.1961691972590998</v>
-      </c>
-      <c r="FL28" t="n">
-        <v>0.2211981566820277</v>
-      </c>
-      <c r="FM28" t="n">
-        <v>0.2211981566820277</v>
-      </c>
-      <c r="FN28" t="n">
-        <v>0.1961691972590998</v>
-      </c>
-      <c r="FO28" t="n">
-        <v>-0.02502895942292782</v>
-      </c>
-      <c r="FP28" t="n">
-        <v>0.02502895942292782</v>
-      </c>
-      <c r="FQ28" t="n">
-        <v>0.5286366471176882</v>
-      </c>
-      <c r="FR28" t="n">
-        <v>0.4105920067618321</v>
-      </c>
-      <c r="FS28" t="n">
-        <v>144</v>
-      </c>
-      <c r="FT28" t="n">
-        <v>0.2187223276407337</v>
-      </c>
-      <c r="FU28" t="n">
-        <v>13.10610785294803</v>
-      </c>
-      <c r="FV28" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="FW28" t="n">
-        <v>30.25247638487572</v>
-      </c>
-      <c r="FX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY28" t="n">
-        <v>22.77783978866688</v>
-      </c>
-      <c r="FZ28" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="GA28" t="n">
-        <v>37.31707317073171</v>
-      </c>
-      <c r="GB28" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="GC28" t="n">
-        <v>27.59028611444577</v>
-      </c>
-      <c r="GD28" t="n">
-        <v>12.10099055395029</v>
-      </c>
-      <c r="GE28" t="inlineStr">
-        <is>
-          <t>no_lineup_order</t>
-        </is>
-      </c>
-      <c r="GF28" t="n">
-        <v>16.87879577416584</v>
-      </c>
-      <c r="GG28" t="n">
-        <v>26.95015267326443</v>
-      </c>
-      <c r="GH28" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="GI28" t="n">
-        <v>43.21435340749922</v>
-      </c>
-      <c r="GJ28" t="n">
-        <v>14.3850055045109</v>
-      </c>
-      <c r="GK28" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="GL28" t="b">
-        <v>0</v>
-      </c>
-      <c r="GM28" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="GN28" t="inlineStr">
-        <is>
-          <t>Upcoming game refreshed this run</t>
-        </is>
-      </c>
-      <c r="GO28" t="b">
-        <v>0</v>
-      </c>
-      <c r="GP28" t="b">
-        <v>0</v>
-      </c>
-      <c r="GQ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="GR28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="GS28" t="inlineStr">
-        <is>
-          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.114 season BAA', 'Model AVG is materially below season AVG by -0.025', 'Model AVG is below preferred threshold at 0.196', 'Low matchup score (12)', 'Low split reliability score (37)', 'No confirmed lineup slot from MLB feed yet', 'Opposing pitcher strikeout rate is elevated', 'Some pinch-hit or role risk']</t>
-        </is>
-      </c>
-      <c r="GT28" t="inlineStr">
-        <is>
-          <t>Hunter Feduccia projects for 0.53 hits with a 41.1% 1+ hit probability.</t>
-        </is>
-      </c>
-      <c r="GU28" t="inlineStr">
-        <is>
-          <t>2026-10-11|849809|676439</t>
-        </is>
-      </c>
-      <c r="GV28" t="b">
-        <v>0</v>
-      </c>
-      <c r="GW28" t="inlineStr">
-        <is>
-          <t>LIVE_REFRESH</t>
-        </is>
-      </c>
-      <c r="GX28" t="inlineStr">
-        <is>
-          <t>2026-10-11 12:22:33 AM</t>
-        </is>
-      </c>
-      <c r="GY28" t="inlineStr">
-        <is>
-          <t>full_day_freeze_started_update_upcoming_et</t>
-        </is>
-      </c>
-      <c r="GZ28" t="inlineStr">
-        <is>
-          <t>Full-day board: all projected players remain visible. Games that have started are frozen from the last saved pregame projection. Only games that have not started are refreshed on reruns.</t>
-        </is>
-      </c>
-      <c r="HA28" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="HB28" t="inlineStr">
-        <is>
-          <t>2026-10-11T00:22:33.246144-04:00</t>
-        </is>
-      </c>
-      <c r="HC28" t="inlineStr">
-        <is>
-          <t>Hourly from 11:00 AM through 10:00 PM Eastern Time</t>
-        </is>
-      </c>
-      <c r="HD28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:39:01 PM</t>
+          <t>2026-10-11 03:23:34 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-11T12:39:01.033130-04:00</t>
+          <t>2026-10-11T15:23:34.017614-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD37"/>
+  <dimension ref="A1:HE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2152,7 +2157,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,8 +2186,9 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2288,7 +2294,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2817,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2855,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2884,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2893,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3564,7 +3575,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3584,7 +3595,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,8 +3604,9 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3700,7 +3712,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4235,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4273,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4302,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4311,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4976,7 +4993,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4996,7 +5013,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,8 +5022,9 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5682,7 +5700,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5702,7 +5720,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,8 +5729,9 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5818,7 +5837,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6360,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6398,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6427,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6436,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6548,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7071,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7109,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7138,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7147,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7259,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7782,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7820,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7849,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7858,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7970,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8493,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8531,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8560,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8569,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -9212,7 +9251,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9232,7 +9271,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,8 +9280,9 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9918,7 +9958,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9938,7 +9978,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,8 +9987,9 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10624,7 +10665,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10644,7 +10685,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,8 +10694,9 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10760,7 +10802,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11325,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11363,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11392,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11401,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11513,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12036,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12074,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12103,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12112,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12742,7 +12794,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12762,7 +12814,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,8 +12823,9 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12878,7 +12931,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13454,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13492,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13521,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13530,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -14154,7 +14212,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14174,7 +14232,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,8 +14241,9 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14860,7 +14919,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14880,7 +14939,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14889,8 +14948,9 @@
         </is>
       </c>
       <c r="HD20" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14996,7 +15056,7 @@
         </is>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
@@ -15519,12 +15579,12 @@
       </c>
       <c r="GM21" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN21" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO21" t="b">
@@ -15557,11 +15617,11 @@
         </is>
       </c>
       <c r="GV21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW21" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX21" t="inlineStr">
@@ -15586,7 +15646,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15595,7 +15655,12 @@
         </is>
       </c>
       <c r="HD21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE21" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -16272,7 +16337,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16292,7 +16357,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16301,8 +16366,9 @@
         </is>
       </c>
       <c r="HD22" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16978,7 +17044,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16998,7 +17064,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17007,8 +17073,9 @@
         </is>
       </c>
       <c r="HD23" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17684,7 +17751,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17704,7 +17771,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17713,8 +17780,9 @@
         </is>
       </c>
       <c r="HD24" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17820,7 +17888,7 @@
         </is>
       </c>
       <c r="Y25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
@@ -18343,12 +18411,12 @@
       </c>
       <c r="GM25" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN25" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO25" t="b">
@@ -18381,11 +18449,11 @@
         </is>
       </c>
       <c r="GV25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW25" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX25" t="inlineStr">
@@ -18410,7 +18478,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18419,7 +18487,12 @@
         </is>
       </c>
       <c r="HD25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE25" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -18526,7 +18599,7 @@
         </is>
       </c>
       <c r="Y26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
@@ -19049,12 +19122,12 @@
       </c>
       <c r="GM26" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN26" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO26" t="b">
@@ -19087,11 +19160,11 @@
         </is>
       </c>
       <c r="GV26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW26" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX26" t="inlineStr">
@@ -19116,7 +19189,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19125,7 +19198,12 @@
         </is>
       </c>
       <c r="HD26" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE26" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -19802,7 +19880,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19822,7 +19900,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19831,8 +19909,9 @@
         </is>
       </c>
       <c r="HD27" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20508,7 +20587,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20528,7 +20607,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">
@@ -20537,8 +20616,9 @@
         </is>
       </c>
       <c r="HD28" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20644,7 +20724,7 @@
         </is>
       </c>
       <c r="Y29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
@@ -21167,12 +21247,12 @@
       </c>
       <c r="GM29" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN29" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO29" t="b">
@@ -21205,11 +21285,11 @@
         </is>
       </c>
       <c r="GV29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW29" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX29" t="inlineStr">
@@ -21234,7 +21314,7 @@
       </c>
       <c r="HB29" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC29" t="inlineStr">
@@ -21243,7 +21323,12 @@
         </is>
       </c>
       <c r="HD29" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE29" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -21350,7 +21435,7 @@
         </is>
       </c>
       <c r="Y30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
@@ -21873,12 +21958,12 @@
       </c>
       <c r="GM30" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN30" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO30" t="b">
@@ -21911,11 +21996,11 @@
         </is>
       </c>
       <c r="GV30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW30" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX30" t="inlineStr">
@@ -21940,7 +22025,7 @@
       </c>
       <c r="HB30" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC30" t="inlineStr">
@@ -21949,7 +22034,12 @@
         </is>
       </c>
       <c r="HD30" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE30" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -22056,7 +22146,7 @@
         </is>
       </c>
       <c r="Y31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
@@ -22579,12 +22669,12 @@
       </c>
       <c r="GM31" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN31" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO31" t="b">
@@ -22617,11 +22707,11 @@
         </is>
       </c>
       <c r="GV31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW31" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX31" t="inlineStr">
@@ -22646,7 +22736,7 @@
       </c>
       <c r="HB31" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC31" t="inlineStr">
@@ -22655,7 +22745,12 @@
         </is>
       </c>
       <c r="HD31" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE31" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -22762,7 +22857,7 @@
         </is>
       </c>
       <c r="Y32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
@@ -23285,12 +23380,12 @@
       </c>
       <c r="GM32" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN32" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO32" t="b">
@@ -23323,11 +23418,11 @@
         </is>
       </c>
       <c r="GV32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW32" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX32" t="inlineStr">
@@ -23352,7 +23447,7 @@
       </c>
       <c r="HB32" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC32" t="inlineStr">
@@ -23361,7 +23456,12 @@
         </is>
       </c>
       <c r="HD32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE32" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -23468,7 +23568,7 @@
         </is>
       </c>
       <c r="Y33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
@@ -23991,12 +24091,12 @@
       </c>
       <c r="GM33" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN33" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO33" t="b">
@@ -24029,11 +24129,11 @@
         </is>
       </c>
       <c r="GV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW33" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX33" t="inlineStr">
@@ -24058,7 +24158,7 @@
       </c>
       <c r="HB33" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC33" t="inlineStr">
@@ -24067,7 +24167,12 @@
         </is>
       </c>
       <c r="HD33" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE33" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -24744,7 +24849,7 @@
       </c>
       <c r="GX34" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY34" t="inlineStr">
@@ -24764,7 +24869,7 @@
       </c>
       <c r="HB34" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC34" t="inlineStr">
@@ -24773,8 +24878,9 @@
         </is>
       </c>
       <c r="HD34" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25450,7 +25556,7 @@
       </c>
       <c r="GX35" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY35" t="inlineStr">
@@ -25470,7 +25576,7 @@
       </c>
       <c r="HB35" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC35" t="inlineStr">
@@ -25479,8 +25585,9 @@
         </is>
       </c>
       <c r="HD35" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -25586,7 +25693,7 @@
         </is>
       </c>
       <c r="Y36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
@@ -26109,12 +26216,12 @@
       </c>
       <c r="GM36" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN36" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO36" t="b">
@@ -26147,11 +26254,11 @@
         </is>
       </c>
       <c r="GV36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW36" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX36" t="inlineStr">
@@ -26176,7 +26283,7 @@
       </c>
       <c r="HB36" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC36" t="inlineStr">
@@ -26185,7 +26292,12 @@
         </is>
       </c>
       <c r="HD36" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE36" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:25:52 PM</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -26862,7 +26974,7 @@
       </c>
       <c r="GX37" t="inlineStr">
         <is>
-          <t>2026-10-12 04:16:06 PM</t>
+          <t>2026-10-12 06:25:52 PM</t>
         </is>
       </c>
       <c r="GY37" t="inlineStr">
@@ -26882,7 +26994,7 @@
       </c>
       <c r="HB37" t="inlineStr">
         <is>
-          <t>2026-10-12T16:16:06.922193-04:00</t>
+          <t>2026-10-12T18:25:52.512562-04:00</t>
         </is>
       </c>
       <c r="HC37" t="inlineStr">
@@ -26891,8 +27003,9 @@
         </is>
       </c>
       <c r="HD37" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="HE37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2148,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2186,9 +2186,13 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2884,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2893,11 +2897,11 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE3" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3528,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3566,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3595,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3604,9 +3608,13 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4302,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4311,11 +4319,11 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE5" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4946,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4984,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -5013,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5022,9 +5030,13 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5130,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5653,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5691,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5720,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5729,9 +5741,13 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6427,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6436,11 +6452,11 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE8" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7147,11 +7163,11 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE9" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7858,11 +7874,11 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE10" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8569,11 +8585,11 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE11" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9204,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9242,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9271,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9280,9 +9296,13 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9388,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9911,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9949,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9978,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9987,9 +10007,13 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10095,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10618,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10656,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10685,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10694,9 +10718,13 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11392,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11401,11 +11429,11 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE15" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12112,11 +12140,11 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE16" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12747,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12785,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12814,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12823,9 +12851,13 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13521,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13530,11 +13562,11 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE18" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14165,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14203,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14232,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14241,9 +14273,13 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14349,7 +14385,7 @@
         </is>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
@@ -14872,12 +14908,12 @@
       </c>
       <c r="GM20" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN20" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO20" t="b">
@@ -14910,11 +14946,11 @@
         </is>
       </c>
       <c r="GV20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW20" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX20" t="inlineStr">
@@ -14939,7 +14975,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14948,9 +14984,13 @@
         </is>
       </c>
       <c r="HD20" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE20" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE20" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15646,7 +15686,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15655,11 +15695,11 @@
         </is>
       </c>
       <c r="HD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE21" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -15767,7 +15807,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
@@ -16290,12 +16330,12 @@
       </c>
       <c r="GM22" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN22" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO22" t="b">
@@ -16328,11 +16368,11 @@
         </is>
       </c>
       <c r="GV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW22" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX22" t="inlineStr">
@@ -16357,7 +16397,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16366,9 +16406,13 @@
         </is>
       </c>
       <c r="HD22" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE22" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16474,7 +16518,7 @@
         </is>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
@@ -16997,12 +17041,12 @@
       </c>
       <c r="GM23" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN23" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO23" t="b">
@@ -17035,11 +17079,11 @@
         </is>
       </c>
       <c r="GV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW23" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX23" t="inlineStr">
@@ -17064,7 +17108,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17073,9 +17117,13 @@
         </is>
       </c>
       <c r="HD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE23" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17181,7 +17229,7 @@
         </is>
       </c>
       <c r="Y24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
@@ -17704,12 +17752,12 @@
       </c>
       <c r="GM24" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN24" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO24" t="b">
@@ -17742,11 +17790,11 @@
         </is>
       </c>
       <c r="GV24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW24" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX24" t="inlineStr">
@@ -17771,7 +17819,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17780,9 +17828,13 @@
         </is>
       </c>
       <c r="HD24" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE24" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE24" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18478,7 +18530,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18487,11 +18539,11 @@
         </is>
       </c>
       <c r="HD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE25" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19241,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19198,11 +19250,11 @@
         </is>
       </c>
       <c r="HD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE26" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19362,7 @@
         </is>
       </c>
       <c r="Y27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
@@ -19833,12 +19885,12 @@
       </c>
       <c r="GM27" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN27" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO27" t="b">
@@ -19871,11 +19923,11 @@
         </is>
       </c>
       <c r="GV27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW27" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX27" t="inlineStr">
@@ -19900,7 +19952,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19909,9 +19961,13 @@
         </is>
       </c>
       <c r="HD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE27" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE27" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20017,7 +20073,7 @@
         </is>
       </c>
       <c r="Y28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
@@ -20540,12 +20596,12 @@
       </c>
       <c r="GM28" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN28" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO28" t="b">
@@ -20578,11 +20634,11 @@
         </is>
       </c>
       <c r="GV28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW28" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX28" t="inlineStr">
@@ -20607,7 +20663,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">
@@ -20616,9 +20672,13 @@
         </is>
       </c>
       <c r="HD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE28" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21314,7 +21374,7 @@
       </c>
       <c r="HB29" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC29" t="inlineStr">
@@ -21323,11 +21383,11 @@
         </is>
       </c>
       <c r="HD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE29" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -22025,7 +22085,7 @@
       </c>
       <c r="HB30" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC30" t="inlineStr">
@@ -22034,11 +22094,11 @@
         </is>
       </c>
       <c r="HD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE30" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22796,7 @@
       </c>
       <c r="HB31" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC31" t="inlineStr">
@@ -22745,11 +22805,11 @@
         </is>
       </c>
       <c r="HD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE31" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -23447,7 +23507,7 @@
       </c>
       <c r="HB32" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC32" t="inlineStr">
@@ -23456,11 +23516,11 @@
         </is>
       </c>
       <c r="HD32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE32" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -24158,7 +24218,7 @@
       </c>
       <c r="HB33" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC33" t="inlineStr">
@@ -24167,11 +24227,11 @@
         </is>
       </c>
       <c r="HD33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE33" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24339,7 @@
         </is>
       </c>
       <c r="Y34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
@@ -24802,12 +24862,12 @@
       </c>
       <c r="GM34" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN34" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO34" t="b">
@@ -24840,11 +24900,11 @@
         </is>
       </c>
       <c r="GV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW34" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX34" t="inlineStr">
@@ -24869,7 +24929,7 @@
       </c>
       <c r="HB34" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC34" t="inlineStr">
@@ -24878,9 +24938,13 @@
         </is>
       </c>
       <c r="HD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE34" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24986,7 +25050,7 @@
         </is>
       </c>
       <c r="Y35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
@@ -25509,12 +25573,12 @@
       </c>
       <c r="GM35" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN35" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO35" t="b">
@@ -25547,11 +25611,11 @@
         </is>
       </c>
       <c r="GV35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW35" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX35" t="inlineStr">
@@ -25576,7 +25640,7 @@
       </c>
       <c r="HB35" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC35" t="inlineStr">
@@ -25585,9 +25649,13 @@
         </is>
       </c>
       <c r="HD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE35" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE35" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26283,7 +26351,7 @@
       </c>
       <c r="HB36" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC36" t="inlineStr">
@@ -26292,11 +26360,11 @@
         </is>
       </c>
       <c r="HD36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE36" t="inlineStr">
         <is>
-          <t>2026-10-12 06:25:52 PM</t>
+          <t>2026-10-12 11:22:40 PM</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26472,7 @@
         </is>
       </c>
       <c r="Y37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
@@ -26927,12 +26995,12 @@
       </c>
       <c r="GM37" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN37" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO37" t="b">
@@ -26965,11 +27033,11 @@
         </is>
       </c>
       <c r="GV37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW37" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX37" t="inlineStr">
@@ -26994,7 +27062,7 @@
       </c>
       <c r="HB37" t="inlineStr">
         <is>
-          <t>2026-10-12T18:25:52.512562-04:00</t>
+          <t>2026-10-12T23:22:40.344679-04:00</t>
         </is>
       </c>
       <c r="HC37" t="inlineStr">
@@ -27003,9 +27071,13 @@
         </is>
       </c>
       <c r="HD37" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE37" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE37" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:22:40 PM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-13T16:32:49.512340-04:00</t>
+          <t>2026-10-13T20:10:40.864891-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:10:40 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:54:38 AM</t>
+          <t>2026-10-14 11:49:46 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-14T01:54:38.368227-04:00</t>
+          <t>2026-10-14T11:49:46.310957-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:46 AM</t>
+          <t>2026-10-14 03:13:47 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:46.310957-04:00</t>
+          <t>2026-10-14T15:13:47.836705-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-14T19:01:23.186804-04:00</t>
+          <t>2026-10-14T21:14:46.483423-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:14:46 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2177,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2186,11 +2186,11 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE2" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2859,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2897,9 +2897,13 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3005,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3528,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3566,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3595,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3604,9 +3608,13 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4302,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4311,11 +4319,11 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE5" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4946,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4984,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -5013,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5022,9 +5030,13 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5720,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5729,11 +5741,11 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE7" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6364,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6402,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6431,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6440,9 +6452,13 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6548,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7071,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7109,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7138,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7147,9 +7163,13 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7845,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7854,11 +7874,11 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE10" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8489,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8527,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8556,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8565,9 +8585,13 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9263,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9272,11 +9296,11 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE12" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9907,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9945,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9974,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9983,9 +10007,13 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10091,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10614,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10652,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10681,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10690,9 +10718,13 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11388,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11397,11 +11429,11 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE15" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -12032,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12070,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12099,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12108,9 +12140,13 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE16" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12806,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12815,11 +12851,11 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE17" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13526,11 +13562,11 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE18" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14161,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14199,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14228,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14237,9 +14273,13 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14935,7 +14975,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14944,11 +14984,11 @@
         </is>
       </c>
       <c r="HD20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE20" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -15646,7 +15686,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15655,11 +15695,11 @@
         </is>
       </c>
       <c r="HD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE21" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -15767,7 +15807,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
@@ -16290,12 +16330,12 @@
       </c>
       <c r="GM22" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN22" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO22" t="b">
@@ -16328,11 +16368,11 @@
         </is>
       </c>
       <c r="GV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW22" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX22" t="inlineStr">
@@ -16357,7 +16397,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16366,9 +16406,13 @@
         </is>
       </c>
       <c r="HD22" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE22" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16474,7 +16518,7 @@
         </is>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
@@ -16997,12 +17041,12 @@
       </c>
       <c r="GM23" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN23" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO23" t="b">
@@ -17035,11 +17079,11 @@
         </is>
       </c>
       <c r="GV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW23" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX23" t="inlineStr">
@@ -17064,7 +17108,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17073,9 +17117,13 @@
         </is>
       </c>
       <c r="HD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE23" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17771,7 +17819,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17780,11 +17828,11 @@
         </is>
       </c>
       <c r="HD24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE24" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -18482,7 +18530,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18491,11 +18539,11 @@
         </is>
       </c>
       <c r="HD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE25" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19241,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19202,11 +19250,11 @@
         </is>
       </c>
       <c r="HD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE26" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19362,7 @@
         </is>
       </c>
       <c r="Y27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
@@ -19837,12 +19885,12 @@
       </c>
       <c r="GM27" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN27" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO27" t="b">
@@ -19875,11 +19923,11 @@
         </is>
       </c>
       <c r="GV27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW27" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX27" t="inlineStr">
@@ -19904,7 +19952,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19913,9 +19961,13 @@
         </is>
       </c>
       <c r="HD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE27" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE27" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20021,7 +20073,7 @@
         </is>
       </c>
       <c r="Y28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
@@ -20544,12 +20596,12 @@
       </c>
       <c r="GM28" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN28" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO28" t="b">
@@ -20582,11 +20634,11 @@
         </is>
       </c>
       <c r="GV28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW28" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX28" t="inlineStr">
@@ -20611,7 +20663,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">
@@ -20620,9 +20672,13 @@
         </is>
       </c>
       <c r="HD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE28" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20728,7 +20784,7 @@
         </is>
       </c>
       <c r="Y29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
@@ -21251,12 +21307,12 @@
       </c>
       <c r="GM29" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN29" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO29" t="b">
@@ -21289,11 +21345,11 @@
         </is>
       </c>
       <c r="GV29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW29" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX29" t="inlineStr">
@@ -21318,7 +21374,7 @@
       </c>
       <c r="HB29" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC29" t="inlineStr">
@@ -21327,9 +21383,13 @@
         </is>
       </c>
       <c r="HD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE29" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -22025,7 +22085,7 @@
       </c>
       <c r="HB30" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC30" t="inlineStr">
@@ -22034,11 +22094,11 @@
         </is>
       </c>
       <c r="HD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE30" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -22146,7 +22206,7 @@
         </is>
       </c>
       <c r="Y31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
@@ -22669,12 +22729,12 @@
       </c>
       <c r="GM31" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN31" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO31" t="b">
@@ -22707,11 +22767,11 @@
         </is>
       </c>
       <c r="GV31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW31" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX31" t="inlineStr">
@@ -22736,7 +22796,7 @@
       </c>
       <c r="HB31" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC31" t="inlineStr">
@@ -22745,9 +22805,13 @@
         </is>
       </c>
       <c r="HD31" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE31" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -23443,7 +23507,7 @@
       </c>
       <c r="HB32" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC32" t="inlineStr">
@@ -23452,11 +23516,11 @@
         </is>
       </c>
       <c r="HD32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE32" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -23564,7 +23628,7 @@
         </is>
       </c>
       <c r="Y33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
@@ -24087,12 +24151,12 @@
       </c>
       <c r="GM33" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN33" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO33" t="b">
@@ -24125,11 +24189,11 @@
         </is>
       </c>
       <c r="GV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW33" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX33" t="inlineStr">
@@ -24154,7 +24218,7 @@
       </c>
       <c r="HB33" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC33" t="inlineStr">
@@ -24163,9 +24227,13 @@
         </is>
       </c>
       <c r="HD33" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE33" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE33" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -24861,7 +24929,7 @@
       </c>
       <c r="HB34" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC34" t="inlineStr">
@@ -24870,11 +24938,11 @@
         </is>
       </c>
       <c r="HD34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE34" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -24982,7 +25050,7 @@
         </is>
       </c>
       <c r="Y35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
@@ -25505,12 +25573,12 @@
       </c>
       <c r="GM35" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN35" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO35" t="b">
@@ -25543,11 +25611,11 @@
         </is>
       </c>
       <c r="GV35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW35" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX35" t="inlineStr">
@@ -25572,7 +25640,7 @@
       </c>
       <c r="HB35" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC35" t="inlineStr">
@@ -25581,9 +25649,13 @@
         </is>
       </c>
       <c r="HD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="HE35" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="HE35" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:06:54 PM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26279,7 +26351,7 @@
       </c>
       <c r="HB36" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC36" t="inlineStr">
@@ -26288,11 +26360,11 @@
         </is>
       </c>
       <c r="HD36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE36" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>
@@ -26990,7 +27062,7 @@
       </c>
       <c r="HB37" t="inlineStr">
         <is>
-          <t>2026-10-15T17:59:18.246746-04:00</t>
+          <t>2026-10-15T20:06:54.957152-04:00</t>
         </is>
       </c>
       <c r="HC37" t="inlineStr">
@@ -26999,11 +27071,11 @@
         </is>
       </c>
       <c r="HD37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HE37" t="inlineStr">
         <is>
-          <t>2026-10-15 05:59:18 PM</t>
+          <t>2026-10-15 08:06:54 PM</t>
         </is>
       </c>
     </row>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-16 11:22:30 AM</t>
+          <t>2026-10-16 02:40:05 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-16T11:22:30.070290-04:00</t>
+          <t>2026-10-16T14:40:05.251608-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-16T17:57:29.457741-04:00</t>
+          <t>2026-10-16T20:11:08.847868-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:11:08 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Chandler Simpson', 'hitter_id': 802415, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Chandler Simpson', 'hitter_id': 802415, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU2" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Yandy Díaz', 'hitter_id': 650490, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Yandy Díaz', 'hitter_id': 650490, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU3" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Junior Caminero', 'hitter_id': 691406, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Junior Caminero', 'hitter_id': 691406, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU4" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Liam Hicks', 'hitter_id': 689414, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Liam Hicks', 'hitter_id': 689414, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU5" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonathan Aranda', 'hitter_id': 666018, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonathan Aranda', 'hitter_id': 666018, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU6" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Nick Fortes', 'hitter_id': 663743, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Nick Fortes', 'hitter_id': 663743, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU7" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonny DeLuca', 'hitter_id': 676356, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonny DeLuca', 'hitter_id': 676356, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU8" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Steven Kwan', 'hitter_id': 680757, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Steven Kwan', 'hitter_id': 680757, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU9" t="n">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Chase DeLauter', 'hitter_id': 800050, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Chase DeLauter', 'hitter_id': 800050, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU10" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="ET11" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Jo Adell', 'hitter_id': 666176, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Jo Adell', 'hitter_id': 666176, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU11" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="ET12" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Nathaniel Lowe', 'hitter_id': 663993, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Nathaniel Lowe', 'hitter_id': 663993, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU12" t="n">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="ET13" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Brayan Rocchio', 'hitter_id': 677587, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Brayan Rocchio', 'hitter_id': 677587, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU13" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="ET14" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ben Williamson', 'hitter_id': 810938, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ben Williamson', 'hitter_id': 810938, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU14" t="n">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="ET15" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'José Ramírez', 'hitter_id': 608070, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'José Ramírez', 'hitter_id': 608070, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU15" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="ET16" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Travis Bazzana', 'hitter_id': 683953, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Travis Bazzana', 'hitter_id': 683953, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU16" t="n">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="ET17" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Angel Martínez', 'hitter_id': 682657, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Angel Martínez', 'hitter_id': 682657, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU17" t="n">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="ET18" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jorge Mateo', 'hitter_id': 622761, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jorge Mateo', 'hitter_id': 622761, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU18" t="n">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="ET19" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Richie Palacios', 'hitter_id': 680700, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Richie Palacios', 'hitter_id': 680700, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU19" t="n">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="ET20" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Taylor Walls', 'hitter_id': 670764, 'bats': 'S', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Taylor Walls', 'hitter_id': 670764, 'bats': 'S', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU20" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="ET21" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Cedric Mullins', 'hitter_id': 656775, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Cedric Mullins', 'hitter_id': 656775, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU21" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="ET22" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Patrick Bailey', 'hitter_id': 672275, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Patrick Bailey', 'hitter_id': 672275, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU22" t="n">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="ET23" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Victor Mesa Jr.', 'hitter_id': 683748, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Victor Mesa Jr.', 'hitter_id': 683748, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU23" t="n">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="ET24" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Austin Hedges', 'hitter_id': 595978, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Austin Hedges', 'hitter_id': 595978, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU24" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="ET25" t="inlineStr">
         <is>
-          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ryan Vilade', 'hitter_id': 668723, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ryan Vilade', 'hitter_id': 668723, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU25" t="n">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="ET26" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'David Fry', 'hitter_id': 681807, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'David Fry', 'hitter_id': 681807, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU26" t="n">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="ET27" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Angel Genao', 'hitter_id': 694197, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Angel Genao', 'hitter_id': 694197, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU27" t="n">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:08 PM</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="ET28" t="inlineStr">
         <is>
-          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Petey Halpin', 'hitter_id': 690984, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:00 PM'}</t>
+          <t>{'era': 3.1, 'whip': 1.09, 'k_rate': 0.15096952908587258, 'bb_rate': 0.036011080332409975, 'hits_per_9': 8.55, 'hr_per_9': 1.1, 'batters_faced': 722, 'baa_vs_lhb_season': 0.23558897243107768, 'baa_vs_rhb_season': 0.2673611111111111, 'baa_vs_lhb_career': 0.25251076040172166, 'baa_vs_rhb_career': 0.2616568583069262, 'pitcher': 'Nick Martinez', 'pitcher_id': 607259, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/607259', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Nick+Martinez', 'hitter': 'Petey Halpin', 'hitter_id': 690984, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849816, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU28" t="n">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-17 01:23:04 AM</t>
+          <t>2026-10-17 10:12:04 AM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-17T01:23:04.643002-04:00</t>
+          <t>2026-10-17T10:12:04.635284-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:12:04 AM</t>
+          <t>2026-10-17 01:48:04 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:12:04.635284-04:00</t>
+          <t>2026-10-17T13:48:04.129672-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-17T18:56:10.219324-04:00</t>
+          <t>2026-10-17T20:41:27.936394-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:41:27 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-18 01:29:58 AM</t>
+          <t>2026-10-18 10:30:55 AM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-18T01:29:58.169845-04:00</t>
+          <t>2026-10-18T10:30:55.488972-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2152,7 +2152,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-18 01:53:20 PM</t>
+          <t>2026-10-18 04:12:10 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-18T13:53:20.312876-04:00</t>
+          <t>2026-10-18T16:12:10.484318-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-18T16:12:10.484318-04:00</t>
+          <t>2026-10-18T18:49:05.810936-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:49:05 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2177,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="HE2" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="HE3" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="HE4" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="HE5" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="HE6" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="HE7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="HE8" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="HE9" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="HE10" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="HE11" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="HE12" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="HE13" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="HE14" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="HE15" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="HE16" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="HE17" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="HE18" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-18T18:49:05.810936-04:00</t>
+          <t>2026-10-18T20:51:41.040942-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="HE19" t="inlineStr">
         <is>
-          <t>2026-10-18 06:49:05 PM</t>
+          <t>2026-10-18 08:51:41 PM</t>
         </is>
       </c>
     </row>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -1549,15 +1549,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Chandler+Simpson</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1838,57 +1852,113 @@
       <c r="DK2" t="n">
         <v>0.3067846607669616</v>
       </c>
-      <c r="DL2" t="inlineStr"/>
+      <c r="DL2" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO2" t="inlineStr"/>
-      <c r="DP2" t="inlineStr"/>
-      <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
-      <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="inlineStr"/>
-      <c r="DV2" t="inlineStr"/>
-      <c r="DW2" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX2" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY2" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
-      <c r="EH2" t="inlineStr"/>
-      <c r="EI2" t="inlineStr"/>
-      <c r="EJ2" t="inlineStr"/>
-      <c r="EK2" t="inlineStr"/>
-      <c r="EL2" t="inlineStr"/>
-      <c r="EM2" t="inlineStr"/>
-      <c r="EN2" t="inlineStr"/>
-      <c r="EO2" t="inlineStr"/>
-      <c r="EP2" t="inlineStr"/>
+      <c r="DZ2" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ2" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER2" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES2" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Chandler Simpson', 'hitter_id': 802415, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Chandler Simpson', 'hitter_id': 802415, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU2" t="n">
@@ -1898,10 +1968,10 @@
         <v>3.32</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX2" t="n">
-        <v>3.097581699346406</v>
+        <v>3.16356950423727</v>
       </c>
       <c r="EY2" t="n">
         <v>0.44</v>
@@ -1909,8 +1979,12 @@
       <c r="EZ2" t="n">
         <v>1</v>
       </c>
-      <c r="FA2" t="inlineStr"/>
-      <c r="FB2" t="inlineStr"/>
+      <c r="FA2" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC2" t="n">
         <v>0.3032418421509971</v>
       </c>
@@ -1930,13 +2004,13 @@
         <v>0.3174444583446197</v>
       </c>
       <c r="FI2" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.3174444583446197</v>
+        <v>0.3063190451862767</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.3174444583446197</v>
+        <v>0.3063190451862767</v>
       </c>
       <c r="FL2" t="n">
         <v>0.3064798598949212</v>
@@ -1945,28 +2019,28 @@
         <v>0.3064798598949212</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.3174444583446197</v>
+        <v>0.3063190451862767</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.01096459844969844</v>
+        <v>-0.0001608147086444855</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.01096459844969844</v>
+        <v>0.0001608147086444855</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.9833101447272262</v>
+        <v>0.9690615899183834</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.6259291813176171</v>
+        <v>0.6205610595868351</v>
       </c>
       <c r="FS2" t="n">
-        <v>-167</v>
+        <v>-164</v>
       </c>
       <c r="FT2" t="n">
         <v>0.3892156862745098</v>
       </c>
       <c r="FU2" t="n">
-        <v>88.88502412120434</v>
+        <v>86.51026498639723</v>
       </c>
       <c r="FV2" t="n">
         <v>91.66666666666667</v>
@@ -1975,7 +2049,7 @@
         <v>77.54421986622087</v>
       </c>
       <c r="FX2" t="n">
-        <v>8.131808278867132</v>
+        <v>13.6307920197725</v>
       </c>
       <c r="FY2" t="n">
         <v>100</v>
@@ -1993,7 +2067,7 @@
         <v>84.36696900982616</v>
       </c>
       <c r="GD2" t="n">
-        <v>59.01768794648836</v>
+        <v>58.28608621488662</v>
       </c>
       <c r="GE2" t="inlineStr">
         <is>
@@ -2001,7 +2075,7 @@
         </is>
       </c>
       <c r="GF2" t="n">
-        <v>76.55579763130017</v>
+        <v>76.61322761458479</v>
       </c>
       <c r="GG2" t="n">
         <v>71.09504535147393</v>
@@ -2012,10 +2086,10 @@
         </is>
       </c>
       <c r="GI2" t="n">
-        <v>73.46662234541684</v>
+        <v>70.73370041124561</v>
       </c>
       <c r="GJ2" t="n">
-        <v>60.93380162330581</v>
+        <v>61.36782549087845</v>
       </c>
       <c r="GK2" t="inlineStr">
         <is>
@@ -2051,12 +2125,12 @@
       </c>
       <c r="GS2" t="inlineStr">
         <is>
-          <t>['No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT2" t="inlineStr">
         <is>
-          <t>Chandler Simpson projects for 0.98 hits with a 62.6% 1+ hit probability.</t>
+          <t>Chandler Simpson projects for 0.97 hits with a 62.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU2" t="inlineStr">
@@ -2074,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2094,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2177,15 +2251,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Yandy+D%C3%ADaz</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2466,57 +2554,113 @@
       <c r="DK3" t="n">
         <v>0.2870036101083033</v>
       </c>
-      <c r="DL3" t="inlineStr"/>
+      <c r="DL3" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM3" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
-      <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX3" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY3" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
-      <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
+      <c r="DZ3" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI3" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ3" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER3" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES3" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Yandy Díaz', 'hitter_id': 650490, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Yandy Díaz', 'hitter_id': 650490, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU3" t="n">
@@ -2526,10 +2670,10 @@
         <v>3.32</v>
       </c>
       <c r="EW3" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX3" t="n">
-        <v>2.971545189504373</v>
+        <v>3.034848037732969</v>
       </c>
       <c r="EY3" t="n">
         <v>0.44</v>
@@ -2537,8 +2681,12 @@
       <c r="EZ3" t="n">
         <v>1</v>
       </c>
-      <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="inlineStr"/>
+      <c r="FA3" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>0.2372881355932203</v>
+      </c>
       <c r="FC3" t="n">
         <v>0.3009291349533977</v>
       </c>
@@ -2558,13 +2706,13 @@
         <v>0.3210197622517778</v>
       </c>
       <c r="FI3" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.3210197622517778</v>
+        <v>0.3097690461244014</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.3210197622517778</v>
+        <v>0.3097690461244014</v>
       </c>
       <c r="FL3" t="n">
         <v>0.2931596091205212</v>
@@ -2573,28 +2721,28 @@
         <v>0.2931596091205212</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.3210197622517778</v>
+        <v>0.3097690461244014</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.02786015313125656</v>
+        <v>0.01660943700388023</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.02786015313125656</v>
+        <v>0.01660943700388023</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.9539247302551078</v>
+        <v>0.9401019817810533</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.6147738560498925</v>
+        <v>0.6094119995326066</v>
       </c>
       <c r="FS3" t="n">
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="FT3" t="n">
         <v>0.4857598039215686</v>
       </c>
       <c r="FU3" t="n">
-        <v>83.98745504251795</v>
+        <v>81.68366363017553</v>
       </c>
       <c r="FV3" t="n">
         <v>100</v>
@@ -2603,7 +2751,7 @@
         <v>68.47419810325809</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>2.904003144414117</v>
       </c>
       <c r="FY3" t="n">
         <v>100</v>
@@ -2621,7 +2769,7 @@
         <v>88.12358276643991</v>
       </c>
       <c r="GD3" t="n">
-        <v>55.38967924130324</v>
+        <v>54.65807750970151</v>
       </c>
       <c r="GE3" t="inlineStr">
         <is>
@@ -2629,7 +2777,7 @@
         </is>
       </c>
       <c r="GF3" t="n">
-        <v>73.94530207650475</v>
+        <v>73.66072509301999</v>
       </c>
       <c r="GG3" t="n">
         <v>77.67853741496599</v>
@@ -2640,10 +2788,10 @@
         </is>
       </c>
       <c r="GI3" t="n">
-        <v>77.61055428749799</v>
+        <v>74.78599838674026</v>
       </c>
       <c r="GJ3" t="n">
-        <v>59.36997128445022</v>
+        <v>59.32467655037482</v>
       </c>
       <c r="GK3" t="inlineStr">
         <is>
@@ -2679,12 +2827,12 @@
       </c>
       <c r="GS3" t="inlineStr">
         <is>
-          <t>['No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Moderate matchup caution (55 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT3" t="inlineStr">
         <is>
-          <t>Yandy Díaz projects for 0.95 hits with a 61.5% 1+ hit probability.</t>
+          <t>Yandy Díaz projects for 0.94 hits with a 60.9% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU3" t="inlineStr">
@@ -2702,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2722,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2805,15 +2953,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Junior+Caminero</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3094,57 +3256,113 @@
       <c r="DK4" t="n">
         <v>0.2645654250238778</v>
       </c>
-      <c r="DL4" t="inlineStr"/>
+      <c r="DL4" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM4" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
-      <c r="DR4" t="inlineStr"/>
-      <c r="DS4" t="inlineStr"/>
-      <c r="DT4" t="inlineStr"/>
-      <c r="DU4" t="inlineStr"/>
-      <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX4" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY4" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
-      <c r="EF4" t="inlineStr"/>
-      <c r="EG4" t="inlineStr"/>
-      <c r="EH4" t="inlineStr"/>
-      <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="inlineStr"/>
-      <c r="EK4" t="inlineStr"/>
-      <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr"/>
-      <c r="EO4" t="inlineStr"/>
-      <c r="EP4" t="inlineStr"/>
+      <c r="DZ4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ4" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER4" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES4" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Junior Caminero', 'hitter_id': 691406, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Junior Caminero', 'hitter_id': 691406, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU4" t="n">
@@ -3154,10 +3372,10 @@
         <v>3.32</v>
       </c>
       <c r="EW4" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX4" t="n">
-        <v>2.913276353276354</v>
+        <v>2.975337900073887</v>
       </c>
       <c r="EY4" t="n">
         <v>0.44</v>
@@ -3165,8 +3383,12 @@
       <c r="EZ4" t="n">
         <v>1</v>
       </c>
-      <c r="FA4" t="inlineStr"/>
-      <c r="FB4" t="inlineStr"/>
+      <c r="FA4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
       <c r="FC4" t="n">
         <v>0.2701373965875051</v>
       </c>
@@ -3186,13 +3408,13 @@
         <v>0.2694910111921755</v>
       </c>
       <c r="FI4" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2694910111921755</v>
+        <v>0.2600462130135986</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2694910111921755</v>
+        <v>0.2600462130135986</v>
       </c>
       <c r="FL4" t="n">
         <v>0.275974025974026</v>
@@ -3201,28 +3423,28 @@
         <v>0.275974025974026</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.2694910111921755</v>
+        <v>0.2600462130135986</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0.006483014781850482</v>
+        <v>-0.01592781296042733</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.006483014781850482</v>
+        <v>0.01592781296042733</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.785101790326698</v>
+        <v>0.7737253533500473</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.5439267244249093</v>
+        <v>0.538708610052633</v>
       </c>
       <c r="FS4" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="FT4" t="n">
         <v>0.2684781783681214</v>
       </c>
       <c r="FU4" t="n">
-        <v>55.850298387783</v>
+        <v>53.95422555834121</v>
       </c>
       <c r="FV4" t="n">
         <v>91.66666666666667</v>
@@ -3249,7 +3471,7 @@
         <v>87.93272864701436</v>
       </c>
       <c r="GD4" t="n">
-        <v>48.80725990885146</v>
+        <v>48.07565817724973</v>
       </c>
       <c r="GE4" t="inlineStr">
         <is>
@@ -3257,7 +3479,7 @@
         </is>
       </c>
       <c r="GF4" t="n">
-        <v>55.79960961262039</v>
+        <v>55.23078776378787</v>
       </c>
       <c r="GG4" t="n">
         <v>77.64990929705215</v>
@@ -3268,10 +3490,10 @@
         </is>
       </c>
       <c r="GI4" t="n">
-        <v>65.43971947510001</v>
+        <v>62.99741980629155</v>
       </c>
       <c r="GJ4" t="n">
-        <v>49.05676580088127</v>
+        <v>48.51425662841172</v>
       </c>
       <c r="GK4" t="inlineStr">
         <is>
@@ -3307,12 +3529,12 @@
       </c>
       <c r="GS4" t="inlineStr">
         <is>
-          <t>['Moderate matchup caution (49 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is slightly below season AVG by -0.016', 'Moderate matchup caution (48 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT4" t="inlineStr">
         <is>
-          <t>Junior Caminero projects for 0.79 hits with a 54.4% 1+ hit probability.</t>
+          <t>Junior Caminero projects for 0.77 hits with a 53.9% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU4" t="inlineStr">
@@ -3330,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3350,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3433,15 +3655,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Liam+Hicks</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3722,57 +3958,113 @@
       <c r="DK5" t="n">
         <v>0.2865853658536585</v>
       </c>
-      <c r="DL5" t="inlineStr"/>
+      <c r="DL5" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM5" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
-      <c r="DT5" t="inlineStr"/>
-      <c r="DU5" t="inlineStr"/>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX5" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY5" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
-      <c r="EB5" t="inlineStr"/>
-      <c r="EC5" t="inlineStr"/>
-      <c r="ED5" t="inlineStr"/>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
-      <c r="EH5" t="inlineStr"/>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
-      <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
-      <c r="EO5" t="inlineStr"/>
-      <c r="EP5" t="inlineStr"/>
+      <c r="DZ5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ5" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER5" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES5" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Liam Hicks', 'hitter_id': 689414, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Liam Hicks', 'hitter_id': 689414, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU5" t="n">
@@ -3782,10 +4074,10 @@
         <v>3.32</v>
       </c>
       <c r="EW5" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.870541516245487</v>
+        <v>2.93169268250693</v>
       </c>
       <c r="EY5" t="n">
         <v>0.44</v>
@@ -3793,8 +4085,12 @@
       <c r="EZ5" t="n">
         <v>1</v>
       </c>
-      <c r="FA5" t="inlineStr"/>
-      <c r="FB5" t="inlineStr"/>
+      <c r="FA5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC5" t="n">
         <v>0.2782293216103052</v>
       </c>
@@ -3814,13 +4110,13 @@
         <v>0.2965043698767501</v>
       </c>
       <c r="FI5" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2965043698767501</v>
+        <v>0.2861128398581291</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2965043698767501</v>
+        <v>0.2861128398581291</v>
       </c>
       <c r="FL5" t="n">
         <v>0.2839248434237996</v>
@@ -3829,28 +4125,28 @@
         <v>0.2839248434237996</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2965043698767501</v>
+        <v>0.2861128398581291</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.01257952645295046</v>
+        <v>0.002187996434329542</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.01257952645295046</v>
+        <v>0.002187996434329542</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.8511281034794189</v>
+        <v>0.8387949189833542</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.5730669644575481</v>
+        <v>0.5677689168191096</v>
       </c>
       <c r="FS5" t="n">
-        <v>-134</v>
+        <v>-131</v>
       </c>
       <c r="FT5" t="n">
         <v>0.3928526249209361</v>
       </c>
       <c r="FU5" t="n">
-        <v>66.85468391323647</v>
+        <v>64.79915316389236</v>
       </c>
       <c r="FV5" t="n">
         <v>66.66666666666664</v>
@@ -3877,7 +4173,7 @@
         <v>65.51965230536658</v>
       </c>
       <c r="GD5" t="n">
-        <v>54.24324107471408</v>
+        <v>53.51163934311234</v>
       </c>
       <c r="GE5" t="inlineStr">
         <is>
@@ -3885,7 +4181,7 @@
         </is>
       </c>
       <c r="GF5" t="n">
-        <v>59.8129354585982</v>
+        <v>59.19627623379496</v>
       </c>
       <c r="GG5" t="n">
         <v>58.91789906531719</v>
@@ -3896,10 +4192,10 @@
         </is>
       </c>
       <c r="GI5" t="n">
-        <v>68.6582447078716</v>
+        <v>65.98011866977782</v>
       </c>
       <c r="GJ5" t="n">
-        <v>48.11826741077922</v>
+        <v>47.55616297772286</v>
       </c>
       <c r="GK5" t="inlineStr">
         <is>
@@ -3935,12 +4231,12 @@
       </c>
       <c r="GS5" t="inlineStr">
         <is>
-          <t>['Moderate matchup caution (54 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Moderate matchup caution (54 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT5" t="inlineStr">
         <is>
-          <t>Liam Hicks projects for 0.85 hits with a 57.3% 1+ hit probability.</t>
+          <t>Liam Hicks projects for 0.84 hits with a 56.8% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU5" t="inlineStr">
@@ -3958,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -3978,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4660,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4680,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -4707,26 +5003,26 @@
         <v>849815</v>
       </c>
       <c r="D7" t="n">
-        <v>666018</v>
+        <v>666176</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -4742,12 +5038,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P7" t="b">
@@ -4755,23 +5051,37 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/666018</t>
+          <t>https://www.mlb.com/player/666176</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jonathan+Aranda</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jo+Adell</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>642547</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/642547</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4782,103 +5092,103 @@
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
-        <v>1078</v>
+        <v>1534</v>
       </c>
       <c r="AB7" t="n">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2838589981447124</v>
+        <v>0.2301173402868318</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6721311475409836</v>
+        <v>0.564625850340136</v>
       </c>
       <c r="AE7" t="n">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="AF7" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="AG7" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.2741379310344828</v>
+        <v>0.2404643449419569</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.6851851851851852</v>
+        <v>0.6049382716049383</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
         <v>7</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.25</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AN7" t="n">
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AR7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AV7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AZ7" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2277227722772277</v>
+        <v>0.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="BD7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BE7" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.29</v>
+        <v>0.2487562189054726</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.675</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="BH7" t="n">
         <v>3</v>
@@ -4887,22 +5197,22 @@
         <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BM7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="BO7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
@@ -4910,88 +5220,88 @@
         </is>
       </c>
       <c r="BQ7" t="n">
-        <v>813</v>
+        <v>1043</v>
       </c>
       <c r="BR7" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.2871150705553488</v>
+        <v>0.2136935196394057</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.6828753238347887</v>
+        <v>0.5746207174716275</v>
       </c>
       <c r="BU7" t="n">
-        <v>416</v>
+        <v>304</v>
       </c>
       <c r="BV7" t="n">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.2836538461538461</v>
+        <v>0.2138157894736842</v>
       </c>
       <c r="BX7" t="n">
         <v>100</v>
       </c>
       <c r="BY7" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.2871150705553488</v>
+        <v>0.2136935196394057</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.2544335740789823</v>
+        <v>0.2863250197895325</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.2502737001396932</v>
+        <v>0.2740800211088347</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.2610247172895132</v>
+        <v>0.2711484552639577</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.2544335740789823</v>
+        <v>0.2863250197895325</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.2544335740789823</v>
+        <v>0.2863250197895325</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.2502737001396932</v>
+        <v>0.2740800211088347</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.25</v>
+        <v>0.3584905660377358</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2528301886792453</v>
+        <v>0.2816326530612245</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2446043165467626</v>
+        <v>0.2591943957968476</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.2778363029165116</v>
+        <v>0.2402701397295543</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.2752366108997246</v>
+        <v>0.2249548157115246</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.2875478099720465</v>
+        <v>0.2189529245293157</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.2778363029165116</v>
+        <v>0.2402701397295543</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.2778363029165116</v>
+        <v>0.2402701397295543</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.2752366108997246</v>
+        <v>0.2249548157115246</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.2836538461538461</v>
+        <v>0.2138157894736842</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.2939729397293973</v>
+        <v>0.2138063279002876</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.2829015544041451</v>
+        <v>0.2132209980557356</v>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -4999,123 +5309,179 @@
         </is>
       </c>
       <c r="CT7" t="n">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="CU7" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.25</v>
+        <v>0.3584905660377358</v>
       </c>
       <c r="CW7" t="n">
-        <v>416</v>
+        <v>304</v>
       </c>
       <c r="CX7" t="n">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2836538461538461</v>
+        <v>0.2138157894736842</v>
       </c>
       <c r="CZ7" t="n">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="DA7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2528301886792453</v>
+        <v>0.2816326530612245</v>
       </c>
       <c r="DC7" t="n">
-        <v>813</v>
+        <v>1043</v>
       </c>
       <c r="DD7" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2939729397293973</v>
+        <v>0.2138063279002876</v>
       </c>
       <c r="DF7" t="n">
-        <v>278</v>
+        <v>571</v>
       </c>
       <c r="DG7" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.2446043165467626</v>
+        <v>0.2591943957968476</v>
       </c>
       <c r="DI7" t="n">
-        <v>965</v>
+        <v>1543</v>
       </c>
       <c r="DJ7" t="n">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2829015544041451</v>
-      </c>
-      <c r="DL7" t="inlineStr"/>
+        <v>0.2132209980557356</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>4.42</v>
+      </c>
       <c r="DM7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
-      <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
-      <c r="DT7" t="inlineStr"/>
-      <c r="DU7" t="inlineStr"/>
-      <c r="DV7" t="inlineStr"/>
-      <c r="DW7" t="inlineStr"/>
+        <v>0.2136986301369863</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.0863013698630137</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>8.57396449704142</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>1.224852071005917</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>730</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>161</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>23</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>63</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>156</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>169</v>
+      </c>
       <c r="DX7" t="n">
-        <v>1</v>
+        <v>0.9526627218934911</v>
       </c>
       <c r="DY7" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="inlineStr"/>
-      <c r="EB7" t="inlineStr"/>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
-      <c r="EE7" t="inlineStr"/>
-      <c r="EF7" t="inlineStr"/>
-      <c r="EG7" t="inlineStr"/>
-      <c r="EH7" t="inlineStr"/>
-      <c r="EI7" t="inlineStr"/>
-      <c r="EJ7" t="inlineStr"/>
-      <c r="EK7" t="inlineStr"/>
-      <c r="EL7" t="inlineStr"/>
-      <c r="EM7" t="inlineStr"/>
-      <c r="EN7" t="inlineStr"/>
-      <c r="EO7" t="inlineStr"/>
-      <c r="EP7" t="inlineStr"/>
+      <c r="DZ7" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>297</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>158</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>2105</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.2099898063200815</v>
+      </c>
       <c r="EQ7" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ER7" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ES7" t="n">
-        <v>1</v>
+        <v>1.003802348336595</v>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Jonathan Aranda', 'hitter_id': 666018, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Jo Adell', 'hitter_id': 666176, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU7" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="EV7" t="n">
         <v>3.32</v>
       </c>
       <c r="EW7" t="n">
-        <v>3.32</v>
+        <v>3.502671341757233</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.882634730538922</v>
+        <v>3.200167907696382</v>
       </c>
       <c r="EY7" t="n">
         <v>0.44</v>
@@ -5123,79 +5489,83 @@
       <c r="EZ7" t="n">
         <v>1</v>
       </c>
-      <c r="FA7" t="inlineStr"/>
-      <c r="FB7" t="inlineStr"/>
+      <c r="FA7" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.2531645569620253</v>
+      </c>
       <c r="FC7" t="n">
-        <v>0.2702014861936581</v>
+        <v>0.2406806233932468</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2862497644549731</v>
+        <v>0.2137240870979753</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2862497644549731</v>
+        <v>0.2137240870979753</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2840909090909091</v>
+        <v>0.2696388888888889</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2799240822217338</v>
+        <v>0.2609514092401962</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2767660369571062</v>
+        <v>0.2362424039571162</v>
       </c>
       <c r="FI7" t="n">
-        <v>1</v>
+        <v>0.9935910096226218</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2767660369571062</v>
+        <v>0.2347283286634264</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2767660369571062</v>
+        <v>0.2347283286634264</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2741379310344828</v>
+        <v>0.2404643449419569</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2741379310344828</v>
+        <v>0.2404643449419569</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2767660369571062</v>
+        <v>0.2347283286634264</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.002628105922623469</v>
+        <v>-0.005736016278530487</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.002628105922623469</v>
+        <v>0.005736016278530487</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.7978153903661732</v>
+        <v>0.7511700644159058</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.5496883545022272</v>
+        <v>0.5281858233327983</v>
       </c>
       <c r="FS7" t="n">
-        <v>-122</v>
+        <v>-112</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.3102272727272727</v>
+        <v>0.29025</v>
       </c>
       <c r="FU7" t="n">
-        <v>57.96923172769552</v>
+        <v>50.1950107359843</v>
       </c>
       <c r="FV7" t="n">
-        <v>41.66666666666666</v>
+        <v>83.33333333333331</v>
       </c>
       <c r="FW7" t="n">
-        <v>63.00886503255813</v>
+        <v>19.81971743494453</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>16.68065897469846</v>
       </c>
       <c r="FY7" t="n">
-        <v>76.60427807486633</v>
+        <v>64.85294117647061</v>
       </c>
       <c r="FZ7" t="n">
-        <v>87.8</v>
+        <v>100</v>
       </c>
       <c r="GA7" t="n">
         <v>100</v>
@@ -5204,10 +5574,10 @@
         <v>19.8</v>
       </c>
       <c r="GC7" t="n">
-        <v>61.9501133786848</v>
+        <v>75.94860166288737</v>
       </c>
       <c r="GD7" t="n">
-        <v>53.20354601302326</v>
+        <v>36.04537456775624</v>
       </c>
       <c r="GE7" t="inlineStr">
         <is>
@@ -5215,21 +5585,21 @@
         </is>
       </c>
       <c r="GF7" t="n">
-        <v>48.427817388453</v>
+        <v>47.97389911474129</v>
       </c>
       <c r="GG7" t="n">
-        <v>70.33651700680272</v>
+        <v>75.85229024943311</v>
       </c>
       <c r="GH7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="GI7" t="n">
-        <v>65.71521953360588</v>
+        <v>62.68251602550238</v>
       </c>
       <c r="GJ7" t="n">
-        <v>45.82654171364366</v>
+        <v>45.34687767639649</v>
       </c>
       <c r="GK7" t="inlineStr">
         <is>
@@ -5260,22 +5630,22 @@
       </c>
       <c r="GR7" t="inlineStr">
         <is>
-          <t>['Real MLB split is favorable vs R-handed pitching']</t>
+          <t>['Strong recent 1+ hit consistency', 'Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS7" t="inlineStr">
         <is>
-          <t>['Moderate matchup caution (53 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is below preferred threshold at 0.235', 'Low matchup score (36)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda projects for 0.80 hits with a 55.0% 1+ hit probability.</t>
+          <t>Jo Adell projects for 0.75 hits with a 52.8% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU7" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|666018</t>
+          <t>2026-10-19|849815|666176</t>
         </is>
       </c>
       <c r="GV7" t="b">
@@ -5288,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5308,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5335,26 +5705,26 @@
         <v>849815</v>
       </c>
       <c r="D8" t="n">
-        <v>666176</v>
+        <v>666018</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -5370,48 +5740,48 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/666018</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jonathan+Aranda</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/player/666176</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jo+Adell</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>642547</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/642547</t>
+          <t>https://www.mlb.com/player/542888</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -5424,103 +5794,103 @@
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
-        <v>1534</v>
+        <v>1078</v>
       </c>
       <c r="AB8" t="n">
-        <v>353</v>
+        <v>306</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2301173402868318</v>
+        <v>0.2838589981447124</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.564625850340136</v>
+        <v>0.6721311475409836</v>
       </c>
       <c r="AE8" t="n">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="AF8" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="AG8" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2404643449419569</v>
+        <v>0.2741379310344828</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.6049382716049383</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.3125</v>
+        <v>0.375</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AV8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BA8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.27</v>
+        <v>0.2277227722772277</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.2487562189054726</v>
+        <v>0.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="BH8" t="n">
         <v>3</v>
@@ -5529,22 +5899,22 @@
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="BO8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
@@ -5552,88 +5922,88 @@
         </is>
       </c>
       <c r="BQ8" t="n">
-        <v>1043</v>
+        <v>813</v>
       </c>
       <c r="BR8" t="n">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.2136935196394057</v>
+        <v>0.2871150705553488</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.5746207174716275</v>
+        <v>0.6828753238347887</v>
       </c>
       <c r="BU8" t="n">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="BV8" t="n">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.2138157894736842</v>
+        <v>0.2836538461538461</v>
       </c>
       <c r="BX8" t="n">
         <v>100</v>
       </c>
       <c r="BY8" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.2136935196394057</v>
+        <v>0.2871150705553488</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2863250197895325</v>
+        <v>0.2544335740789823</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.2740800211088347</v>
+        <v>0.2502737001396932</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.2711484552639577</v>
+        <v>0.2610247172895132</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.2863250197895325</v>
+        <v>0.2544335740789823</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.2863250197895325</v>
+        <v>0.2544335740789823</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.2740800211088347</v>
+        <v>0.2502737001396932</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.3584905660377358</v>
+        <v>0.25</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.2816326530612245</v>
+        <v>0.2528301886792453</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.2591943957968476</v>
+        <v>0.2446043165467626</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.2402701397295543</v>
+        <v>0.2778363029165116</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.2249548157115246</v>
+        <v>0.2752366108997246</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.2189529245293157</v>
+        <v>0.2875478099720465</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.2402701397295543</v>
+        <v>0.2778363029165116</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.2402701397295543</v>
+        <v>0.2778363029165116</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.2249548157115246</v>
+        <v>0.2752366108997246</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.2138157894736842</v>
+        <v>0.2836538461538461</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.2138063279002876</v>
+        <v>0.2939729397293973</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.2132209980557356</v>
+        <v>0.2829015544041451</v>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -5641,124 +6011,124 @@
         </is>
       </c>
       <c r="CT8" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="CU8" t="n">
+        <v>41</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>416</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>118</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.2836538461538461</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>265</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.2528301886792453</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>813</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>239</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.2939729397293973</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>278</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>68</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.2446043165467626</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>965</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>273</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0.2829015544041451</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU8" t="n">
         <v>19</v>
       </c>
-      <c r="CV8" t="n">
-        <v>0.3584905660377358</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>304</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>65</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0.2138157894736842</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>245</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0.2816326530612245</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1043</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>223</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.2138063279002876</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>571</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>148</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.2591943957968476</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>1543</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>329</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>0.2132209980557356</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.2136986301369863</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.0863013698630137</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>8.57396449704142</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>1.224852071005917</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>730</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>161</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>23</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>63</v>
-      </c>
       <c r="DV8" t="n">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="DW8" t="n">
-        <v>169</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.9526627218934911</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY8" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="ED8" t="n">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="EE8" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="EF8" t="n">
-        <v>2105</v>
+        <v>685</v>
       </c>
       <c r="EG8" t="n">
-        <v>1962</v>
+        <v>1045</v>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
@@ -5766,54 +6136,54 @@
         </is>
       </c>
       <c r="EI8" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EQ8" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER8" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES8" t="n">
-        <v>1.003802348336595</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Jo Adell', 'hitter_id': 666176, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonathan Aranda', 'hitter_id': 666018, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU8" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="EV8" t="n">
         <v>3.32</v>
       </c>
       <c r="EW8" t="n">
-        <v>3.502671341757233</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX8" t="n">
-        <v>3.200167907696382</v>
+        <v>2.944043518630151</v>
       </c>
       <c r="EY8" t="n">
         <v>0.44</v>
@@ -5822,82 +6192,82 @@
         <v>1</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2406806233932468</v>
+        <v>0.2702014861936581</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.2137240870979753</v>
+        <v>0.2862497644549731</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2137240870979753</v>
+        <v>0.2862497644549731</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.2696388888888889</v>
+        <v>0.2840909090909091</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.2609514092401962</v>
+        <v>0.2799240822217338</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2362424039571162</v>
+        <v>0.2767660369571062</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.9935910096226218</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2347283286634264</v>
+        <v>0.2670662723891505</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.2347283286634264</v>
+        <v>0.2670662723891505</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.2404643449419569</v>
+        <v>0.2741379310344828</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.2404643449419569</v>
+        <v>0.2741379310344828</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.2347283286634264</v>
+        <v>0.2670662723891505</v>
       </c>
       <c r="FO8" t="n">
-        <v>-0.005736016278530487</v>
+        <v>-0.007071658645332213</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.005736016278530487</v>
+        <v>0.007071658645332213</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.7511700644159058</v>
+        <v>0.7862547282719932</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.5281858233327983</v>
+        <v>0.5444522456052867</v>
       </c>
       <c r="FS8" t="n">
-        <v>-112</v>
+        <v>-120</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.29025</v>
+        <v>0.3102272727272727</v>
       </c>
       <c r="FU8" t="n">
-        <v>50.1950107359843</v>
+        <v>56.04245471199885</v>
       </c>
       <c r="FV8" t="n">
-        <v>83.33333333333331</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="FW8" t="n">
-        <v>19.81971743494453</v>
+        <v>63.00886503255813</v>
       </c>
       <c r="FX8" t="n">
-        <v>16.68065897469846</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>64.85294117647061</v>
+        <v>76.60427807486633</v>
       </c>
       <c r="FZ8" t="n">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="GA8" t="n">
         <v>100</v>
@@ -5906,10 +6276,10 @@
         <v>19.8</v>
       </c>
       <c r="GC8" t="n">
-        <v>75.94860166288737</v>
+        <v>61.9501133786848</v>
       </c>
       <c r="GD8" t="n">
-        <v>36.04537456775624</v>
+        <v>52.47194428142152</v>
       </c>
       <c r="GE8" t="inlineStr">
         <is>
@@ -5917,21 +6287,21 @@
         </is>
       </c>
       <c r="GF8" t="n">
-        <v>47.97389911474129</v>
+        <v>47.849784283744</v>
       </c>
       <c r="GG8" t="n">
-        <v>75.85229024943311</v>
+        <v>70.33651700680272</v>
       </c>
       <c r="GH8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="GI8" t="n">
-        <v>62.68251602550238</v>
+        <v>63.21006990528872</v>
       </c>
       <c r="GJ8" t="n">
-        <v>45.34687767639649</v>
+        <v>45.2801509423151</v>
       </c>
       <c r="GK8" t="inlineStr">
         <is>
@@ -5962,22 +6332,22 @@
       </c>
       <c r="GR8" t="inlineStr">
         <is>
-          <t>['Strong recent 1+ hit consistency', 'Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
+          <t>['Real MLB split is favorable vs R-handed pitching']</t>
         </is>
       </c>
       <c r="GS8" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.235', 'Low matchup score (36)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Moderate matchup caution (52 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT8" t="inlineStr">
         <is>
-          <t>Jo Adell projects for 0.75 hits with a 52.8% 1+ hit probability.</t>
+          <t>Jonathan Aranda projects for 0.79 hits with a 54.4% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU8" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|666176</t>
+          <t>2026-10-19|849815|666018</t>
         </is>
       </c>
       <c r="GV8" t="b">
@@ -5990,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6010,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6692,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -6712,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -6739,26 +7109,26 @@
         <v>849815</v>
       </c>
       <c r="D10" t="n">
-        <v>677587</v>
+        <v>663743</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -6774,12 +7144,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P10" t="b">
@@ -6787,20 +7157,20 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/677587</t>
+          <t>https://www.mlb.com/player/663743</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Brayan+Rocchio</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Nick+Fortes</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>642547</v>
+        <v>542888</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -6810,12 +7180,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/642547</t>
+          <t>https://www.mlb.com/player/542888</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -6828,216 +7198,216 @@
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
-        <v>1261</v>
+        <v>824</v>
       </c>
       <c r="AB10" t="n">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2331482950039651</v>
+        <v>0.2390776699029126</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5206812652068127</v>
+        <v>0.4746835443037974</v>
       </c>
       <c r="AE10" t="n">
-        <v>534</v>
+        <v>298</v>
       </c>
       <c r="AF10" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AG10" t="n">
-        <v>592</v>
+        <v>323</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.252808988764045</v>
+        <v>0.2583892617449665</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.6049382716049383</v>
+        <v>0.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.375</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AV10" t="n">
         <v>50</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="AY10" t="n">
         <v>0.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.2788461538461539</v>
+        <v>0.2815533980582524</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BE10" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.2786069651741294</v>
+        <v>0.2574257425742574</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.555</v>
+        <v>0.465</v>
       </c>
       <c r="BH10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
         <v>1</v>
       </c>
       <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>41</v>
+      </c>
+      <c r="BO10" t="n">
         <v>8</v>
       </c>
-      <c r="BK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>13</v>
-      </c>
       <c r="BP10" t="inlineStr">
         <is>
           <t>real_mlb_statSplits</t>
         </is>
       </c>
       <c r="BQ10" t="n">
-        <v>874</v>
+        <v>400</v>
       </c>
       <c r="BR10" t="n">
-        <v>212</v>
+        <v>97</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.2564108277052573</v>
+        <v>0.2494720030823695</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.6414342780149636</v>
+        <v>0.6313427809450207</v>
       </c>
       <c r="BU10" t="n">
-        <v>353</v>
+        <v>151</v>
       </c>
       <c r="BV10" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.2719546742209632</v>
+        <v>0.2649006622516556</v>
       </c>
       <c r="BX10" t="n">
         <v>100</v>
       </c>
       <c r="BY10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.2564108277052573</v>
+        <v>0.2494720030823695</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2110728250548517</v>
+        <v>0.2589660132256786</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.2275802441610726</v>
+        <v>0.2472077603857077</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.2243402465049513</v>
+        <v>0.2414420097085744</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.2110728250548517</v>
+        <v>0.2589660132256786</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2110728250548517</v>
+        <v>0.2589660132256786</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.2275802441610726</v>
+        <v>0.2472077603857077</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.2154696132596685</v>
+        <v>0.2517006802721088</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.2118863049095607</v>
+        <v>0.2214765100671141</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.208133971291866</v>
+        <v>0.2389558232931727</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.242308120778943</v>
+        <v>0.2671040023117771</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2608978929334366</v>
+        <v>0.2558882820775461</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.2597402483255881</v>
+        <v>0.2506650640061526</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.242308120778943</v>
+        <v>0.2671040023117771</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.242308120778943</v>
+        <v>0.2671040023117771</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.2608978929334366</v>
+        <v>0.2558882820775461</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.2719546742209632</v>
+        <v>0.2649006622516556</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.2425629290617849</v>
+        <v>0.2425</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.2456709956709957</v>
+        <v>0.2269585253456221</v>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -7045,124 +7415,124 @@
         </is>
       </c>
       <c r="CT10" t="n">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="CU10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.2154696132596685</v>
+        <v>0.2517006802721088</v>
       </c>
       <c r="CW10" t="n">
-        <v>353</v>
+        <v>151</v>
       </c>
       <c r="CX10" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.2719546742209632</v>
+        <v>0.2649006622516556</v>
       </c>
       <c r="CZ10" t="n">
-        <v>387</v>
+        <v>298</v>
       </c>
       <c r="DA10" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.2118863049095607</v>
+        <v>0.2214765100671141</v>
       </c>
       <c r="DC10" t="n">
-        <v>874</v>
+        <v>400</v>
       </c>
       <c r="DD10" t="n">
-        <v>212</v>
+        <v>97</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2425629290617849</v>
+        <v>0.2425</v>
       </c>
       <c r="DF10" t="n">
-        <v>418</v>
+        <v>498</v>
       </c>
       <c r="DG10" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.208133971291866</v>
+        <v>0.2389558232931727</v>
       </c>
       <c r="DI10" t="n">
-        <v>924</v>
+        <v>868</v>
       </c>
       <c r="DJ10" t="n">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.2456709956709957</v>
+        <v>0.2269585253456221</v>
       </c>
       <c r="DL10" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="DM10" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0863013698630137</v>
+        <v>0.1233766233766234</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.57396449704142</v>
+        <v>7.641509433962264</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.224852071005917</v>
+        <v>1.018867924528302</v>
       </c>
       <c r="DR10" t="n">
-        <v>730</v>
+        <v>154</v>
       </c>
       <c r="DS10" t="n">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="DT10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="DU10" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="DV10" t="n">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="DW10" t="n">
-        <v>169</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.9526627218934911</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY10" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="ED10" t="n">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="EE10" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="EF10" t="n">
-        <v>2105</v>
+        <v>685</v>
       </c>
       <c r="EG10" t="n">
-        <v>1962</v>
+        <v>1045</v>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
@@ -7170,150 +7540,150 @@
         </is>
       </c>
       <c r="EI10" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EQ10" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER10" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES10" t="n">
-        <v>1.003802348336595</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Brayan Rocchio', 'hitter_id': 677587, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Nick Fortes', 'hitter_id': 663743, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU10" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="EV10" t="n">
         <v>3.32</v>
       </c>
       <c r="EW10" t="n">
-        <v>3.502671341757233</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX10" t="n">
-        <v>3.159504217058045</v>
+        <v>3.1282858919216</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="EZ10" t="n">
         <v>1</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2472030402124228</v>
+        <v>0.2524007134944941</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.2602967893341838</v>
+        <v>0.253329167874691</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2602967893341838</v>
+        <v>0.253329167874691</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.1929411764705882</v>
+        <v>0.3330375494071146</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2092197355931386</v>
+        <v>0.3088464986333284</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2442941701174799</v>
+        <v>0.2628394911335433</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.9935910096226218</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2427284911319474</v>
+        <v>0.2536278074631522</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.2427284911319474</v>
+        <v>0.2536278074631522</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.252808988764045</v>
+        <v>0.2583892617449665</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.252808988764045</v>
+        <v>0.2583892617449665</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.2427284911319474</v>
+        <v>0.2536278074631522</v>
       </c>
       <c r="FO10" t="n">
-        <v>-0.01008049763209753</v>
+        <v>-0.004761454281814237</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01008049763209753</v>
+        <v>0.004761454281814237</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.7669016913315241</v>
+        <v>0.793420291885987</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5355501496378317</v>
+        <v>0.5477048347841924</v>
       </c>
       <c r="FS10" t="n">
-        <v>-115</v>
+        <v>-121</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1882352941176471</v>
+        <v>0.3424090909090909</v>
       </c>
       <c r="FU10" t="n">
-        <v>52.816948555254</v>
+        <v>57.23671531433115</v>
       </c>
       <c r="FV10" t="n">
-        <v>49.99999999999999</v>
+        <v>66.66666666666664</v>
       </c>
       <c r="FW10" t="n">
-        <v>44.94754570897489</v>
+        <v>40.8658841660997</v>
       </c>
       <c r="FX10" t="n">
-        <v>13.29201808817041</v>
+        <v>10.69049099346664</v>
       </c>
       <c r="FY10" t="n">
-        <v>4.844290657439466</v>
+        <v>95.53475935828881</v>
       </c>
       <c r="FZ10" t="n">
-        <v>100</v>
+        <v>62.4</v>
       </c>
       <c r="GA10" t="n">
-        <v>100</v>
+        <v>87.80487804878049</v>
       </c>
       <c r="GB10" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="GC10" t="n">
-        <v>50.57445200302342</v>
+        <v>49.94897959183672</v>
       </c>
       <c r="GD10" t="n">
-        <v>46.09650587736838</v>
+        <v>43.61475193483815</v>
       </c>
       <c r="GE10" t="inlineStr">
         <is>
@@ -7321,10 +7691,10 @@
         </is>
       </c>
       <c r="GF10" t="n">
-        <v>40.93144586457944</v>
+        <v>52.37628410691737</v>
       </c>
       <c r="GG10" t="n">
-        <v>72.28616780045351</v>
+        <v>58.13166401194624</v>
       </c>
       <c r="GH10" t="inlineStr">
         <is>
@@ -7332,10 +7702,10 @@
         </is>
       </c>
       <c r="GI10" t="n">
-        <v>61.67805490372122</v>
+        <v>61.984890266766</v>
       </c>
       <c r="GJ10" t="n">
-        <v>43.73821502457901</v>
+        <v>43.92789482924989</v>
       </c>
       <c r="GK10" t="inlineStr">
         <is>
@@ -7366,22 +7736,22 @@
       </c>
       <c r="GR10" t="inlineStr">
         <is>
-          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
+          <t>['Strong recent 1+ hit consistency']</t>
         </is>
       </c>
       <c r="GS10" t="inlineStr">
         <is>
-          <t>['Model AVG is slightly below season AVG by -0.010', 'Model AVG is below preferred threshold at 0.243', 'Moderate matchup caution (46 matchup score)', 'Recent 15 AB form is cold at 0.176', 'Recent 30 AB form is below target at 0.200', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is below preferred threshold at 0.254', 'Low matchup score (44)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT10" t="inlineStr">
         <is>
-          <t>Brayan Rocchio projects for 0.77 hits with a 53.6% 1+ hit probability.</t>
+          <t>Nick Fortes projects for 0.79 hits with a 54.8% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU10" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|677587</t>
+          <t>2026-10-19|849815|663743</t>
         </is>
       </c>
       <c r="GV10" t="b">
@@ -7394,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7414,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7441,11 +7811,11 @@
         <v>849815</v>
       </c>
       <c r="D11" t="n">
-        <v>663993</v>
+        <v>677587</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7476,12 +7846,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P11" t="b">
@@ -7489,12 +7859,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/663993</t>
+          <t>https://www.mlb.com/player/677587</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Nathaniel+Lowe</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Brayan+Rocchio</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -7530,52 +7900,52 @@
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
-        <v>1407</v>
+        <v>1261</v>
       </c>
       <c r="AB11" t="n">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2473347547974414</v>
+        <v>0.2331482950039651</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5894988066825776</v>
+        <v>0.5206812652068127</v>
       </c>
       <c r="AE11" t="n">
-        <v>381</v>
+        <v>534</v>
       </c>
       <c r="AF11" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="n">
-        <v>429</v>
+        <v>592</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2519685039370079</v>
+        <v>0.252808988764045</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.5679012345679012</v>
+        <v>0.6049382716049383</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="AM11" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.4666666666666667</v>
@@ -7584,70 +7954,70 @@
         <v>30</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>104</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.2596153846153846</v>
+        <v>0.2788461538461539</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BD11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.25</v>
+        <v>0.2786069651741294</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.58</v>
+        <v>0.555</v>
       </c>
       <c r="BH11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BK11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BL11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BM11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BO11" t="n">
         <v>13</v>
@@ -7658,88 +8028,88 @@
         </is>
       </c>
       <c r="BQ11" t="n">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="BR11" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.271807624667595</v>
+        <v>0.2564108277052573</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.6628510636623495</v>
+        <v>0.6414342780149636</v>
       </c>
       <c r="BU11" t="n">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="BV11" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2719546742209632</v>
       </c>
       <c r="BX11" t="n">
         <v>100</v>
       </c>
       <c r="BY11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.271807624667595</v>
+        <v>0.2564108277052573</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.2527321438491696</v>
+        <v>0.2110728250548517</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.2445809534391143</v>
+        <v>0.2275802441610726</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.2421989937982897</v>
+        <v>0.2243402465049513</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.2527321438491696</v>
+        <v>0.2110728250548517</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.2527321438491696</v>
+        <v>0.2110728250548517</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.2445809534391143</v>
+        <v>0.2275802441610726</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2154696132596685</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2118863049095607</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.2505376344086022</v>
+        <v>0.208133971291866</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.2759711031160809</v>
+        <v>0.242308120778943</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.269369176657153</v>
+        <v>0.2608978929334366</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.2685364809674557</v>
+        <v>0.2597402483255881</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.2759711031160809</v>
+        <v>0.242308120778943</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.2759711031160809</v>
+        <v>0.242308120778943</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.269369176657153</v>
+        <v>0.2608978929334366</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2719546742209632</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.2567264573991032</v>
+        <v>0.2425629290617849</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.2669096800324018</v>
+        <v>0.2456709956709957</v>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -7747,58 +8117,58 @@
         </is>
       </c>
       <c r="CT11" t="n">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="CU11" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2154696132596685</v>
       </c>
       <c r="CW11" t="n">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="CX11" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2719546742209632</v>
       </c>
       <c r="CZ11" t="n">
-        <v>158</v>
+        <v>387</v>
       </c>
       <c r="DA11" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2118863049095607</v>
       </c>
       <c r="DC11" t="n">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="DD11" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2567264573991032</v>
+        <v>0.2425629290617849</v>
       </c>
       <c r="DF11" t="n">
-        <v>930</v>
+        <v>418</v>
       </c>
       <c r="DG11" t="n">
-        <v>233</v>
+        <v>87</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.2505376344086022</v>
+        <v>0.208133971291866</v>
       </c>
       <c r="DI11" t="n">
-        <v>2469</v>
+        <v>924</v>
       </c>
       <c r="DJ11" t="n">
-        <v>659</v>
+        <v>227</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.2669096800324018</v>
+        <v>0.2456709956709957</v>
       </c>
       <c r="DL11" t="n">
         <v>4.42</v>
@@ -7906,7 +8276,7 @@
       </c>
       <c r="ET11" t="inlineStr">
         <is>
-          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Nathaniel Lowe', 'hitter_id': 663993, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Brayan Rocchio', 'hitter_id': 677587, 'bats': 'S', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU11" t="n">
@@ -7919,88 +8289,88 @@
         <v>3.502671341757233</v>
       </c>
       <c r="EX11" t="n">
-        <v>3.110764058763417</v>
+        <v>3.159504217058045</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="EZ11" t="n">
         <v>1</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.2509493180459217</v>
+        <v>0.2472030402124228</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.2752842899292677</v>
+        <v>0.2602967893341838</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.2752842899292677</v>
+        <v>0.2602967893341838</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.2326556776556777</v>
+        <v>0.1929411764705882</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.2381437697727509</v>
+        <v>0.2092197355931386</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.2559448109217547</v>
+        <v>0.2442941701174799</v>
       </c>
       <c r="FI11" t="n">
         <v>0.9935910096226218</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.2543044630914173</v>
+        <v>0.2427284911319474</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.2543044630914173</v>
+        <v>0.2427284911319474</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.2519685039370079</v>
+        <v>0.252808988764045</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.2519685039370079</v>
+        <v>0.252808988764045</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.2543044630914173</v>
+        <v>0.2427284911319474</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.002335959154409428</v>
+        <v>-0.01008049763209753</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002335959154409428</v>
+        <v>0.01008049763209753</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.7910811837679089</v>
+        <v>0.7669016913315241</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.5466456291761976</v>
+        <v>0.5355501496378317</v>
       </c>
       <c r="FS11" t="n">
-        <v>-121</v>
+        <v>-115</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.2388034188034188</v>
+        <v>0.1882352941176471</v>
       </c>
       <c r="FU11" t="n">
-        <v>56.84686396131814</v>
+        <v>52.816948555254</v>
       </c>
       <c r="FV11" t="n">
-        <v>24.99999999999999</v>
+        <v>49.99999999999999</v>
       </c>
       <c r="FW11" t="n">
-        <v>54.00448509858531</v>
+        <v>44.94754570897489</v>
       </c>
       <c r="FX11" t="n">
-        <v>9.230338230284776</v>
+        <v>13.29201808817041</v>
       </c>
       <c r="FY11" t="n">
-        <v>34.59024635495224</v>
+        <v>4.844290657439466</v>
       </c>
       <c r="FZ11" t="n">
         <v>100</v>
@@ -8009,13 +8379,13 @@
         <v>100</v>
       </c>
       <c r="GB11" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="GC11" t="n">
-        <v>41.01095993953136</v>
+        <v>50.57445200302342</v>
       </c>
       <c r="GD11" t="n">
-        <v>49.71928163321255</v>
+        <v>46.09650587736838</v>
       </c>
       <c r="GE11" t="inlineStr">
         <is>
@@ -8023,10 +8393,10 @@
         </is>
       </c>
       <c r="GF11" t="n">
-        <v>39.78455782170611</v>
+        <v>40.93144586457944</v>
       </c>
       <c r="GG11" t="n">
-        <v>70.61164399092971</v>
+        <v>72.28616780045351</v>
       </c>
       <c r="GH11" t="inlineStr">
         <is>
@@ -8034,10 +8404,10 @@
         </is>
       </c>
       <c r="GI11" t="n">
-        <v>63.77940892701677</v>
+        <v>61.67805490372122</v>
       </c>
       <c r="GJ11" t="n">
-        <v>43.49216347909624</v>
+        <v>43.73821502457901</v>
       </c>
       <c r="GK11" t="inlineStr">
         <is>
@@ -8068,22 +8438,22 @@
       </c>
       <c r="GR11" t="inlineStr">
         <is>
-          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.269 season BAA vs this batter hand']</t>
+          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS11" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.254', 'Moderate matchup caution (50 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is slightly below season AVG by -0.010', 'Model AVG is below preferred threshold at 0.243', 'Moderate matchup caution (46 matchup score)', 'Recent 15 AB form is cold at 0.176', 'Recent 30 AB form is below target at 0.200', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe projects for 0.79 hits with a 54.7% 1+ hit probability.</t>
+          <t>Brayan Rocchio projects for 0.77 hits with a 53.6% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU11" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|663993</t>
+          <t>2026-10-19|849815|677587</t>
         </is>
       </c>
       <c r="GV11" t="b">
@@ -8096,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8116,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8143,11 +8513,11 @@
         <v>849815</v>
       </c>
       <c r="D12" t="n">
-        <v>663743</v>
+        <v>676356</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8178,7 +8548,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -8191,23 +8561,37 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/663743</t>
+          <t>https://www.mlb.com/player/676356</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Nick+Fortes</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jonny+DeLuca</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8218,127 +8602,127 @@
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
-        <v>824</v>
+        <v>739</v>
       </c>
       <c r="AB12" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2390776699029126</v>
+        <v>0.2489851150202977</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4746835443037974</v>
+        <v>0.5397489539748954</v>
       </c>
       <c r="AE12" t="n">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="AF12" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AG12" t="n">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2583892617449665</v>
+        <v>0.2657142857142857</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.5</v>
+        <v>0.5493827160493827</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.8</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AR12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AV12" t="n">
         <v>50</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="AZ12" t="n">
         <v>103</v>
       </c>
       <c r="BA12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.2815533980582524</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BD12" t="n">
         <v>202</v>
       </c>
       <c r="BE12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.2574257425742574</v>
+        <v>0.2623762376237624</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.465</v>
+        <v>0.53</v>
       </c>
       <c r="BH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK12" t="n">
         <v>4</v>
       </c>
-      <c r="BI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>3</v>
-      </c>
       <c r="BL12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BM12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BO12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
@@ -8346,88 +8730,88 @@
         </is>
       </c>
       <c r="BQ12" t="n">
-        <v>400</v>
+        <v>479</v>
       </c>
       <c r="BR12" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.2494720030823695</v>
+        <v>0.2598798967414352</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.6313427809450207</v>
+        <v>0.6463754730103703</v>
       </c>
       <c r="BU12" t="n">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="BV12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.2649006622516556</v>
+        <v>0.2673267326732673</v>
       </c>
       <c r="BX12" t="n">
         <v>100</v>
       </c>
       <c r="BY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.2494720030823695</v>
+        <v>0.2598798967414352</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2589660132256786</v>
+        <v>0.2588829884640101</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.2472077603857077</v>
+        <v>0.2558441197337791</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.2414420097085744</v>
+        <v>0.2534238225694425</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.2589660132256786</v>
+        <v>0.2588829884640101</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.2589660132256786</v>
+        <v>0.2588829884640101</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.2472077603857077</v>
+        <v>0.2558441197337791</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.2517006802721088</v>
+        <v>0.2635135135135135</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.2214765100671141</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.2389558232931727</v>
+        <v>0.2431506849315068</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.2671040023117771</v>
+        <v>0.2649099225560764</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.2558882820775461</v>
+        <v>0.2622728494319831</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.2506650640061526</v>
+        <v>0.2602543478737843</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.2671040023117771</v>
+        <v>0.2649099225560764</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.2671040023117771</v>
+        <v>0.2649099225560764</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.2558882820775461</v>
+        <v>0.2622728494319831</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.2649006622516556</v>
+        <v>0.2673267326732673</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.2425</v>
+        <v>0.2546972860125261</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.2269585253456221</v>
+        <v>0.2535787321063395</v>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -8435,110 +8819,166 @@
         </is>
       </c>
       <c r="CT12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="CU12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.2517006802721088</v>
+        <v>0.2635135135135135</v>
       </c>
       <c r="CW12" t="n">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="CX12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.2649006622516556</v>
+        <v>0.2673267326732673</v>
       </c>
       <c r="CZ12" t="n">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="DA12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.2214765100671141</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="DC12" t="n">
-        <v>400</v>
+        <v>479</v>
       </c>
       <c r="DD12" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2425</v>
+        <v>0.2546972860125261</v>
       </c>
       <c r="DF12" t="n">
-        <v>498</v>
+        <v>292</v>
       </c>
       <c r="DG12" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.2389558232931727</v>
+        <v>0.2431506849315068</v>
       </c>
       <c r="DI12" t="n">
-        <v>868</v>
+        <v>489</v>
       </c>
       <c r="DJ12" t="n">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.2269585253456221</v>
-      </c>
-      <c r="DL12" t="inlineStr"/>
+        <v>0.2535787321063395</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM12" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
-      <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
-      <c r="DT12" t="inlineStr"/>
-      <c r="DU12" t="inlineStr"/>
-      <c r="DV12" t="inlineStr"/>
-      <c r="DW12" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX12" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY12" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ12" t="inlineStr"/>
-      <c r="EA12" t="inlineStr"/>
-      <c r="EB12" t="inlineStr"/>
-      <c r="EC12" t="inlineStr"/>
-      <c r="ED12" t="inlineStr"/>
-      <c r="EE12" t="inlineStr"/>
-      <c r="EF12" t="inlineStr"/>
-      <c r="EG12" t="inlineStr"/>
-      <c r="EH12" t="inlineStr"/>
-      <c r="EI12" t="inlineStr"/>
-      <c r="EJ12" t="inlineStr"/>
-      <c r="EK12" t="inlineStr"/>
-      <c r="EL12" t="inlineStr"/>
-      <c r="EM12" t="inlineStr"/>
-      <c r="EN12" t="inlineStr"/>
-      <c r="EO12" t="inlineStr"/>
-      <c r="EP12" t="inlineStr"/>
+      <c r="DZ12" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ12" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER12" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES12" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET12" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Nick Fortes', 'hitter_id': 663743, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jonny DeLuca', 'hitter_id': 676356, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU12" t="n">
@@ -8548,10 +8988,10 @@
         <v>3.32</v>
       </c>
       <c r="EW12" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX12" t="n">
-        <v>3.063034055727555</v>
+        <v>3.187282424514215</v>
       </c>
       <c r="EY12" t="n">
         <v>0.44</v>
@@ -8559,91 +8999,95 @@
       <c r="EZ12" t="n">
         <v>1</v>
       </c>
-      <c r="FA12" t="inlineStr"/>
-      <c r="FB12" t="inlineStr"/>
+      <c r="FA12" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.2372881355932203</v>
+      </c>
       <c r="FC12" t="n">
-        <v>0.2524007134944941</v>
+        <v>0.2577393167285701</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.253329167874691</v>
+        <v>0.2617416057243933</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.253329167874691</v>
+        <v>0.2617416057243933</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.3330375494071146</v>
+        <v>0.2971176470588235</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.3088464986333284</v>
+        <v>0.2853041479597475</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.2628394911335433</v>
+        <v>0.263901673048929</v>
       </c>
       <c r="FI12" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.2628394911335433</v>
+        <v>0.2546527632989912</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.2628394911335433</v>
+        <v>0.2546527632989912</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.2583892617449665</v>
+        <v>0.2657142857142857</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.2583892617449665</v>
+        <v>0.2657142857142857</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.2628394911335433</v>
+        <v>0.2546527632989912</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.004450229388576865</v>
+        <v>-0.01106152241529451</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.004450229388576865</v>
+        <v>0.01106152241529451</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.8050863125321438</v>
+        <v>0.8116502768168532</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.5529506610663539</v>
+        <v>0.5558754672973789</v>
       </c>
       <c r="FS12" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.3424090909090909</v>
+        <v>0.302078431372549</v>
       </c>
       <c r="FU12" t="n">
-        <v>59.18105208869063</v>
+        <v>60.27504613614219</v>
       </c>
       <c r="FV12" t="n">
-        <v>66.66666666666664</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="FW12" t="n">
-        <v>40.8658841660997</v>
+        <v>46.98817455378545</v>
       </c>
       <c r="FX12" t="n">
-        <v>5.252837977296216</v>
+        <v>15.60686870951788</v>
       </c>
       <c r="FY12" t="n">
-        <v>95.53475935828881</v>
+        <v>71.81084198385237</v>
       </c>
       <c r="FZ12" t="n">
-        <v>62.4</v>
+        <v>53.9</v>
       </c>
       <c r="GA12" t="n">
-        <v>87.80487804878049</v>
+        <v>100</v>
       </c>
       <c r="GB12" t="n">
         <v>19.8</v>
       </c>
       <c r="GC12" t="n">
-        <v>49.94897959183672</v>
+        <v>44.14588057445199</v>
       </c>
       <c r="GD12" t="n">
-        <v>44.34635366643988</v>
+        <v>46.06366808991245</v>
       </c>
       <c r="GE12" t="inlineStr">
         <is>
@@ -8651,10 +9095,10 @@
         </is>
       </c>
       <c r="GF12" t="n">
-        <v>52.19831371696136</v>
+        <v>47.23628963292067</v>
       </c>
       <c r="GG12" t="n">
-        <v>58.13166401194624</v>
+        <v>58.1738820861678</v>
       </c>
       <c r="GH12" t="inlineStr">
         <is>
@@ -8662,10 +9106,10 @@
         </is>
       </c>
       <c r="GI12" t="n">
-        <v>64.23681985062795</v>
+        <v>59.79847705530977</v>
       </c>
       <c r="GJ12" t="n">
-        <v>43.45637788117936</v>
+        <v>43.6599698554475</v>
       </c>
       <c r="GK12" t="inlineStr">
         <is>
@@ -8696,22 +9140,22 @@
       </c>
       <c r="GR12" t="inlineStr">
         <is>
-          <t>['Strong recent 1+ hit consistency']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="GS12" t="inlineStr">
         <is>
-          <t>['Low matchup score (44)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is slightly below season AVG by -0.011', 'Model AVG is below preferred threshold at 0.255', 'Moderate matchup caution (46 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT12" t="inlineStr">
         <is>
-          <t>Nick Fortes projects for 0.81 hits with a 55.3% 1+ hit probability.</t>
+          <t>Jonny DeLuca projects for 0.81 hits with a 55.6% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU12" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|663743</t>
+          <t>2026-10-19|849815|676356</t>
         </is>
       </c>
       <c r="GV12" t="b">
@@ -8724,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -8744,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -8771,26 +9215,26 @@
         <v>849815</v>
       </c>
       <c r="D13" t="n">
-        <v>676356</v>
+        <v>663993</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -8806,36 +9250,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/663993</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Nathaniel+Lowe</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>642547</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/player/676356</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jonny+DeLuca</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/642547</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8846,112 +9304,112 @@
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
-        <v>739</v>
+        <v>1407</v>
       </c>
       <c r="AB13" t="n">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2489851150202977</v>
+        <v>0.2473347547974414</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5397489539748954</v>
+        <v>0.5894988066825776</v>
       </c>
       <c r="AE13" t="n">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="AF13" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AG13" t="n">
-        <v>370</v>
+        <v>429</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.2657142857142857</v>
+        <v>0.2519685039370079</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.5493827160493827</v>
+        <v>0.5679012345679012</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="AM13" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="AN13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>52</v>
+      </c>
+      <c r="AW13" t="n">
         <v>15</v>
       </c>
-      <c r="AO13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.2647058823529412</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14</v>
-      </c>
       <c r="AX13" t="n">
-        <v>0.28</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="AZ13" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.2718446601941747</v>
+        <v>0.2596153846153846</v>
       </c>
       <c r="BC13" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BE13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.2623762376237624</v>
+        <v>0.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="BH13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
         <v>4</v>
@@ -8963,10 +9421,10 @@
         <v>8</v>
       </c>
       <c r="BN13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BO13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
@@ -8974,88 +9432,88 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>479</v>
+        <v>892</v>
       </c>
       <c r="BR13" t="n">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.2598798967414352</v>
+        <v>0.271807624667595</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.6463754730103703</v>
+        <v>0.6628510636623495</v>
       </c>
       <c r="BU13" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="BV13" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.2673267326732673</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="BX13" t="n">
         <v>100</v>
       </c>
       <c r="BY13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.2598798967414352</v>
+        <v>0.271807624667595</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.2588829884640101</v>
+        <v>0.2527321438491696</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.2558441197337791</v>
+        <v>0.2445809534391143</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.2534238225694425</v>
+        <v>0.2421989937982897</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.2588829884640101</v>
+        <v>0.2527321438491696</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.2588829884640101</v>
+        <v>0.2527321438491696</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.2558441197337791</v>
+        <v>0.2445809534391143</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.2635135135135135</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.2384615384615385</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.2431506849315068</v>
+        <v>0.2505376344086022</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.2649099225560764</v>
+        <v>0.2759711031160809</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.2622728494319831</v>
+        <v>0.269369176657153</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.2602543478737843</v>
+        <v>0.2685364809674557</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.2649099225560764</v>
+        <v>0.2759711031160809</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.2649099225560764</v>
+        <v>0.2759711031160809</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.2622728494319831</v>
+        <v>0.269369176657153</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.2673267326732673</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.2546972860125261</v>
+        <v>0.2567264573991032</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.2535787321063395</v>
+        <v>0.2669096800324018</v>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -9063,123 +9521,179 @@
         </is>
       </c>
       <c r="CT13" t="n">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="CU13" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.2635135135135135</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CW13" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="CX13" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.2673267326732673</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CZ13" t="n">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="DA13" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.2384615384615385</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="DC13" t="n">
-        <v>479</v>
+        <v>892</v>
       </c>
       <c r="DD13" t="n">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2546972860125261</v>
+        <v>0.2567264573991032</v>
       </c>
       <c r="DF13" t="n">
-        <v>292</v>
+        <v>930</v>
       </c>
       <c r="DG13" t="n">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.2431506849315068</v>
+        <v>0.2505376344086022</v>
       </c>
       <c r="DI13" t="n">
-        <v>489</v>
+        <v>2469</v>
       </c>
       <c r="DJ13" t="n">
-        <v>124</v>
+        <v>659</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.2535787321063395</v>
-      </c>
-      <c r="DL13" t="inlineStr"/>
+        <v>0.2669096800324018</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>4.42</v>
+      </c>
       <c r="DM13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO13" t="inlineStr"/>
-      <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
-      <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
-      <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="inlineStr"/>
-      <c r="DV13" t="inlineStr"/>
-      <c r="DW13" t="inlineStr"/>
+        <v>0.2136986301369863</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.0863013698630137</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>8.57396449704142</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>1.224852071005917</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>730</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>161</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>23</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>63</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>156</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>169</v>
+      </c>
       <c r="DX13" t="n">
-        <v>1</v>
+        <v>0.9526627218934911</v>
       </c>
       <c r="DY13" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
-      <c r="ED13" t="inlineStr"/>
-      <c r="EE13" t="inlineStr"/>
-      <c r="EF13" t="inlineStr"/>
-      <c r="EG13" t="inlineStr"/>
-      <c r="EH13" t="inlineStr"/>
-      <c r="EI13" t="inlineStr"/>
-      <c r="EJ13" t="inlineStr"/>
-      <c r="EK13" t="inlineStr"/>
-      <c r="EL13" t="inlineStr"/>
-      <c r="EM13" t="inlineStr"/>
-      <c r="EN13" t="inlineStr"/>
-      <c r="EO13" t="inlineStr"/>
-      <c r="EP13" t="inlineStr"/>
+      <c r="DZ13" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>297</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>158</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>2105</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>1962</v>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.2099898063200815</v>
+      </c>
       <c r="EQ13" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ER13" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ES13" t="n">
-        <v>1</v>
+        <v>1.003802348336595</v>
       </c>
       <c r="ET13" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Jonny DeLuca', 'hitter_id': 676356, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Nathaniel Lowe', 'hitter_id': 663993, 'bats': 'L', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU13" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="EV13" t="n">
         <v>3.32</v>
       </c>
       <c r="EW13" t="n">
-        <v>3.32</v>
+        <v>3.502671341757233</v>
       </c>
       <c r="EX13" t="n">
-        <v>3.1208</v>
+        <v>3.110764058763417</v>
       </c>
       <c r="EY13" t="n">
         <v>0.44</v>
@@ -9187,79 +9701,83 @@
       <c r="EZ13" t="n">
         <v>1</v>
       </c>
-      <c r="FA13" t="inlineStr"/>
-      <c r="FB13" t="inlineStr"/>
+      <c r="FA13" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.2693602693602694</v>
+      </c>
       <c r="FC13" t="n">
-        <v>0.2577393167285701</v>
+        <v>0.2509493180459217</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.2617416057243933</v>
+        <v>0.2752842899292677</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.2617416057243933</v>
+        <v>0.2752842899292677</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.2971176470588235</v>
+        <v>0.2326556776556777</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.2853041479597475</v>
+        <v>0.2381437697727509</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.263901673048929</v>
+        <v>0.2559448109217547</v>
       </c>
       <c r="FI13" t="n">
-        <v>1</v>
+        <v>0.9935910096226218</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.263901673048929</v>
+        <v>0.2543044630914173</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.263901673048929</v>
+        <v>0.2543044630914173</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.2657142857142857</v>
+        <v>0.2519685039370079</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.2657142857142857</v>
+        <v>0.2519685039370079</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.263901673048929</v>
+        <v>0.2543044630914173</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.001812612665356705</v>
+        <v>0.002335959154409428</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001812612665356705</v>
+        <v>0.002335959154409428</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.8235843412510977</v>
+        <v>0.7910811837679089</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.5611441769954835</v>
+        <v>0.5466456291761976</v>
       </c>
       <c r="FS13" t="n">
-        <v>-128</v>
+        <v>-121</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.302078431372549</v>
+        <v>0.2388034188034188</v>
       </c>
       <c r="FU13" t="n">
-        <v>62.26405687518294</v>
+        <v>56.84686396131814</v>
       </c>
       <c r="FV13" t="n">
-        <v>41.66666666666666</v>
+        <v>24.99999999999999</v>
       </c>
       <c r="FW13" t="n">
-        <v>46.98817455378545</v>
+        <v>54.00448509858531</v>
       </c>
       <c r="FX13" t="n">
-        <v>10.06666666666667</v>
+        <v>9.230338230284776</v>
       </c>
       <c r="FY13" t="n">
-        <v>71.81084198385237</v>
+        <v>34.59024635495224</v>
       </c>
       <c r="FZ13" t="n">
-        <v>53.9</v>
+        <v>100</v>
       </c>
       <c r="GA13" t="n">
         <v>100</v>
@@ -9268,10 +9786,10 @@
         <v>19.8</v>
       </c>
       <c r="GC13" t="n">
-        <v>44.14588057445199</v>
+        <v>41.01095993953136</v>
       </c>
       <c r="GD13" t="n">
-        <v>46.79526982151418</v>
+        <v>49.71928163321255</v>
       </c>
       <c r="GE13" t="inlineStr">
         <is>
@@ -9279,10 +9797,10 @@
         </is>
       </c>
       <c r="GF13" t="n">
-        <v>47.05736456863372</v>
+        <v>39.78455782170611</v>
       </c>
       <c r="GG13" t="n">
-        <v>58.1738820861678</v>
+        <v>70.61164399092971</v>
       </c>
       <c r="GH13" t="inlineStr">
         <is>
@@ -9290,10 +9808,10 @@
         </is>
       </c>
       <c r="GI13" t="n">
-        <v>62.05916905688338</v>
+        <v>63.77940892701677</v>
       </c>
       <c r="GJ13" t="n">
-        <v>43.17472493003343</v>
+        <v>43.49216347909624</v>
       </c>
       <c r="GK13" t="inlineStr">
         <is>
@@ -9324,22 +9842,22 @@
       </c>
       <c r="GR13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.269 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS13" t="inlineStr">
         <is>
-          <t>['Moderate matchup caution (47 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is below preferred threshold at 0.254', 'Moderate matchup caution (50 matchup score)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca projects for 0.82 hits with a 56.1% 1+ hit probability.</t>
+          <t>Nathaniel Lowe projects for 0.79 hits with a 54.7% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU13" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|676356</t>
+          <t>2026-10-19|849815|663993</t>
         </is>
       </c>
       <c r="GV13" t="b">
@@ -9352,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9372,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10054,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10074,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10756,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -10776,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11458,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11478,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -11561,15 +12079,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Ben+Williamson</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -11850,57 +12382,113 @@
       <c r="DK17" t="n">
         <v>0.25</v>
       </c>
-      <c r="DL17" t="inlineStr"/>
+      <c r="DL17" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM17" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO17" t="inlineStr"/>
-      <c r="DP17" t="inlineStr"/>
-      <c r="DQ17" t="inlineStr"/>
-      <c r="DR17" t="inlineStr"/>
-      <c r="DS17" t="inlineStr"/>
-      <c r="DT17" t="inlineStr"/>
-      <c r="DU17" t="inlineStr"/>
-      <c r="DV17" t="inlineStr"/>
-      <c r="DW17" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX17" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY17" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ17" t="inlineStr"/>
-      <c r="EA17" t="inlineStr"/>
-      <c r="EB17" t="inlineStr"/>
-      <c r="EC17" t="inlineStr"/>
-      <c r="ED17" t="inlineStr"/>
-      <c r="EE17" t="inlineStr"/>
-      <c r="EF17" t="inlineStr"/>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
-      <c r="EI17" t="inlineStr"/>
-      <c r="EJ17" t="inlineStr"/>
-      <c r="EK17" t="inlineStr"/>
-      <c r="EL17" t="inlineStr"/>
-      <c r="EM17" t="inlineStr"/>
-      <c r="EN17" t="inlineStr"/>
-      <c r="EO17" t="inlineStr"/>
-      <c r="EP17" t="inlineStr"/>
+      <c r="DZ17" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI17" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ17" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER17" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES17" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET17" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Ben Williamson', 'hitter_id': 810938, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ben Williamson', 'hitter_id': 810938, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU17" t="n">
@@ -11910,10 +12498,10 @@
         <v>3.32</v>
       </c>
       <c r="EW17" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX17" t="n">
-        <v>3.02979020979021</v>
+        <v>3.094333852098684</v>
       </c>
       <c r="EY17" t="n">
         <v>0.44</v>
@@ -11921,8 +12509,12 @@
       <c r="EZ17" t="n">
         <v>1</v>
       </c>
-      <c r="FA17" t="inlineStr"/>
-      <c r="FB17" t="inlineStr"/>
+      <c r="FA17" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.2372881355932203</v>
+      </c>
       <c r="FC17" t="n">
         <v>0.2477965576329457</v>
       </c>
@@ -11942,13 +12534,13 @@
         <v>0.2536077379242086</v>
       </c>
       <c r="FI17" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.2536077379242086</v>
+        <v>0.244719597683006</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.2536077379242086</v>
+        <v>0.244719597683006</v>
       </c>
       <c r="FL17" t="n">
         <v>0.2375478927203065</v>
@@ -11957,28 +12549,28 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.2536077379242086</v>
+        <v>0.244719597683006</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.01605984520390208</v>
+        <v>0.007171704962699477</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.01605984520390208</v>
+        <v>0.007171704962699477</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.7683782414898086</v>
+        <v>0.7572441353824961</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.5362354270901303</v>
+        <v>0.5310429700844796</v>
       </c>
       <c r="FS17" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="FT17" t="n">
         <v>0.2916053921568627</v>
       </c>
       <c r="FU17" t="n">
-        <v>53.06304024830142</v>
+        <v>51.20735589708268</v>
       </c>
       <c r="FV17" t="n">
         <v>24.99999999999999</v>
@@ -11987,7 +12579,7 @@
         <v>40.88594545624942</v>
       </c>
       <c r="FX17" t="n">
-        <v>2.482517482517525</v>
+        <v>7.861154341556985</v>
       </c>
       <c r="FY17" t="n">
         <v>65.65023068050748</v>
@@ -12005,7 +12597,7 @@
         <v>39.62207105064247</v>
       </c>
       <c r="GD17" t="n">
-        <v>44.35437818249977</v>
+        <v>43.62277645089804</v>
       </c>
       <c r="GE17" t="inlineStr">
         <is>
@@ -12013,7 +12605,7 @@
         </is>
       </c>
       <c r="GF17" t="n">
-        <v>37.17225043142084</v>
+        <v>37.36855428632074</v>
       </c>
       <c r="GG17" t="n">
         <v>43.83316431613296</v>
@@ -12024,10 +12616,10 @@
         </is>
       </c>
       <c r="GI17" t="n">
-        <v>62.31744874910085</v>
+        <v>60.14646961193402</v>
       </c>
       <c r="GJ17" t="n">
-        <v>33.8330078983795</v>
+        <v>34.30471968238724</v>
       </c>
       <c r="GK17" t="inlineStr">
         <is>
@@ -12063,12 +12655,12 @@
       </c>
       <c r="GS17" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.254', 'Low matchup score (44)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is below preferred threshold at 0.245', 'Low matchup score (44)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT17" t="inlineStr">
         <is>
-          <t>Ben Williamson projects for 0.77 hits with a 53.6% 1+ hit probability.</t>
+          <t>Ben Williamson projects for 0.76 hits with a 53.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU17" t="inlineStr">
@@ -12086,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12106,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12788,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -12808,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -12891,15 +13483,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Richie+Palacios</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -13180,57 +13786,113 @@
       <c r="DK19" t="n">
         <v>0.2380952380952381</v>
       </c>
-      <c r="DL19" t="inlineStr"/>
+      <c r="DL19" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM19" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO19" t="inlineStr"/>
-      <c r="DP19" t="inlineStr"/>
-      <c r="DQ19" t="inlineStr"/>
-      <c r="DR19" t="inlineStr"/>
-      <c r="DS19" t="inlineStr"/>
-      <c r="DT19" t="inlineStr"/>
-      <c r="DU19" t="inlineStr"/>
-      <c r="DV19" t="inlineStr"/>
-      <c r="DW19" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX19" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY19" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ19" t="inlineStr"/>
-      <c r="EA19" t="inlineStr"/>
-      <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr"/>
-      <c r="EF19" t="inlineStr"/>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
-      <c r="EI19" t="inlineStr"/>
-      <c r="EJ19" t="inlineStr"/>
-      <c r="EK19" t="inlineStr"/>
-      <c r="EL19" t="inlineStr"/>
-      <c r="EM19" t="inlineStr"/>
-      <c r="EN19" t="inlineStr"/>
-      <c r="EO19" t="inlineStr"/>
-      <c r="EP19" t="inlineStr"/>
+      <c r="DZ19" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI19" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ19" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER19" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES19" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET19" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Richie Palacios', 'hitter_id': 680700, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Richie Palacios', 'hitter_id': 680700, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU19" t="n">
@@ -13240,10 +13902,10 @@
         <v>3.32</v>
       </c>
       <c r="EW19" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX19" t="n">
-        <v>2.870676691729324</v>
+        <v>2.931830737635056</v>
       </c>
       <c r="EY19" t="n">
         <v>0.44</v>
@@ -13251,8 +13913,12 @@
       <c r="EZ19" t="n">
         <v>1</v>
       </c>
-      <c r="FA19" t="inlineStr"/>
-      <c r="FB19" t="inlineStr"/>
+      <c r="FA19" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC19" t="n">
         <v>0.2408031790556335</v>
       </c>
@@ -13272,13 +13938,13 @@
         <v>0.2447023368890705</v>
       </c>
       <c r="FI19" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.2447023368890705</v>
+        <v>0.2361263024769421</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.2447023368890705</v>
+        <v>0.2361263024769421</v>
       </c>
       <c r="FL19" t="n">
         <v>0.2347826086956522</v>
@@ -13287,28 +13953,28 @@
         <v>0.2347826086956522</v>
       </c>
       <c r="FN19" t="n">
-        <v>0.2447023368890705</v>
+        <v>0.2361263024769421</v>
       </c>
       <c r="FO19" t="n">
-        <v>0.009919728193418326</v>
+        <v>0.001343693781289873</v>
       </c>
       <c r="FP19" t="n">
-        <v>0.009919728193418326</v>
+        <v>0.001343693781289873</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.7024612949191513</v>
+        <v>0.6922823515660115</v>
       </c>
       <c r="FR19" t="n">
-        <v>0.5046354361769293</v>
+        <v>0.4995673984668216</v>
       </c>
       <c r="FS19" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="FT19" t="n">
         <v>0.2505583126550869</v>
       </c>
       <c r="FU19" t="n">
-        <v>42.07688248652521</v>
+        <v>40.38039192766858</v>
       </c>
       <c r="FV19" t="n">
         <v>0</v>
@@ -13335,7 +14001,7 @@
         <v>20.50642479213907</v>
       </c>
       <c r="GD19" t="n">
-        <v>43.20042499758524</v>
+        <v>42.46882326598351</v>
       </c>
       <c r="GE19" t="inlineStr">
         <is>
@@ -13343,7 +14009,7 @@
         </is>
       </c>
       <c r="GF19" t="n">
-        <v>24.68370030333787</v>
+        <v>24.17475313568088</v>
       </c>
       <c r="GG19" t="n">
         <v>52.16396371882086</v>
@@ -13354,10 +14020,10 @@
         </is>
       </c>
       <c r="GI19" t="n">
-        <v>59.64679824141467</v>
+        <v>57.4237793191654</v>
       </c>
       <c r="GJ19" t="n">
-        <v>29.71436240258928</v>
+        <v>29.19846381597644</v>
       </c>
       <c r="GK19" t="inlineStr">
         <is>
@@ -13393,12 +14059,12 @@
       </c>
       <c r="GS19" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.245', 'Low matchup score (43)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Model AVG is below preferred threshold at 0.236', 'Low matchup score (42)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT19" t="inlineStr">
         <is>
-          <t>Richie Palacios projects for 0.70 hits with a 50.5% 1+ hit probability.</t>
+          <t>Richie Palacios projects for 0.69 hits with a 50.0% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU19" t="inlineStr">
@@ -13416,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -13436,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -13519,15 +14185,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Taylor+Walls</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -13808,57 +14488,113 @@
       <c r="DK20" t="n">
         <v>0.1943048576214405</v>
       </c>
-      <c r="DL20" t="inlineStr"/>
+      <c r="DL20" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM20" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO20" t="inlineStr"/>
-      <c r="DP20" t="inlineStr"/>
-      <c r="DQ20" t="inlineStr"/>
-      <c r="DR20" t="inlineStr"/>
-      <c r="DS20" t="inlineStr"/>
-      <c r="DT20" t="inlineStr"/>
-      <c r="DU20" t="inlineStr"/>
-      <c r="DV20" t="inlineStr"/>
-      <c r="DW20" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX20" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY20" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ20" t="inlineStr"/>
-      <c r="EA20" t="inlineStr"/>
-      <c r="EB20" t="inlineStr"/>
-      <c r="EC20" t="inlineStr"/>
-      <c r="ED20" t="inlineStr"/>
-      <c r="EE20" t="inlineStr"/>
-      <c r="EF20" t="inlineStr"/>
-      <c r="EG20" t="inlineStr"/>
-      <c r="EH20" t="inlineStr"/>
-      <c r="EI20" t="inlineStr"/>
-      <c r="EJ20" t="inlineStr"/>
-      <c r="EK20" t="inlineStr"/>
-      <c r="EL20" t="inlineStr"/>
-      <c r="EM20" t="inlineStr"/>
-      <c r="EN20" t="inlineStr"/>
-      <c r="EO20" t="inlineStr"/>
-      <c r="EP20" t="inlineStr"/>
+      <c r="DZ20" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB20" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC20" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED20" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE20" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF20" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG20" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI20" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ20" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK20" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL20" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM20" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN20" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO20" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP20" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ20" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER20" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES20" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET20" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Taylor Walls', 'hitter_id': 670764, 'bats': 'S', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Taylor Walls', 'hitter_id': 670764, 'bats': 'S', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU20" t="n">
@@ -13868,10 +14604,10 @@
         <v>3.32</v>
       </c>
       <c r="EW20" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX20" t="n">
-        <v>2.829284064665127</v>
+        <v>2.8895563231432</v>
       </c>
       <c r="EY20" t="n">
         <v>0.4</v>
@@ -13879,8 +14615,12 @@
       <c r="EZ20" t="n">
         <v>1</v>
       </c>
-      <c r="FA20" t="inlineStr"/>
-      <c r="FB20" t="inlineStr"/>
+      <c r="FA20" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB20" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC20" t="n">
         <v>0.215148506660048</v>
       </c>
@@ -13900,13 +14640,13 @@
         <v>0.2232394194602052</v>
       </c>
       <c r="FI20" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.2232394194602052</v>
+        <v>0.2154155916710076</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.2232394194602052</v>
+        <v>0.2154155916710076</v>
       </c>
       <c r="FL20" t="n">
         <v>0.2222222222222222</v>
@@ -13915,28 +14655,28 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="FN20" t="n">
-        <v>0.2232394194602052</v>
+        <v>0.2154155916710076</v>
       </c>
       <c r="FO20" t="n">
-        <v>0.001017197237982992</v>
+        <v>-0.006806630551214582</v>
       </c>
       <c r="FP20" t="n">
-        <v>0.001017197237982992</v>
+        <v>0.006806630551214582</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.6316077320838527</v>
+        <v>0.6224554850165938</v>
       </c>
       <c r="FR20" t="n">
-        <v>0.4682637759656125</v>
+        <v>0.463374856495284</v>
       </c>
       <c r="FS20" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="FT20" t="n">
         <v>0.2504761904761905</v>
       </c>
       <c r="FU20" t="n">
-        <v>30.26795534730877</v>
+        <v>28.74258083609895</v>
       </c>
       <c r="FV20" t="n">
         <v>24.99999999999999</v>
@@ -13963,7 +14703,7 @@
         <v>27.75510204081632</v>
       </c>
       <c r="GD20" t="n">
-        <v>36.6644319770098</v>
+        <v>35.93283024540806</v>
       </c>
       <c r="GE20" t="inlineStr">
         <is>
@@ -13971,7 +14711,7 @@
         </is>
       </c>
       <c r="GF20" t="n">
-        <v>23.62896160161752</v>
+        <v>23.17134924825458</v>
       </c>
       <c r="GG20" t="n">
         <v>59.59526530612245</v>
@@ -13982,10 +14722,10 @@
         </is>
       </c>
       <c r="GI20" t="n">
-        <v>58.5071207659652</v>
+        <v>56.47387169979227</v>
       </c>
       <c r="GJ20" t="n">
-        <v>28.93630837388111</v>
+        <v>28.64903186204939</v>
       </c>
       <c r="GK20" t="inlineStr">
         <is>
@@ -14021,12 +14761,12 @@
       </c>
       <c r="GS20" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.223', 'Low matchup score (37)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Model AVG is below preferred threshold at 0.215', 'Low matchup score (36)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT20" t="inlineStr">
         <is>
-          <t>Taylor Walls projects for 0.63 hits with a 46.8% 1+ hit probability.</t>
+          <t>Taylor Walls projects for 0.62 hits with a 46.3% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU20" t="inlineStr">
@@ -14044,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14064,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14746,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -14766,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -14793,26 +15533,26 @@
         <v>849815</v>
       </c>
       <c r="D22" t="n">
-        <v>595978</v>
+        <v>622761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austin Hedges</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -14828,7 +15568,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -14841,20 +15581,20 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/595978</t>
+          <t>https://www.mlb.com/player/622761</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Austin+Hedges</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jorge+Mateo</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>642547</v>
+        <v>542888</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -14864,12 +15604,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/642547</t>
+          <t>https://www.mlb.com/player/542888</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -14882,55 +15622,55 @@
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="AB22" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1952191235059761</v>
+        <v>0.2092050209205021</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.3820754716981132</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="AE22" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AF22" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AG22" t="n">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.2465116279069768</v>
+        <v>0.2028985507246377</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.4320987654320987</v>
+        <v>0.345679012345679</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
         <v>7</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AN22" t="n">
         <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.4</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="AR22" t="n">
         <v>30</v>
@@ -14942,67 +15682,67 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AV22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AW22" t="n">
         <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="AZ22" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.26</v>
+        <v>0.2772277227722773</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="BD22" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BE22" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.255</v>
+        <v>0.202970297029703</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI22" t="n">
         <v>2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BK22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BM22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BN22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BO22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
@@ -15010,88 +15750,88 @@
         </is>
       </c>
       <c r="BQ22" t="n">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="BR22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BS22" t="n">
-        <v>0.2075126721578107</v>
+        <v>0.2200826137037087</v>
       </c>
       <c r="BT22" t="n">
-        <v>0.563972815859773</v>
+        <v>0.5853541326839626</v>
       </c>
       <c r="BU22" t="n">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="BV22" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.2429906542056075</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="BX22" t="n">
         <v>100</v>
       </c>
       <c r="BY22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.2075126721578107</v>
+        <v>0.2200826137037087</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.2400432992839359</v>
+        <v>0.2397906685364844</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.2296148133538454</v>
+        <v>0.2342991807369619</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.2269657391884607</v>
+        <v>0.2204775329983686</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.2400432992839359</v>
+        <v>0.2397906685364844</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.2400432992839359</v>
+        <v>0.2397906685364844</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.2296148133538454</v>
+        <v>0.2342991807369619</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.2163265306122449</v>
+        <v>0.24</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.1881188118811881</v>
+        <v>0.2329246935201401</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.2291639158830639</v>
+        <v>0.2371773448931661</v>
       </c>
       <c r="CK22" t="n">
-        <v>0.2180101377262486</v>
+        <v>0.2315116355174224</v>
       </c>
       <c r="CL22" t="n">
-        <v>0.2146357713341391</v>
+        <v>0.2175157662026078</v>
       </c>
       <c r="CM22" t="n">
-        <v>0.2291639158830639</v>
+        <v>0.2371773448931661</v>
       </c>
       <c r="CN22" t="n">
-        <v>0.2291639158830639</v>
+        <v>0.2371773448931661</v>
       </c>
       <c r="CO22" t="n">
-        <v>0.2180101377262486</v>
+        <v>0.2315116355174224</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.2429906542056075</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="CQ22" t="n">
-        <v>0.1750972762645914</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="CR22" t="n">
-        <v>0.1910112359550562</v>
+        <v>0.2097976570820021</v>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -15099,124 +15839,124 @@
         </is>
       </c>
       <c r="CT22" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="CU22" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="CV22" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CW22" t="n">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="CX22" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="CY22" t="n">
-        <v>0.2429906542056075</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="CZ22" t="n">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="DA22" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="DB22" t="n">
-        <v>0.2163265306122449</v>
+        <v>0.24</v>
       </c>
       <c r="DC22" t="n">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="DD22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.1750972762645914</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="DF22" t="n">
-        <v>808</v>
+        <v>571</v>
       </c>
       <c r="DG22" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="DH22" t="n">
-        <v>0.1881188118811881</v>
+        <v>0.2329246935201401</v>
       </c>
       <c r="DI22" t="n">
-        <v>1691</v>
+        <v>939</v>
       </c>
       <c r="DJ22" t="n">
-        <v>323</v>
+        <v>197</v>
       </c>
       <c r="DK22" t="n">
-        <v>0.1910112359550562</v>
+        <v>0.2097976570820021</v>
       </c>
       <c r="DL22" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="DM22" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="DO22" t="n">
-        <v>0.0863013698630137</v>
+        <v>0.1233766233766234</v>
       </c>
       <c r="DP22" t="n">
-        <v>8.57396449704142</v>
+        <v>7.641509433962264</v>
       </c>
       <c r="DQ22" t="n">
-        <v>1.224852071005917</v>
+        <v>1.018867924528302</v>
       </c>
       <c r="DR22" t="n">
-        <v>730</v>
+        <v>154</v>
       </c>
       <c r="DS22" t="n">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="DT22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="DU22" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="DV22" t="n">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="DW22" t="n">
-        <v>169</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="DX22" t="n">
-        <v>0.9526627218934911</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY22" t="n">
         <v>0.245</v>
       </c>
       <c r="DZ22" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EA22" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EB22" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EC22" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="ED22" t="n">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="EE22" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="EF22" t="n">
-        <v>2105</v>
+        <v>685</v>
       </c>
       <c r="EG22" t="n">
-        <v>1962</v>
+        <v>1045</v>
       </c>
       <c r="EH22" t="inlineStr">
         <is>
@@ -15224,54 +15964,54 @@
         </is>
       </c>
       <c r="EI22" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EJ22" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EK22" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EL22" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EM22" t="n">
-        <v>0.2693602693602694</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EN22" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="EO22" t="n">
-        <v>0.2104513064133017</v>
+        <v>0.254014598540146</v>
       </c>
       <c r="EP22" t="n">
-        <v>0.2099898063200815</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="EQ22" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER22" t="n">
-        <v>1.002791983464375</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES22" t="n">
-        <v>1.003802348336595</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET22" t="inlineStr">
         <is>
-          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Austin Hedges', 'hitter_id': 595978, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Jorge Mateo', 'hitter_id': 622761, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU22" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="EV22" t="n">
         <v>3.32</v>
       </c>
       <c r="EW22" t="n">
-        <v>3.502671341757233</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX22" t="n">
-        <v>3.048883961448604</v>
+        <v>3.175928862397432</v>
       </c>
       <c r="EY22" t="n">
         <v>0.44</v>
@@ -15280,94 +16020,94 @@
         <v>1</v>
       </c>
       <c r="FA22" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="FB22" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="FC22" t="n">
-        <v>0.2209984249050311</v>
+        <v>0.221232943741891</v>
       </c>
       <c r="FD22" t="n">
-        <v>0.2163821676697599</v>
+        <v>0.2267502719660932</v>
       </c>
       <c r="FE22" t="n">
-        <v>0.2163821676697599</v>
+        <v>0.2267502719660932</v>
       </c>
       <c r="FF22" t="n">
-        <v>0.3131617647058824</v>
+        <v>0.3588461538461539</v>
       </c>
       <c r="FG22" t="n">
-        <v>0.2855127627656269</v>
+        <v>0.317562190814875</v>
       </c>
       <c r="FH22" t="n">
-        <v>0.231226128549357</v>
+        <v>0.2402274066822888</v>
       </c>
       <c r="FI22" t="n">
-        <v>0.9935910096226218</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ22" t="n">
-        <v>0.2297442025164858</v>
+        <v>0.2318082042642195</v>
       </c>
       <c r="FK22" t="n">
-        <v>0.2297442025164858</v>
+        <v>0.2318082042642195</v>
       </c>
       <c r="FL22" t="n">
-        <v>0.2465116279069768</v>
+        <v>0.2028985507246377</v>
       </c>
       <c r="FM22" t="n">
-        <v>0.2465116279069768</v>
+        <v>0.2028985507246377</v>
       </c>
       <c r="FN22" t="n">
-        <v>0.2297442025164858</v>
+        <v>0.2318082042642195</v>
       </c>
       <c r="FO22" t="n">
-        <v>-0.016767425390491</v>
+        <v>0.02890965353958178</v>
       </c>
       <c r="FP22" t="n">
-        <v>0.016767425390491</v>
+        <v>0.02890965353958178</v>
       </c>
       <c r="FQ22" t="n">
-        <v>0.7004634142883134</v>
+        <v>0.7362063664632541</v>
       </c>
       <c r="FR22" t="n">
-        <v>0.5036447676204268</v>
+        <v>0.5210726515530727</v>
       </c>
       <c r="FS22" t="n">
-        <v>-101</v>
+        <v>-109</v>
       </c>
       <c r="FT22" t="n">
-        <v>0.3388235294117647</v>
+        <v>0.3710256410256411</v>
       </c>
       <c r="FU22" t="n">
-        <v>41.74390238138555</v>
+        <v>47.701061077209</v>
       </c>
       <c r="FV22" t="n">
-        <v>33.33333333333332</v>
+        <v>0</v>
       </c>
       <c r="FW22" t="n">
-        <v>16.18392479871218</v>
+        <v>23.5780080610051</v>
       </c>
       <c r="FX22" t="n">
-        <v>4.073663454050321</v>
+        <v>14.66073853311933</v>
       </c>
       <c r="FY22" t="n">
-        <v>93.42560553633221</v>
+        <v>100</v>
       </c>
       <c r="FZ22" t="n">
-        <v>30.2</v>
+        <v>27.8</v>
       </c>
       <c r="GA22" t="n">
-        <v>52.92682926829269</v>
+        <v>45.1219512195122</v>
       </c>
       <c r="GB22" t="n">
         <v>19.8</v>
       </c>
       <c r="GC22" t="n">
-        <v>28.7339380196523</v>
+        <v>14.5578231292517</v>
       </c>
       <c r="GD22" t="n">
-        <v>34.59105751326329</v>
+        <v>36.69960149280031</v>
       </c>
       <c r="GE22" t="inlineStr">
         <is>
@@ -15375,10 +16115,10 @@
         </is>
       </c>
       <c r="GF22" t="n">
-        <v>32.62316807792642</v>
+        <v>29.78576357183058</v>
       </c>
       <c r="GG22" t="n">
-        <v>36.51633460538687</v>
+        <v>31.61060029865605</v>
       </c>
       <c r="GH22" t="inlineStr">
         <is>
@@ -15386,10 +16126,10 @@
         </is>
       </c>
       <c r="GI22" t="n">
-        <v>51.6193807563894</v>
+        <v>61.59519848352102</v>
       </c>
       <c r="GJ22" t="n">
-        <v>27.63769933859338</v>
+        <v>28.08349583081864</v>
       </c>
       <c r="GK22" t="inlineStr">
         <is>
@@ -15420,22 +16160,22 @@
       </c>
       <c r="GR22" t="inlineStr">
         <is>
-          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="GS22" t="inlineStr">
         <is>
-          <t>['Model AVG is slightly below season AVG by -0.017', 'Model AVG is below preferred threshold at 0.230', 'Low matchup score (35)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is below preferred threshold at 0.232', 'Low matchup score (37)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT22" t="inlineStr">
         <is>
-          <t>Austin Hedges projects for 0.70 hits with a 50.4% 1+ hit probability.</t>
+          <t>Jorge Mateo projects for 0.74 hits with a 52.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU22" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|595978</t>
+          <t>2026-10-19|849815|622761</t>
         </is>
       </c>
       <c r="GV22" t="b">
@@ -15448,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -15468,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -15495,26 +16235,26 @@
         <v>849815</v>
       </c>
       <c r="D23" t="n">
-        <v>622761</v>
+        <v>595978</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -15530,7 +16270,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -15543,23 +16283,37 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/player/622761</t>
+          <t>https://www.mlb.com/player/595978</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://www.baseball-reference.com/search/search.fcgi?search=Jorge+Mateo</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Austin+Hedges</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>642547</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/642547</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -15570,55 +16324,55 @@
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="AB23" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.2092050209205021</v>
+        <v>0.1952191235059761</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.391304347826087</v>
+        <v>0.3820754716981132</v>
       </c>
       <c r="AE23" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AF23" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AG23" t="n">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.2465116279069768</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.345679012345679</v>
+        <v>0.4320987654320987</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>7</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AN23" t="n">
         <v>15</v>
       </c>
       <c r="AO23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AR23" t="n">
         <v>30</v>
@@ -15630,67 +16384,67 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AV23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="AZ23" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.2772277227722773</v>
+        <v>0.26</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="BD23" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BE23" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="BF23" t="n">
-        <v>0.202970297029703</v>
+        <v>0.255</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.39</v>
+        <v>0.395</v>
       </c>
       <c r="BH23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI23" t="n">
         <v>2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BM23" t="n">
         <v>5</v>
       </c>
-      <c r="BL23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>9</v>
-      </c>
       <c r="BN23" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BO23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
@@ -15698,88 +16452,88 @@
         </is>
       </c>
       <c r="BQ23" t="n">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="BR23" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BS23" t="n">
-        <v>0.2200826137037087</v>
+        <v>0.2075126721578107</v>
       </c>
       <c r="BT23" t="n">
-        <v>0.5853541326839626</v>
+        <v>0.563972815859773</v>
       </c>
       <c r="BU23" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="BV23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.2467532467532468</v>
+        <v>0.2429906542056075</v>
       </c>
       <c r="BX23" t="n">
         <v>100</v>
       </c>
       <c r="BY23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.2200826137037087</v>
+        <v>0.2075126721578107</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.2397906685364844</v>
+        <v>0.2400432992839359</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.2342991807369619</v>
+        <v>0.2296148133538454</v>
       </c>
       <c r="CC23" t="n">
-        <v>0.2204775329983686</v>
+        <v>0.2269657391884607</v>
       </c>
       <c r="CD23" t="n">
-        <v>0.2397906685364844</v>
+        <v>0.2400432992839359</v>
       </c>
       <c r="CE23" t="n">
-        <v>0.2397906685364844</v>
+        <v>0.2400432992839359</v>
       </c>
       <c r="CF23" t="n">
-        <v>0.2342991807369619</v>
+        <v>0.2296148133538454</v>
       </c>
       <c r="CG23" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.25</v>
       </c>
       <c r="CH23" t="n">
-        <v>0.24</v>
+        <v>0.2163265306122449</v>
       </c>
       <c r="CI23" t="n">
-        <v>0.2329246935201401</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.2371773448931661</v>
+        <v>0.2291639158830639</v>
       </c>
       <c r="CK23" t="n">
-        <v>0.2315116355174224</v>
+        <v>0.2180101377262486</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.2175157662026078</v>
+        <v>0.2146357713341391</v>
       </c>
       <c r="CM23" t="n">
-        <v>0.2371773448931661</v>
+        <v>0.2291639158830639</v>
       </c>
       <c r="CN23" t="n">
-        <v>0.2371773448931661</v>
+        <v>0.2291639158830639</v>
       </c>
       <c r="CO23" t="n">
-        <v>0.2315116355174224</v>
+        <v>0.2180101377262486</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.2467532467532468</v>
+        <v>0.2429906542056075</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.2088888888888889</v>
+        <v>0.1750972762645914</v>
       </c>
       <c r="CR23" t="n">
-        <v>0.2097976570820021</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -15787,123 +16541,179 @@
         </is>
       </c>
       <c r="CT23" t="n">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="CU23" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="CV23" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.25</v>
       </c>
       <c r="CW23" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="CX23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="CY23" t="n">
-        <v>0.2467532467532468</v>
+        <v>0.2429906542056075</v>
       </c>
       <c r="CZ23" t="n">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="DA23" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="DB23" t="n">
-        <v>0.24</v>
+        <v>0.2163265306122449</v>
       </c>
       <c r="DC23" t="n">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="DD23" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.2088888888888889</v>
+        <v>0.1750972762645914</v>
       </c>
       <c r="DF23" t="n">
-        <v>571</v>
+        <v>808</v>
       </c>
       <c r="DG23" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="DH23" t="n">
-        <v>0.2329246935201401</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="DI23" t="n">
-        <v>939</v>
+        <v>1691</v>
       </c>
       <c r="DJ23" t="n">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="DK23" t="n">
-        <v>0.2097976570820021</v>
-      </c>
-      <c r="DL23" t="inlineStr"/>
+        <v>0.1910112359550562</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>4.42</v>
+      </c>
       <c r="DM23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO23" t="inlineStr"/>
-      <c r="DP23" t="inlineStr"/>
-      <c r="DQ23" t="inlineStr"/>
-      <c r="DR23" t="inlineStr"/>
-      <c r="DS23" t="inlineStr"/>
-      <c r="DT23" t="inlineStr"/>
-      <c r="DU23" t="inlineStr"/>
-      <c r="DV23" t="inlineStr"/>
-      <c r="DW23" t="inlineStr"/>
+        <v>0.2136986301369863</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>0.0863013698630137</v>
+      </c>
+      <c r="DP23" t="n">
+        <v>8.57396449704142</v>
+      </c>
+      <c r="DQ23" t="n">
+        <v>1.224852071005917</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>730</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>161</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>23</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>63</v>
+      </c>
+      <c r="DV23" t="n">
+        <v>156</v>
+      </c>
+      <c r="DW23" t="n">
+        <v>169</v>
+      </c>
       <c r="DX23" t="n">
-        <v>1</v>
+        <v>0.9526627218934911</v>
       </c>
       <c r="DY23" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ23" t="inlineStr"/>
-      <c r="EA23" t="inlineStr"/>
-      <c r="EB23" t="inlineStr"/>
-      <c r="EC23" t="inlineStr"/>
-      <c r="ED23" t="inlineStr"/>
-      <c r="EE23" t="inlineStr"/>
-      <c r="EF23" t="inlineStr"/>
-      <c r="EG23" t="inlineStr"/>
-      <c r="EH23" t="inlineStr"/>
-      <c r="EI23" t="inlineStr"/>
-      <c r="EJ23" t="inlineStr"/>
-      <c r="EK23" t="inlineStr"/>
-      <c r="EL23" t="inlineStr"/>
-      <c r="EM23" t="inlineStr"/>
-      <c r="EN23" t="inlineStr"/>
-      <c r="EO23" t="inlineStr"/>
-      <c r="EP23" t="inlineStr"/>
+      <c r="DZ23" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EA23" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EB23" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EC23" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="ED23" t="n">
+        <v>297</v>
+      </c>
+      <c r="EE23" t="n">
+        <v>158</v>
+      </c>
+      <c r="EF23" t="n">
+        <v>2105</v>
+      </c>
+      <c r="EG23" t="n">
+        <v>1962</v>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI23" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EJ23" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EK23" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EL23" t="n">
+        <v>0.2099898063200815</v>
+      </c>
+      <c r="EM23" t="n">
+        <v>0.2693602693602694</v>
+      </c>
+      <c r="EN23" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="EO23" t="n">
+        <v>0.2104513064133017</v>
+      </c>
+      <c r="EP23" t="n">
+        <v>0.2099898063200815</v>
+      </c>
       <c r="EQ23" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ER23" t="n">
-        <v>1</v>
+        <v>1.002791983464375</v>
       </c>
       <c r="ES23" t="n">
-        <v>1</v>
+        <v>1.003802348336595</v>
       </c>
       <c r="ET23" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Jorge Mateo', 'hitter_id': 622761, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.42, 'whip': 1.33, 'k_rate': 0.2136986301369863, 'bb_rate': 0.0863013698630137, 'hits_per_9': 8.57396449704142, 'hr_per_9': 1.2248520710059172, 'batters_faced': 730, 'baa_vs_lhb_season': 0.26936026936026936, 'baa_vs_rhb_season': 0.25316455696202533, 'baa_vs_lhb_career': 0.21045130641330168, 'baa_vs_rhb_career': 0.20998980632008155, 'pitcher': 'Freddy Peralta', 'pitcher_id': 642547, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/642547', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Freddy+Peralta', 'hitter': 'Austin Hedges', 'hitter_id': 595978, 'bats': 'R', 'team': 'CLE', 'opp': 'TB', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU23" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="EV23" t="n">
         <v>3.32</v>
       </c>
       <c r="EW23" t="n">
-        <v>3.32</v>
+        <v>3.502671341757233</v>
       </c>
       <c r="EX23" t="n">
-        <v>3.109683257918552</v>
+        <v>3.048883961448604</v>
       </c>
       <c r="EY23" t="n">
         <v>0.44</v>
@@ -15911,91 +16721,95 @@
       <c r="EZ23" t="n">
         <v>1</v>
       </c>
-      <c r="FA23" t="inlineStr"/>
-      <c r="FB23" t="inlineStr"/>
+      <c r="FA23" t="n">
+        <v>0.2531645569620253</v>
+      </c>
+      <c r="FB23" t="n">
+        <v>0.2531645569620253</v>
+      </c>
       <c r="FC23" t="n">
-        <v>0.221232943741891</v>
+        <v>0.2209984249050311</v>
       </c>
       <c r="FD23" t="n">
-        <v>0.2267502719660932</v>
+        <v>0.2163821676697599</v>
       </c>
       <c r="FE23" t="n">
-        <v>0.2267502719660932</v>
+        <v>0.2163821676697599</v>
       </c>
       <c r="FF23" t="n">
-        <v>0.3588461538461539</v>
+        <v>0.3131617647058824</v>
       </c>
       <c r="FG23" t="n">
-        <v>0.317562190814875</v>
+        <v>0.2855127627656269</v>
       </c>
       <c r="FH23" t="n">
-        <v>0.2402274066822888</v>
+        <v>0.231226128549357</v>
       </c>
       <c r="FI23" t="n">
-        <v>1</v>
+        <v>0.9935910096226218</v>
       </c>
       <c r="FJ23" t="n">
-        <v>0.2402274066822888</v>
+        <v>0.2297442025164858</v>
       </c>
       <c r="FK23" t="n">
-        <v>0.2402274066822888</v>
+        <v>0.2297442025164858</v>
       </c>
       <c r="FL23" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.2465116279069768</v>
       </c>
       <c r="FM23" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.2465116279069768</v>
       </c>
       <c r="FN23" t="n">
-        <v>0.2402274066822888</v>
+        <v>0.2297442025164858</v>
       </c>
       <c r="FO23" t="n">
-        <v>0.03732885595765112</v>
+        <v>-0.016767425390491</v>
       </c>
       <c r="FP23" t="n">
-        <v>0.03732885595765112</v>
+        <v>0.016767425390491</v>
       </c>
       <c r="FQ23" t="n">
-        <v>0.7470311446531048</v>
+        <v>0.7004634142883134</v>
       </c>
       <c r="FR23" t="n">
-        <v>0.5262289754880186</v>
+        <v>0.5036447676204268</v>
       </c>
       <c r="FS23" t="n">
-        <v>-111</v>
+        <v>-101</v>
       </c>
       <c r="FT23" t="n">
-        <v>0.3710256410256411</v>
+        <v>0.3388235294117647</v>
       </c>
       <c r="FU23" t="n">
-        <v>49.50519077551746</v>
+        <v>41.74390238138555</v>
       </c>
       <c r="FV23" t="n">
-        <v>0</v>
+        <v>33.33333333333332</v>
       </c>
       <c r="FW23" t="n">
-        <v>23.5780080610051</v>
+        <v>16.18392479871218</v>
       </c>
       <c r="FX23" t="n">
-        <v>9.140271493212687</v>
+        <v>4.073663454050321</v>
       </c>
       <c r="FY23" t="n">
-        <v>100</v>
+        <v>93.42560553633221</v>
       </c>
       <c r="FZ23" t="n">
-        <v>27.8</v>
+        <v>30.2</v>
       </c>
       <c r="GA23" t="n">
-        <v>45.1219512195122</v>
+        <v>52.92682926829269</v>
       </c>
       <c r="GB23" t="n">
         <v>19.8</v>
       </c>
       <c r="GC23" t="n">
-        <v>14.5578231292517</v>
+        <v>28.7339380196523</v>
       </c>
       <c r="GD23" t="n">
-        <v>37.43120322440204</v>
+        <v>34.59105751326329</v>
       </c>
       <c r="GE23" t="inlineStr">
         <is>
@@ -16003,10 +16817,10 @@
         </is>
       </c>
       <c r="GF23" t="n">
-        <v>29.55413709573619</v>
+        <v>32.62316807792642</v>
       </c>
       <c r="GG23" t="n">
-        <v>31.61060029865605</v>
+        <v>36.51633460538687</v>
       </c>
       <c r="GH23" t="inlineStr">
         <is>
@@ -16014,10 +16828,10 @@
         </is>
       </c>
       <c r="GI23" t="n">
-        <v>63.64727447132084</v>
+        <v>51.6193807563894</v>
       </c>
       <c r="GJ23" t="n">
-        <v>27.57841258567068</v>
+        <v>27.63769933859338</v>
       </c>
       <c r="GK23" t="inlineStr">
         <is>
@@ -16048,22 +16862,22 @@
       </c>
       <c r="GR23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Neutral-to-favorable pitcher matchup: opposing pitcher allows a 0.253 season BAA vs this batter hand']</t>
         </is>
       </c>
       <c r="GS23" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.240', 'Low matchup score (37)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Model AVG is slightly below season AVG by -0.017', 'Model AVG is below preferred threshold at 0.230', 'Low matchup score (35)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT23" t="inlineStr">
         <is>
-          <t>Jorge Mateo projects for 0.75 hits with a 52.6% 1+ hit probability.</t>
+          <t>Austin Hedges projects for 0.70 hits with a 50.4% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU23" t="inlineStr">
         <is>
-          <t>2026-10-19|849815|622761</t>
+          <t>2026-10-19|849815|595978</t>
         </is>
       </c>
       <c r="GV23" t="b">
@@ -16076,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16096,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16179,15 +16993,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Cedric+Mullins</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -16468,57 +17296,113 @@
       <c r="DK24" t="n">
         <v>0.2468619246861925</v>
       </c>
-      <c r="DL24" t="inlineStr"/>
+      <c r="DL24" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM24" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO24" t="inlineStr"/>
-      <c r="DP24" t="inlineStr"/>
-      <c r="DQ24" t="inlineStr"/>
-      <c r="DR24" t="inlineStr"/>
-      <c r="DS24" t="inlineStr"/>
-      <c r="DT24" t="inlineStr"/>
-      <c r="DU24" t="inlineStr"/>
-      <c r="DV24" t="inlineStr"/>
-      <c r="DW24" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP24" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ24" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX24" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY24" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ24" t="inlineStr"/>
-      <c r="EA24" t="inlineStr"/>
-      <c r="EB24" t="inlineStr"/>
-      <c r="EC24" t="inlineStr"/>
-      <c r="ED24" t="inlineStr"/>
-      <c r="EE24" t="inlineStr"/>
-      <c r="EF24" t="inlineStr"/>
-      <c r="EG24" t="inlineStr"/>
-      <c r="EH24" t="inlineStr"/>
-      <c r="EI24" t="inlineStr"/>
-      <c r="EJ24" t="inlineStr"/>
-      <c r="EK24" t="inlineStr"/>
-      <c r="EL24" t="inlineStr"/>
-      <c r="EM24" t="inlineStr"/>
-      <c r="EN24" t="inlineStr"/>
-      <c r="EO24" t="inlineStr"/>
-      <c r="EP24" t="inlineStr"/>
+      <c r="DZ24" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA24" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB24" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC24" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED24" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE24" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF24" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG24" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI24" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ24" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK24" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL24" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM24" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN24" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO24" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP24" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ24" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER24" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES24" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET24" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Cedric Mullins', 'hitter_id': 656775, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Cedric Mullins', 'hitter_id': 656775, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU24" t="n">
@@ -16528,10 +17412,10 @@
         <v>3.32</v>
       </c>
       <c r="EW24" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX24" t="n">
-        <v>2.903346613545817</v>
+        <v>2.965196627027508</v>
       </c>
       <c r="EY24" t="n">
         <v>0.44</v>
@@ -16539,8 +17423,12 @@
       <c r="EZ24" t="n">
         <v>1</v>
       </c>
-      <c r="FA24" t="inlineStr"/>
-      <c r="FB24" t="inlineStr"/>
+      <c r="FA24" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB24" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC24" t="n">
         <v>0.1969251375407837</v>
       </c>
@@ -16560,13 +17448,13 @@
         <v>0.1910128387010195</v>
       </c>
       <c r="FI24" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ24" t="n">
-        <v>0.1910128387010195</v>
+        <v>0.1843184495150229</v>
       </c>
       <c r="FK24" t="n">
-        <v>0.1910128387010195</v>
+        <v>0.1843184495150229</v>
       </c>
       <c r="FL24" t="n">
         <v>0.2050113895216401</v>
@@ -16575,28 +17463,28 @@
         <v>0.2050113895216401</v>
       </c>
       <c r="FN24" t="n">
-        <v>0.1910128387010195</v>
+        <v>0.1843184495150229</v>
       </c>
       <c r="FO24" t="n">
-        <v>-0.0139985508206206</v>
+        <v>-0.02069294000661717</v>
       </c>
       <c r="FP24" t="n">
-        <v>0.0139985508206206</v>
+        <v>0.02069294000661717</v>
       </c>
       <c r="FQ24" t="n">
-        <v>0.5545764783863782</v>
+        <v>0.5465404448008859</v>
       </c>
       <c r="FR24" t="n">
-        <v>0.4256845553000667</v>
+        <v>0.4210507433001299</v>
       </c>
       <c r="FS24" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="FT24" t="n">
         <v>0.1007843137254902</v>
       </c>
       <c r="FU24" t="n">
-        <v>17.42941306439637</v>
+        <v>16.09007413348098</v>
       </c>
       <c r="FV24" t="n">
         <v>0</v>
@@ -16623,7 +17511,7 @@
         <v>26.52494331065759</v>
       </c>
       <c r="GD24" t="n">
-        <v>37.15515009005803</v>
+        <v>36.42354835845629</v>
       </c>
       <c r="GE24" t="inlineStr">
         <is>
@@ -16631,7 +17519,7 @@
         </is>
       </c>
       <c r="GF24" t="n">
-        <v>10.49303522110228</v>
+        <v>10.09123354182766</v>
       </c>
       <c r="GG24" t="n">
         <v>68.43874149659864</v>
@@ -16642,10 +17530,10 @@
         </is>
       </c>
       <c r="GI24" t="n">
-        <v>53.02603296137909</v>
+        <v>51.2738950813103</v>
       </c>
       <c r="GJ24" t="n">
-        <v>26.6808569505689</v>
+        <v>26.41255606792721</v>
       </c>
       <c r="GK24" t="inlineStr">
         <is>
@@ -16681,12 +17569,12 @@
       </c>
       <c r="GS24" t="inlineStr">
         <is>
-          <t>['Model AVG is slightly below season AVG by -0.014', 'Model AVG is below preferred threshold at 0.191', 'Low matchup score (37)', 'Recent 15 AB form is cold at 0.067', 'Recent 30 AB form is below target at 0.133', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Model AVG is slightly below season AVG by -0.021', 'Model AVG is below preferred threshold at 0.184', 'Low matchup score (36)', 'Recent 15 AB form is cold at 0.067', 'Recent 30 AB form is below target at 0.133', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT24" t="inlineStr">
         <is>
-          <t>Cedric Mullins projects for 0.55 hits with a 42.6% 1+ hit probability.</t>
+          <t>Cedric Mullins projects for 0.55 hits with a 42.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU24" t="inlineStr">
@@ -16704,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -16724,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17406,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -17426,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18108,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -18128,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -18211,15 +19099,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Victor+Mesa+Jr.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -18500,57 +19402,113 @@
       <c r="DK27" t="n">
         <v>0.2233502538071066</v>
       </c>
-      <c r="DL27" t="inlineStr"/>
+      <c r="DL27" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM27" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN27" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO27" t="inlineStr"/>
-      <c r="DP27" t="inlineStr"/>
-      <c r="DQ27" t="inlineStr"/>
-      <c r="DR27" t="inlineStr"/>
-      <c r="DS27" t="inlineStr"/>
-      <c r="DT27" t="inlineStr"/>
-      <c r="DU27" t="inlineStr"/>
-      <c r="DV27" t="inlineStr"/>
-      <c r="DW27" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP27" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ27" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR27" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU27" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV27" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW27" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX27" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY27" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ27" t="inlineStr"/>
-      <c r="EA27" t="inlineStr"/>
-      <c r="EB27" t="inlineStr"/>
-      <c r="EC27" t="inlineStr"/>
-      <c r="ED27" t="inlineStr"/>
-      <c r="EE27" t="inlineStr"/>
-      <c r="EF27" t="inlineStr"/>
-      <c r="EG27" t="inlineStr"/>
-      <c r="EH27" t="inlineStr"/>
-      <c r="EI27" t="inlineStr"/>
-      <c r="EJ27" t="inlineStr"/>
-      <c r="EK27" t="inlineStr"/>
-      <c r="EL27" t="inlineStr"/>
-      <c r="EM27" t="inlineStr"/>
-      <c r="EN27" t="inlineStr"/>
-      <c r="EO27" t="inlineStr"/>
-      <c r="EP27" t="inlineStr"/>
+      <c r="DZ27" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA27" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB27" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC27" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED27" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE27" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF27" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG27" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI27" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ27" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK27" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL27" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM27" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN27" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO27" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP27" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ27" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER27" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES27" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET27" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Victor Mesa Jr.', 'hitter_id': 683748, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Victor Mesa Jr.', 'hitter_id': 683748, 'bats': 'L', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU27" t="n">
@@ -18560,10 +19518,10 @@
         <v>3.32</v>
       </c>
       <c r="EW27" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX27" t="n">
-        <v>2.977862595419848</v>
+        <v>3.041300023391427</v>
       </c>
       <c r="EY27" t="n">
         <v>0.44</v>
@@ -18571,8 +19529,12 @@
       <c r="EZ27" t="n">
         <v>1</v>
       </c>
-      <c r="FA27" t="inlineStr"/>
-      <c r="FB27" t="inlineStr"/>
+      <c r="FA27" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="FB27" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="FC27" t="n">
         <v>0.2464729547303284</v>
       </c>
@@ -18592,13 +19554,13 @@
         <v>0.2366978073989155</v>
       </c>
       <c r="FI27" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ27" t="n">
-        <v>0.2366978073989155</v>
+        <v>0.2284023061489676</v>
       </c>
       <c r="FK27" t="n">
-        <v>0.2366978073989155</v>
+        <v>0.2284023061489676</v>
       </c>
       <c r="FL27" t="n">
         <v>0.2595744680851064</v>
@@ -18607,28 +19569,28 @@
         <v>0.2595744680851064</v>
       </c>
       <c r="FN27" t="n">
-        <v>0.2366978073989155</v>
+        <v>0.2284023061489676</v>
       </c>
       <c r="FO27" t="n">
-        <v>-0.0228766606861909</v>
+        <v>-0.03117216193613878</v>
       </c>
       <c r="FP27" t="n">
-        <v>0.0228766606861909</v>
+        <v>0.03117216193613878</v>
       </c>
       <c r="FQ27" t="n">
-        <v>0.7048535470711216</v>
+        <v>0.694639939033511</v>
       </c>
       <c r="FR27" t="n">
-        <v>0.5058190567967817</v>
+        <v>0.5007458224319106</v>
       </c>
       <c r="FS27" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="FT27" t="n">
         <v>0.2093870967741936</v>
       </c>
       <c r="FU27" t="n">
-        <v>42.47559117852025</v>
+        <v>40.77332317225182</v>
       </c>
       <c r="FV27" t="n">
         <v>8.33333333333333</v>
@@ -18637,7 +19599,7 @@
         <v>32.67685351294076</v>
       </c>
       <c r="FX27" t="n">
-        <v>0</v>
+        <v>3.441668615952223</v>
       </c>
       <c r="FY27" t="n">
         <v>17.28652751423152</v>
@@ -18655,7 +19617,7 @@
         <v>22.59129967776584</v>
       </c>
       <c r="GD27" t="n">
-        <v>41.07074140517631</v>
+        <v>40.33913967357457</v>
       </c>
       <c r="GE27" t="inlineStr">
         <is>
@@ -18663,7 +19625,7 @@
         </is>
       </c>
       <c r="GF27" t="n">
-        <v>23.7246091960043</v>
+        <v>23.69576240035709</v>
       </c>
       <c r="GG27" t="n">
         <v>25.06371934190878</v>
@@ -18674,10 +19636,10 @@
         </is>
       </c>
       <c r="GI27" t="n">
-        <v>47.59602593897981</v>
+        <v>45.52675304261565</v>
       </c>
       <c r="GJ27" t="n">
-        <v>22.55018725483054</v>
+        <v>22.67913987365253</v>
       </c>
       <c r="GK27" t="inlineStr">
         <is>
@@ -18713,12 +19675,12 @@
       </c>
       <c r="GS27" t="inlineStr">
         <is>
-          <t>['Model AVG is slightly below season AVG by -0.023', 'Model AVG is below preferred threshold at 0.237', 'Low matchup score (41)', 'Low split reliability score (38)', 'Recent 30 AB form is below target at 0.161', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup risk: opposing pitcher has limited this batter hand to a 0.222 season BAA', 'Model AVG is materially below season AVG by -0.031', 'Model AVG is below preferred threshold at 0.228', 'Low matchup score (40)', 'Low split reliability score (38)', 'Recent 30 AB form is below target at 0.161', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT27" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr. projects for 0.70 hits with a 50.6% 1+ hit probability.</t>
+          <t>Victor Mesa Jr. projects for 0.69 hits with a 50.1% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU27" t="inlineStr">
@@ -18736,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -18756,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -18839,15 +19801,29 @@
           <t>https://www.baseball-reference.com/search/search.fcgi?search=Ryan+Vilade</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>542888</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/player/542888</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -19128,57 +20104,113 @@
       <c r="DK28" t="n">
         <v>0.1869918699186992</v>
       </c>
-      <c r="DL28" t="inlineStr"/>
+      <c r="DL28" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DM28" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="DN28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO28" t="inlineStr"/>
-      <c r="DP28" t="inlineStr"/>
-      <c r="DQ28" t="inlineStr"/>
-      <c r="DR28" t="inlineStr"/>
-      <c r="DS28" t="inlineStr"/>
-      <c r="DT28" t="inlineStr"/>
-      <c r="DU28" t="inlineStr"/>
-      <c r="DV28" t="inlineStr"/>
-      <c r="DW28" t="inlineStr"/>
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="DP28" t="n">
+        <v>7.641509433962264</v>
+      </c>
+      <c r="DQ28" t="n">
+        <v>1.018867924528302</v>
+      </c>
+      <c r="DR28" t="n">
+        <v>154</v>
+      </c>
+      <c r="DS28" t="n">
+        <v>30</v>
+      </c>
+      <c r="DT28" t="n">
+        <v>4</v>
+      </c>
+      <c r="DU28" t="n">
+        <v>19</v>
+      </c>
+      <c r="DV28" t="n">
+        <v>34</v>
+      </c>
+      <c r="DW28" t="n">
+        <v>35.33333333333334</v>
+      </c>
       <c r="DX28" t="n">
-        <v>1</v>
+        <v>0.8490566037735848</v>
       </c>
       <c r="DY28" t="n">
         <v>0.245</v>
       </c>
-      <c r="DZ28" t="inlineStr"/>
-      <c r="EA28" t="inlineStr"/>
-      <c r="EB28" t="inlineStr"/>
-      <c r="EC28" t="inlineStr"/>
-      <c r="ED28" t="inlineStr"/>
-      <c r="EE28" t="inlineStr"/>
-      <c r="EF28" t="inlineStr"/>
-      <c r="EG28" t="inlineStr"/>
-      <c r="EH28" t="inlineStr"/>
-      <c r="EI28" t="inlineStr"/>
-      <c r="EJ28" t="inlineStr"/>
-      <c r="EK28" t="inlineStr"/>
-      <c r="EL28" t="inlineStr"/>
-      <c r="EM28" t="inlineStr"/>
-      <c r="EN28" t="inlineStr"/>
-      <c r="EO28" t="inlineStr"/>
-      <c r="EP28" t="inlineStr"/>
+      <c r="DZ28" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EA28" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EB28" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EC28" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="ED28" t="n">
+        <v>72</v>
+      </c>
+      <c r="EE28" t="n">
+        <v>59</v>
+      </c>
+      <c r="EF28" t="n">
+        <v>685</v>
+      </c>
+      <c r="EG28" t="n">
+        <v>1045</v>
+      </c>
+      <c r="EH28" t="inlineStr">
+        <is>
+          <t>mlb_pitching_statSplits</t>
+        </is>
+      </c>
+      <c r="EI28" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EJ28" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EK28" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EL28" t="n">
+        <v>0.2248803827751196</v>
+      </c>
+      <c r="EM28" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="EN28" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="EO28" t="n">
+        <v>0.254014598540146</v>
+      </c>
+      <c r="EP28" t="n">
+        <v>0.2248803827751196</v>
+      </c>
       <c r="EQ28" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ER28" t="n">
-        <v>1</v>
+        <v>1.007492624356775</v>
       </c>
       <c r="ES28" t="n">
-        <v>1</v>
+        <v>1.006168831168831</v>
       </c>
       <c r="ET28" t="inlineStr">
         <is>
-          <t>{'era': None, 'whip': 1.28, 'k_rate': 0.22, 'bb_rate': None, 'hits_per_9': None, 'hr_per_9': None, 'baa_vs_lhb_season': None, 'baa_vs_rhb_season': None, 'baa_vs_lhb_career': None, 'baa_vs_rhb_career': None, 'pitcher': None, 'pitcher_id': None, 'pitcher_hand': 'R', 'pitcher_mlb_url': None, 'pitcher_baseball_reference_url': None, 'hitter': 'Ryan Vilade', 'hitter_id': 668723, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
+          <t>{'era': 4.58, 'whip': 1.39, 'k_rate': 0.22077922077922077, 'bb_rate': 0.12337662337662338, 'hits_per_9': 7.641509433962264, 'hr_per_9': 1.0188679245283019, 'batters_faced': 154, 'baa_vs_lhb_season': 0.2222222222222222, 'baa_vs_rhb_season': 0.23728813559322035, 'baa_vs_lhb_career': 0.25401459854014596, 'baa_vs_rhb_career': 0.22488038277511962, 'pitcher': 'Shawn Armstrong', 'pitcher_id': 542888, 'pitcher_hand': 'R', 'pitcher_mlb_url': 'https://www.mlb.com/player/542888', 'pitcher_baseball_reference_url': 'https://www.baseball-reference.com/search/search.fcgi?search=Shawn+Armstrong', 'hitter': 'Ryan Vilade', 'hitter_id': 668723, 'bats': 'R', 'team': 'TB', 'opp': 'CLE', 'game_pk': 849815, 'game_time_et': '8:08 PM'}</t>
         </is>
       </c>
       <c r="EU28" t="n">
@@ -19188,10 +20220,10 @@
         <v>3.32</v>
       </c>
       <c r="EW28" t="n">
-        <v>3.32</v>
+        <v>3.390725983525761</v>
       </c>
       <c r="EX28" t="n">
-        <v>2.925899280575539</v>
+        <v>2.988229733682775</v>
       </c>
       <c r="EY28" t="n">
         <v>0.44</v>
@@ -19199,8 +20231,12 @@
       <c r="EZ28" t="n">
         <v>1</v>
       </c>
-      <c r="FA28" t="inlineStr"/>
-      <c r="FB28" t="inlineStr"/>
+      <c r="FA28" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="FB28" t="n">
+        <v>0.2372881355932203</v>
+      </c>
       <c r="FC28" t="n">
         <v>0.2464720145483936</v>
       </c>
@@ -19220,13 +20256,13 @@
         <v>0.2444980049430815</v>
       </c>
       <c r="FI28" t="n">
-        <v>1</v>
+        <v>0.9649531977456506</v>
       </c>
       <c r="FJ28" t="n">
-        <v>0.2444980049430815</v>
+        <v>0.2359291317122584</v>
       </c>
       <c r="FK28" t="n">
-        <v>0.2444980049430815</v>
+        <v>0.2359291317122584</v>
       </c>
       <c r="FL28" t="n">
         <v>0.2448979591836735</v>
@@ -19235,28 +20271,28 @@
         <v>0.2448979591836735</v>
       </c>
       <c r="FN28" t="n">
-        <v>0.2444980049430815</v>
+        <v>0.2359291317122584</v>
       </c>
       <c r="FO28" t="n">
-        <v>-0.0003999542405919154</v>
+        <v>-0.008968827471415031</v>
       </c>
       <c r="FP28" t="n">
-        <v>0.0003999542405919154</v>
+        <v>0.008968827471415031</v>
       </c>
       <c r="FQ28" t="n">
-        <v>0.715376536765117</v>
+        <v>0.7050104464245303</v>
       </c>
       <c r="FR28" t="n">
-        <v>0.5109920523445042</v>
+        <v>0.5058965873848287</v>
       </c>
       <c r="FS28" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="FT28" t="n">
         <v>0.2856843395252838</v>
       </c>
       <c r="FU28" t="n">
-        <v>44.22942279418616</v>
+        <v>42.50174107075503</v>
       </c>
       <c r="FV28" t="n">
         <v>8.33333333333333</v>
@@ -19283,7 +20319,7 @@
         <v>15.7312925170068</v>
       </c>
       <c r="GD28" t="n">
-        <v>35.39393183015781</v>
+        <v>34.66233009855608</v>
       </c>
       <c r="GE28" t="inlineStr">
         <is>
@@ -19291,7 +20327,7 @@
         </is>
       </c>
       <c r="GF28" t="n">
-        <v>24.57705165747269</v>
+        <v>24.05874714044334</v>
       </c>
       <c r="GG28" t="n">
         <v>20.16954753608761</v>
@@ -19302,10 +20338,10 @@
         </is>
       </c>
       <c r="GI28" t="n">
-        <v>51.89101011867108</v>
+        <v>49.66802555704807</v>
       </c>
       <c r="GJ28" t="n">
-        <v>20.85913221598449</v>
+        <v>20.33890932851972</v>
       </c>
       <c r="GK28" t="inlineStr">
         <is>
@@ -19341,12 +20377,12 @@
       </c>
       <c r="GS28" t="inlineStr">
         <is>
-          <t>['Model AVG is below preferred threshold at 0.244', 'Low matchup score (35)', 'Low split reliability score (20)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
+          <t>['Pitcher matchup caution: opposing pitcher allows only a 0.237 season BAA vs this batter hand', 'Model AVG is below preferred threshold at 0.236', 'Low matchup score (35)', 'Low split reliability score (20)', 'No confirmed lineup slot from MLB feed yet', 'Some pinch-hit or role risk']</t>
         </is>
       </c>
       <c r="GT28" t="inlineStr">
         <is>
-          <t>Ryan Vilade projects for 0.72 hits with a 51.1% 1+ hit probability.</t>
+          <t>Ryan Vilade projects for 0.71 hits with a 50.6% 1+ hit probability.</t>
         </is>
       </c>
       <c r="GU28" t="inlineStr">
@@ -19364,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-19 01:48:32 AM</t>
+          <t>2026-10-19 01:27:47 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -19384,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-19T01:48:32.502694-04:00</t>
+          <t>2026-10-19T13:27:47.713786-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-19T16:25:24.963345-04:00</t>
+          <t>2026-10-19T20:07:55.870963-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:07:55 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-23 03:04:16 AM</t>
+          <t>2026-10-23 11:43:58 AM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-23T03:04:16.948519-04:00</t>
+          <t>2026-10-23T11:43:58.422191-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43:58 AM</t>
+          <t>2026-10-23 02:55:33 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-23T11:43:58.422191-04:00</t>
+          <t>2026-10-23T14:55:33.502360-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-23T17:53:44.315315-04:00</t>
+          <t>2026-10-23T20:18:39.843544-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:18:39 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-24 01:27:26 AM</t>
+          <t>2026-10-24 10:28:20 AM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-24T01:27:26.083986-04:00</t>
+          <t>2026-10-24T10:28:20.486817-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-24 10:28:20 AM</t>
+          <t>2026-10-24 01:54:44 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-24T10:28:20.486817-04:00</t>
+          <t>2026-10-24T13:54:44.706948-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2152,7 +2152,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-24 04:20:43 PM</t>
+          <t>2026-10-24 06:57:14 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-24T16:20:43.173360-04:00</t>
+          <t>2026-10-24T18:57:14.127223-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD19"/>
+  <dimension ref="A1:HE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5818,7 +5853,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6341,12 +6376,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6379,11 +6414,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6408,7 +6443,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6417,7 +6452,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6524,7 +6564,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7047,12 +7087,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7085,11 +7125,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7114,7 +7154,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7123,7 +7163,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7230,7 +7275,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7753,12 +7798,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7791,11 +7836,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7820,7 +7865,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7829,7 +7874,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7936,7 +7986,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8459,12 +8509,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8497,11 +8547,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8526,7 +8576,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8535,7 +8585,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8642,7 +8697,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9165,12 +9220,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9232,7 +9287,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9241,7 +9296,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9348,7 +9408,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9871,12 +9931,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9909,11 +9969,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9938,7 +9998,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9947,7 +10007,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10054,7 +10119,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10577,12 +10642,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10615,11 +10680,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10644,7 +10709,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10653,7 +10718,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10760,7 +10830,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11283,12 +11353,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11321,11 +11391,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11350,7 +11420,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11359,7 +11429,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11466,7 +11541,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11989,12 +12064,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -12027,11 +12102,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12056,7 +12131,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12065,7 +12140,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12172,7 +12252,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12695,12 +12775,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12733,11 +12813,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12762,7 +12842,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12771,7 +12851,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12878,7 +12963,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13401,12 +13486,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13439,11 +13524,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13468,7 +13553,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13477,7 +13562,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13584,7 +13674,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14107,12 +14197,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14145,11 +14235,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14174,7 +14264,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-24T18:57:14.127223-04:00</t>
+          <t>2026-10-24T20:53:06.350605-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14183,7 +14273,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:53:06 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD23"/>
+  <dimension ref="A1:HE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3696,7 +3716,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4219,12 +4239,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4257,11 +4277,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4286,7 +4306,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4295,7 +4315,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4402,7 +4427,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4925,12 +4950,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4963,11 +4988,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4992,7 +5017,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5001,7 +5026,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5104,7 +5134,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5627,12 +5657,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5665,11 +5695,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5694,7 +5724,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5703,7 +5733,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5810,7 +5845,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6333,12 +6368,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6371,11 +6406,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6400,7 +6435,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6409,7 +6444,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6512,7 +6552,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7035,12 +7075,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7073,11 +7113,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7102,7 +7142,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7111,7 +7151,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7218,7 +7263,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7741,12 +7786,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7779,11 +7824,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7808,7 +7853,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7817,7 +7862,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7924,7 +7974,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8447,12 +8497,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8485,11 +8535,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8514,7 +8564,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8523,7 +8573,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8626,7 +8681,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9149,12 +9204,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9187,11 +9242,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9216,7 +9271,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9225,7 +9280,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9328,7 +9388,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9851,12 +9911,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9889,11 +9949,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9918,7 +9978,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9927,7 +9987,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10030,7 +10095,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10553,12 +10618,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10591,11 +10656,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10620,7 +10685,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10629,7 +10694,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10732,7 +10802,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11255,12 +11325,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11293,11 +11363,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11322,7 +11392,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11331,7 +11401,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11434,7 +11509,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11957,12 +12032,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -11995,11 +12070,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12024,7 +12099,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12033,7 +12108,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12136,7 +12216,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12659,12 +12739,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12697,11 +12777,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12726,7 +12806,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12735,7 +12815,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12838,7 +12923,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13361,12 +13446,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13399,11 +13484,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13428,7 +13513,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13437,7 +13522,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13544,7 +13634,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14067,12 +14157,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14105,11 +14195,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14134,7 +14224,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14143,7 +14233,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -14246,7 +14341,7 @@
         </is>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
@@ -14769,12 +14864,12 @@
       </c>
       <c r="GM20" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN20" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO20" t="b">
@@ -14807,11 +14902,11 @@
         </is>
       </c>
       <c r="GV20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW20" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX20" t="inlineStr">
@@ -14836,7 +14931,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14845,7 +14940,12 @@
         </is>
       </c>
       <c r="HD20" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE20" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -14948,7 +15048,7 @@
         </is>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
@@ -15471,12 +15571,12 @@
       </c>
       <c r="GM21" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN21" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO21" t="b">
@@ -15509,11 +15609,11 @@
         </is>
       </c>
       <c r="GV21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW21" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX21" t="inlineStr">
@@ -15538,7 +15638,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15547,7 +15647,12 @@
         </is>
       </c>
       <c r="HD21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE21" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -15654,7 +15759,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
@@ -16177,12 +16282,12 @@
       </c>
       <c r="GM22" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN22" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO22" t="b">
@@ -16215,11 +16320,11 @@
         </is>
       </c>
       <c r="GV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW22" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX22" t="inlineStr">
@@ -16244,7 +16349,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16253,7 +16358,12 @@
         </is>
       </c>
       <c r="HD22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE22" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -16356,7 +16466,7 @@
         </is>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
@@ -16879,12 +16989,12 @@
       </c>
       <c r="GM23" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN23" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO23" t="b">
@@ -16917,11 +17027,11 @@
         </is>
       </c>
       <c r="GV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW23" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX23" t="inlineStr">
@@ -16946,7 +17056,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-26T16:20:38.783792-04:00</t>
+          <t>2026-10-26T20:15:37.671726-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16955,7 +17065,12 @@
         </is>
       </c>
       <c r="HD23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE23" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:15:37 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2074,7 +2074,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:01:33 AM</t>
+          <t>2026-10-27 12:28:35 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-27T02:01:33.796446-04:00</t>
+          <t>2026-10-27T12:28:35.731644-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -2074,7 +2074,7 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="GX3" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY3" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="GX4" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="GX5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY5" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="GX6" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY6" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="GX7" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY7" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="GX8" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY8" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="GX9" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY9" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="GX10" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY10" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="GX11" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY11" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="GX12" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY12" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="GX13" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY13" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="GX14" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY14" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="GX15" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY15" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="GX16" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY16" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="GX17" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY17" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="GX18" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY18" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="GX19" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY19" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="GX20" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY20" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="GX21" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY21" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="GX22" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY22" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="GX23" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY23" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="GX24" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY24" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="HB24" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC24" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="GX25" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY25" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="HB25" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC25" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="GX26" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY26" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="HB26" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC26" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="GX27" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY27" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="HB27" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC27" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="GX28" t="inlineStr">
         <is>
-          <t>2026-10-27 12:28:35 PM</t>
+          <t>2026-10-27 03:55:17 PM</t>
         </is>
       </c>
       <c r="GY28" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="HB28" t="inlineStr">
         <is>
-          <t>2026-10-27T12:28:35.731644-04:00</t>
+          <t>2026-10-27T15:55:17.577903-04:00</t>
         </is>
       </c>
       <c r="HC28" t="inlineStr">

--- a/outputs/prophit_today.xlsx
+++ b/outputs/prophit_today.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD23"/>
+  <dimension ref="A1:HE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,11 @@
           <t>started_or_ineligible_games_preserved_from_freeze_count</t>
         </is>
       </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>frozen_as_of_et</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
@@ -2105,12 +2110,12 @@
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO2" t="b">
@@ -2143,11 +2148,11 @@
         </is>
       </c>
       <c r="GV2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
@@ -2181,7 +2186,12 @@
         </is>
       </c>
       <c r="HD2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2298,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
@@ -2811,12 +2821,12 @@
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN3" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO3" t="b">
@@ -2849,11 +2859,11 @@
         </is>
       </c>
       <c r="GV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW3" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX3" t="inlineStr">
@@ -2878,7 +2888,7 @@
       </c>
       <c r="HB3" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC3" t="inlineStr">
@@ -2887,7 +2897,12 @@
         </is>
       </c>
       <c r="HD3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE3" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2994,7 +3009,7 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
@@ -3517,12 +3532,12 @@
       </c>
       <c r="GM4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN4" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO4" t="b">
@@ -3555,11 +3570,11 @@
         </is>
       </c>
       <c r="GV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW4" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX4" t="inlineStr">
@@ -3584,7 +3599,7 @@
       </c>
       <c r="HB4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC4" t="inlineStr">
@@ -3593,7 +3608,12 @@
         </is>
       </c>
       <c r="HD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE4" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3700,7 +3720,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -4223,12 +4243,12 @@
       </c>
       <c r="GM5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN5" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO5" t="b">
@@ -4261,11 +4281,11 @@
         </is>
       </c>
       <c r="GV5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW5" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX5" t="inlineStr">
@@ -4290,7 +4310,7 @@
       </c>
       <c r="HB5" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC5" t="inlineStr">
@@ -4299,7 +4319,12 @@
         </is>
       </c>
       <c r="HD5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE5" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4406,7 +4431,7 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -4929,12 +4954,12 @@
       </c>
       <c r="GM6" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN6" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO6" t="b">
@@ -4967,11 +4992,11 @@
         </is>
       </c>
       <c r="GV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW6" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX6" t="inlineStr">
@@ -4996,7 +5021,7 @@
       </c>
       <c r="HB6" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC6" t="inlineStr">
@@ -5005,7 +5030,12 @@
         </is>
       </c>
       <c r="HD6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE6" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5112,7 +5142,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
@@ -5635,12 +5665,12 @@
       </c>
       <c r="GM7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN7" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO7" t="b">
@@ -5673,11 +5703,11 @@
         </is>
       </c>
       <c r="GV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW7" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX7" t="inlineStr">
@@ -5702,7 +5732,7 @@
       </c>
       <c r="HB7" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC7" t="inlineStr">
@@ -5711,7 +5741,12 @@
         </is>
       </c>
       <c r="HD7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE7" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5814,7 +5849,7 @@
         </is>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
@@ -6337,12 +6372,12 @@
       </c>
       <c r="GM8" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN8" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO8" t="b">
@@ -6375,11 +6410,11 @@
         </is>
       </c>
       <c r="GV8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW8" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX8" t="inlineStr">
@@ -6404,7 +6439,7 @@
       </c>
       <c r="HB8" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC8" t="inlineStr">
@@ -6413,7 +6448,12 @@
         </is>
       </c>
       <c r="HD8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE8" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6516,7 +6556,7 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
@@ -7039,12 +7079,12 @@
       </c>
       <c r="GM9" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN9" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO9" t="b">
@@ -7077,11 +7117,11 @@
         </is>
       </c>
       <c r="GV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW9" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX9" t="inlineStr">
@@ -7106,7 +7146,7 @@
       </c>
       <c r="HB9" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC9" t="inlineStr">
@@ -7115,7 +7155,12 @@
         </is>
       </c>
       <c r="HD9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE9" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7218,7 +7263,7 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
@@ -7741,12 +7786,12 @@
       </c>
       <c r="GM10" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN10" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO10" t="b">
@@ -7779,11 +7824,11 @@
         </is>
       </c>
       <c r="GV10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW10" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX10" t="inlineStr">
@@ -7808,7 +7853,7 @@
       </c>
       <c r="HB10" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC10" t="inlineStr">
@@ -7817,7 +7862,12 @@
         </is>
       </c>
       <c r="HD10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE10" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7920,7 +7970,7 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
@@ -8443,12 +8493,12 @@
       </c>
       <c r="GM11" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN11" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO11" t="b">
@@ -8481,11 +8531,11 @@
         </is>
       </c>
       <c r="GV11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW11" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX11" t="inlineStr">
@@ -8510,7 +8560,7 @@
       </c>
       <c r="HB11" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC11" t="inlineStr">
@@ -8519,7 +8569,12 @@
         </is>
       </c>
       <c r="HD11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE11" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8622,7 +8677,7 @@
         </is>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
@@ -9145,12 +9200,12 @@
       </c>
       <c r="GM12" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN12" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO12" t="b">
@@ -9183,11 +9238,11 @@
         </is>
       </c>
       <c r="GV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW12" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX12" t="inlineStr">
@@ -9212,7 +9267,7 @@
       </c>
       <c r="HB12" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC12" t="inlineStr">
@@ -9221,7 +9276,12 @@
         </is>
       </c>
       <c r="HD12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE12" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9328,7 +9388,7 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
@@ -9851,12 +9911,12 @@
       </c>
       <c r="GM13" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN13" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO13" t="b">
@@ -9889,11 +9949,11 @@
         </is>
       </c>
       <c r="GV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW13" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX13" t="inlineStr">
@@ -9918,7 +9978,7 @@
       </c>
       <c r="HB13" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC13" t="inlineStr">
@@ -9927,7 +9987,12 @@
         </is>
       </c>
       <c r="HD13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10030,7 +10095,7 @@
         </is>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
@@ -10553,12 +10618,12 @@
       </c>
       <c r="GM14" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN14" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO14" t="b">
@@ -10591,11 +10656,11 @@
         </is>
       </c>
       <c r="GV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW14" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX14" t="inlineStr">
@@ -10620,7 +10685,7 @@
       </c>
       <c r="HB14" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC14" t="inlineStr">
@@ -10629,7 +10694,12 @@
         </is>
       </c>
       <c r="HD14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE14" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10732,7 +10802,7 @@
         </is>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
@@ -11255,12 +11325,12 @@
       </c>
       <c r="GM15" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN15" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO15" t="b">
@@ -11293,11 +11363,11 @@
         </is>
       </c>
       <c r="GV15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW15" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX15" t="inlineStr">
@@ -11322,7 +11392,7 @@
       </c>
       <c r="HB15" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC15" t="inlineStr">
@@ -11331,7 +11401,12 @@
         </is>
       </c>
       <c r="HD15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE15" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11434,7 +11509,7 @@
         </is>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
@@ -11957,12 +12032,12 @@
       </c>
       <c r="GM16" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN16" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO16" t="b">
@@ -11995,11 +12070,11 @@
         </is>
       </c>
       <c r="GV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW16" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX16" t="inlineStr">
@@ -12024,7 +12099,7 @@
       </c>
       <c r="HB16" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC16" t="inlineStr">
@@ -12033,7 +12108,12 @@
         </is>
       </c>
       <c r="HD16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE16" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12136,7 +12216,7 @@
         </is>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
@@ -12659,12 +12739,12 @@
       </c>
       <c r="GM17" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN17" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO17" t="b">
@@ -12697,11 +12777,11 @@
         </is>
       </c>
       <c r="GV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW17" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX17" t="inlineStr">
@@ -12726,7 +12806,7 @@
       </c>
       <c r="HB17" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC17" t="inlineStr">
@@ -12735,7 +12815,12 @@
         </is>
       </c>
       <c r="HD17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE17" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12838,7 +12923,7 @@
         </is>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
@@ -13361,12 +13446,12 @@
       </c>
       <c r="GM18" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN18" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO18" t="b">
@@ -13399,11 +13484,11 @@
         </is>
       </c>
       <c r="GV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW18" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX18" t="inlineStr">
@@ -13428,7 +13513,7 @@
       </c>
       <c r="HB18" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC18" t="inlineStr">
@@ -13437,7 +13522,12 @@
         </is>
       </c>
       <c r="HD18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE18" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13544,7 +13634,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
@@ -14067,12 +14157,12 @@
       </c>
       <c r="GM19" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN19" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO19" t="b">
@@ -14105,11 +14195,11 @@
         </is>
       </c>
       <c r="GV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW19" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX19" t="inlineStr">
@@ -14134,7 +14224,7 @@
       </c>
       <c r="HB19" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC19" t="inlineStr">
@@ -14143,7 +14233,12 @@
         </is>
       </c>
       <c r="HD19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE19" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -14246,7 +14341,7 @@
         </is>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
@@ -14769,12 +14864,12 @@
       </c>
       <c r="GM20" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN20" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO20" t="b">
@@ -14807,11 +14902,11 @@
         </is>
       </c>
       <c r="GV20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW20" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX20" t="inlineStr">
@@ -14836,7 +14931,7 @@
       </c>
       <c r="HB20" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC20" t="inlineStr">
@@ -14845,7 +14940,12 @@
         </is>
       </c>
       <c r="HD20" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE20" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -14948,7 +15048,7 @@
         </is>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
@@ -15471,12 +15571,12 @@
       </c>
       <c r="GM21" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN21" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO21" t="b">
@@ -15509,11 +15609,11 @@
         </is>
       </c>
       <c r="GV21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW21" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX21" t="inlineStr">
@@ -15538,7 +15638,7 @@
       </c>
       <c r="HB21" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC21" t="inlineStr">
@@ -15547,7 +15647,12 @@
         </is>
       </c>
       <c r="HD21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE21" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -15654,7 +15759,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
@@ -16177,12 +16282,12 @@
       </c>
       <c r="GM22" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN22" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO22" t="b">
@@ -16215,11 +16320,11 @@
         </is>
       </c>
       <c r="GV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW22" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX22" t="inlineStr">
@@ -16244,7 +16349,7 @@
       </c>
       <c r="HB22" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC22" t="inlineStr">
@@ -16253,7 +16358,12 @@
         </is>
       </c>
       <c r="HD22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE22" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -16356,7 +16466,7 @@
         </is>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
@@ -16879,12 +16989,12 @@
       </c>
       <c r="GM23" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="GN23" t="inlineStr">
         <is>
-          <t>Upcoming game refreshed this run</t>
+          <t>Game started; projection frozen from last pregame run</t>
         </is>
       </c>
       <c r="GO23" t="b">
@@ -16917,11 +17027,11 @@
         </is>
       </c>
       <c r="GV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GW23" t="inlineStr">
         <is>
-          <t>LIVE_REFRESH</t>
+          <t>FROZEN_STARTED</t>
         </is>
       </c>
       <c r="GX23" t="inlineStr">
@@ -16946,7 +17056,7 @@
       </c>
       <c r="HB23" t="inlineStr">
         <is>
-          <t>2026-10-28T16:08:09.485812-04:00</t>
+          <t>2026-10-28T20:38:24.065483-04:00</t>
         </is>
       </c>
       <c r="HC23" t="inlineStr">
@@ -16955,7 +17065,12 @@
         </is>
       </c>
       <c r="HD23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HE23" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:38:24 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>
